--- a/introducciones/comparacion_introducciones.xlsx
+++ b/introducciones/comparacion_introducciones.xlsx
@@ -491,11 +491,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>La traducción automática es un campo de investigación crítico dentro del procesamiento de lenguaje natural que ha evolucionado significativamente en las últimas décadas. Ante el incremento de la globalización y la necesidad de comunicación entre hablantes de diferentes lenguas, se ha vuelto esencial contar con sistemas que traduzcan de manera automática y precisa. A pesar de los avances logrados, especialmente con la introducción de mecanismos de atención que permiten a los modelos enfocarse en partes relevantes de la entrada, persisten desafíos significativos. Las arquitecturas tradicionales, que dependen predominantemente de redes neuronales recurrentes (RNN) o convolucionales, han encontrado dificultades al gestionar largas dependencias en oraciones complejas. Además, las soluciones actuales enfrentan limitaciones sobre cómo representan oraciones, a menudo utilizando vectores de longitud fija que restringen su capacidad para capturar la riqueza del contexto lingüístico, lo que resulta en un rendimiento decreciente con oraciones más largas. En este sentido, se justifica la exploración de nuevas arquitecturas que no sólo eliminen estas restricciones, sino que también optimicen el proceso de traducción, permitiendo un manejo más efectivo de las relaciones en el texto.
-La propuesta central de este trabajo se enfoca en el desarrollo de una nueva arquitectura de traducción automática que busca superar las limitaciones de las soluciones anteriormente mencionadas. Con el objetivo de abordar el desafío que plantea el uso de vectores de longitud fija, esta investigación introduce el concepto de representaciones contextuales dinámicas, las cuales permiten captar la riqueza y los matices del lenguaje en oraciones más extensas. Esta nueva aproximación no solo mejora el manejo de la complejidad lingüística, sino que también agiliza el tratamiento de relaciones a largo plazo dentro del texto, ofreciendo así una respuesta más precisa y flexible ante las variabilidades del lenguaje natural. Al deshacerse de la dependencia de las secuencias alineadas, que han lastrado enfoques previos, se busca también una mayor adaptabilidad y eficacia en el proceso de traducción, un aspecto esencial en un contexto donde las demandas lingüísticas son cada vez más complejas.
-Las contribuciones de este trabajo son múltiples y se detallan a lo largo del documento. En primer lugar, se presenta el desarrollo de una nueva arquitectura de traducción automática que supere las limitaciones anteriores, detallado en la sección 2. A continuación, se discuten las representaciones contextuales dinámicas y su eficacia en la captura de matices del lenguaje en oraciones más largas, y la mejora en el manejo de la complejidad lingüística, presentados en las secciones 3 y 4 respectivamente. La eliminación de la dependencia de secuencias alineadas se evalúa en la sección 5, mientras que la fomento de adaptabilidad y eficacia se analiza en la sección 6. Adicionalmente, en la sección 7, se abordarán las respuestas a las complejas demandas del uso del lenguaje actual, culminando en la sección 8 con una discusión sobre la provisión de soluciones más robustas y coherentes alineadas con las expectativas de precisión y fluidez en la comunicación multilingüe.
-Para validar nuestras contribuciones, se llevarán a cabo una serie de experimentos comparativos que demostrarán el rendimiento superior de la nueva arquitectura de traducción automática frente a modelos existentes. Se realizarán estudios de caso y análisis cualitativos que evidencien la efectividad de las representaciones contextuales dinámicas, así como la optimización en el manejo de la complejidad lingüística, garantizando así soluciones alineadas con las necesidades actuales en el ámbito de la traducción. Las métricas, tales como el análisis de BLEU, se utilizarán para medir la calidad de las traducciones generadas, complementando los resultados obtenidos en los experimentos y reforzando la relevancia de las aportaciones presentadas.
-El resto del artículo está organizado en secciones que detallan los distintos aspectos de la investigación y los hallazgos obtenidos a través de la evaluación. Cada parte aborda de manera específica y estructurada los experimentos comparativos, los estudios de caso y los análisis cualitativos, así como las métricas empleadas para medir la eficacia de las soluciones propuestas. Esta estructura busca proporcionar un marco claro y coherente que facilite la comprensión de la importancia y el impacto de la nueva arquitectura propuesta en el campo de la traducción automática.</t>
+          <t>El artículo "Attention Is All You Need" se sitúa en el ámbito de la traducción automática, un campo que ha visto una notable evolución con la adopción de modelos secuenciales basados en redes neuronales recurrentes (RNN) y redes neuronales convolucionales (CNN). Estos enfoques han permitido avances significativos en la calidad de las traducciones, aunque presentan limitaciones en términos de eficiencia y en la capacidad para manejar oraciones largas. La relevancia de este estudio radica en la creciente demanda de sistemas de traducción más robustos, que sean capaces de ofrecer resultados precisos y coherentes, especialmente en un contexto global donde la comunicación intercultural es esencial.
+En este marco, el trabajo identifica un hueco en los enfoques existentes que dependen de vectores de longitud fija generados por RNNs, lo que limita el rendimiento en oraciones largas. Referencias a trabajos anteriores como los de Bahdanau et al., que introdujeron un modelo de atención, y Sutskever et al., con su arquitectura de codificador-decodificador usando LSTM, muestran que aunque estos modelos han realizado avances, todavía luchan por capturar efectivamente las dependencias a largo plazo y manipular oraciones complejas. Por ende, se presenta la necesidad de desarrollar métodos que aborden de manera más efectiva estas limitaciones, evidenciando el hueco que justifica esta investigación.
+La propuesta central de este trabajo es la introducción del modelo Transformer, que sustituye las arquitecturas tradicionales basadas en RNN y CNN con un enfoque que recurre exclusivamente a mecanismos de atención. Este enfoque es crítico para superar las limitaciones de los modelos existentes, ya que permite gestionar las relaciones de dependencia a largo plazo, lo cual es fundamental para tareas de traducción que requieren un contexto profundo y coherente. Al eliminar la necesidad de estructuras secuenciales rígidas, el Transformer facilita un análisis más eficiente de los datos de entrada y salida, proporcionando al modelo la flexibilidad necesaria para enfocarse en diferentes partes de la secuencia a medida que genera la traducción.
+Las contribuciones del trabajo son significativas e incluyen: la introducción de la arquitectura Transformer que utiliza exclusivamente mecanismos de atención; mejoras en las puntuaciones BLEU en las tareas de traducción de inglés a alemán y francés; y la generalización del modelo para otras tareas de procesamiento de lenguaje natural, como el análisis de la estructura de oraciones. Estas aportaciones se desarrollan a lo largo del documento, destacando en secciones dedicadas a experimentos comparativos.
+La validación del modelo se fundamenta en una serie de experimentos que evalúan su rendimiento frente a arquitecturas anteriores. Se utilizan métricas estándar, como BLEU, para cuantificar la efectividad de las traducciones producidas, además de análisis de casos de estudio que permiten una comprensión profunda sobre cómo el Transformer gestiona las dependencias a largo plazo y las longitudes variables de las secuencias. De esta manera, las contribuciones del modelo están respaldadas por evidencia empírica que demuestra su robustez y eficacia.
+El artículo se organiza en secciones que abordan de manera clara los diversos aspectos de la investigación, comenzando con una introducción que establece el contexto y la importancia del tema. Se sigue con una descripción del modelo Transformer propuesto, luego se presentan los experimentos realizados y, finalmente, una discusión sobre los resultados obtenidos, resaltando la relevancia del enfoque presentado para futuras investigaciones en el ámbito de la traducción automática y otras tareas de procesamiento de lenguaje natural.</t>
         </is>
       </c>
     </row>

--- a/introducciones/comparacion_introducciones.xlsx
+++ b/introducciones/comparacion_introducciones.xlsx
@@ -491,12 +491,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>El artículo "Attention Is All You Need" se sitúa en el ámbito de la traducción automática, un campo que ha visto una notable evolución con la adopción de modelos secuenciales basados en redes neuronales recurrentes (RNN) y redes neuronales convolucionales (CNN). Estos enfoques han permitido avances significativos en la calidad de las traducciones, aunque presentan limitaciones en términos de eficiencia y en la capacidad para manejar oraciones largas. La relevancia de este estudio radica en la creciente demanda de sistemas de traducción más robustos, que sean capaces de ofrecer resultados precisos y coherentes, especialmente en un contexto global donde la comunicación intercultural es esencial.
-En este marco, el trabajo identifica un hueco en los enfoques existentes que dependen de vectores de longitud fija generados por RNNs, lo que limita el rendimiento en oraciones largas. Referencias a trabajos anteriores como los de Bahdanau et al., que introdujeron un modelo de atención, y Sutskever et al., con su arquitectura de codificador-decodificador usando LSTM, muestran que aunque estos modelos han realizado avances, todavía luchan por capturar efectivamente las dependencias a largo plazo y manipular oraciones complejas. Por ende, se presenta la necesidad de desarrollar métodos que aborden de manera más efectiva estas limitaciones, evidenciando el hueco que justifica esta investigación.
-La propuesta central de este trabajo es la introducción del modelo Transformer, que sustituye las arquitecturas tradicionales basadas en RNN y CNN con un enfoque que recurre exclusivamente a mecanismos de atención. Este enfoque es crítico para superar las limitaciones de los modelos existentes, ya que permite gestionar las relaciones de dependencia a largo plazo, lo cual es fundamental para tareas de traducción que requieren un contexto profundo y coherente. Al eliminar la necesidad de estructuras secuenciales rígidas, el Transformer facilita un análisis más eficiente de los datos de entrada y salida, proporcionando al modelo la flexibilidad necesaria para enfocarse en diferentes partes de la secuencia a medida que genera la traducción.
-Las contribuciones del trabajo son significativas e incluyen: la introducción de la arquitectura Transformer que utiliza exclusivamente mecanismos de atención; mejoras en las puntuaciones BLEU en las tareas de traducción de inglés a alemán y francés; y la generalización del modelo para otras tareas de procesamiento de lenguaje natural, como el análisis de la estructura de oraciones. Estas aportaciones se desarrollan a lo largo del documento, destacando en secciones dedicadas a experimentos comparativos.
-La validación del modelo se fundamenta en una serie de experimentos que evalúan su rendimiento frente a arquitecturas anteriores. Se utilizan métricas estándar, como BLEU, para cuantificar la efectividad de las traducciones producidas, además de análisis de casos de estudio que permiten una comprensión profunda sobre cómo el Transformer gestiona las dependencias a largo plazo y las longitudes variables de las secuencias. De esta manera, las contribuciones del modelo están respaldadas por evidencia empírica que demuestra su robustez y eficacia.
-El artículo se organiza en secciones que abordan de manera clara los diversos aspectos de la investigación, comenzando con una introducción que establece el contexto y la importancia del tema. Se sigue con una descripción del modelo Transformer propuesto, luego se presentan los experimentos realizados y, finalmente, una discusión sobre los resultados obtenidos, resaltando la relevancia del enfoque presentado para futuras investigaciones en el ámbito de la traducción automática y otras tareas de procesamiento de lenguaje natural.</t>
+          <t>﻿El campo de la traducción automática ha experimentado avances significativos en las últimas décadas, impulsados por la creciente disponibilidad de datos y mejoras en las técnicas de aprendizaje automático. En particular, la traducción automática basada en redes neuronales ha demostrado ser una innovación clave, superando a los enfoques tradicionales de traducción estadística mediante la utilización de modelos end-to-end que pueden ser entrenados para aprender relaciones complejas entre secuencias de entrada y salida. A medida que los modelos han evolucionado, se ha vuelto evidente que las arquitecturas convencionales, que dependen de vectores de longitud fija para representar oraciones, presentan limitaciones significativas, especialmente cuando se enfrentan a oraciones largas y complejas.
+Las arquitecturas de codificador-decodificador, como las implementadas en los modelos de traducción automática, se han convertido en la base del estado del arte. Sin embargo, a menudo enfrentan desafíos al intentar capturar la rica contextualidad y las dependencias a largo plazo que caracterizan los textos naturales. En este contexto, el surgimiento del modelo Transformer, introducido por 'Attention Is All You Need', representa una convergencia crítica de la investigación, prometiendo mejorar la calidad y la eficiencia de la traducción automática al utilizar mecanismos de atención que permiten una interacción más directa y flexible con las entradas. Este enfoque no solo aborda las limitaciones de sus predecesores, sino que también establece un nuevo paradigma en el ámbito de la traducción automática.
+A pesar de los avances significativos en el campo de la traducción automática, persisten limitaciones en los enfoques existentes que utilizan vectores de longitud fija para representar oraciones en las arquitecturas de codificador-decodificador. Por ejemplo, el trabajo de Bahdanau et al. (2014) presenta un modelo de atención que permite un mejor manejo de la información en contextos complejos, pero su dependencia de un vector de longitud fija todavía restringe su capacidad para traducir oraciones largas de manera eficaz. De manera similar, Sutskever et al. (2014) discuten cómo esta limitación afecta negativamente el rendimiento de los modelos de LSTM cuando se enfrentan a oraciones más extensas, resaltando la necesidad de un enfoque más flexible. Cho et al. (2014) también abordan este problema al presentar una arquitectura que mejora la alineación entre palabras de las entradas y salidas, pero aún se enfrentan a retos debido a la rigidez de los vectores de longitud fija en la representación de oraciones. Estas carencias en la literatura justifican la investigación de nuevos métodos que superen estas limitaciones y ofrezcan soluciones más efectivas en la traducción automática de secuencias complejas.
+La propuesta central del trabajo radica en el desarrollo del modelo Transformer, que utiliza exclusivamente mecanismos de atención para abordar las limitaciones de las arquitecturas de codificador-decodificador tradicionales que dependen de vectores de longitud fija. A diferencia de modelos previos que se ven restringidos al intentar comprimir toda la información necesaria de una oración en un único vector, el Transformer permite que cada palabra en la secuencia de salida pueda considerar todas las posiciones en la entrada de manera flexible y dinámica. Este enfoque es especialmente relevante para resolver la limitación identificada, ya que facilita el manejo de oraciones largas y complejas, permitiendo una traducción más efectiva al captar mejor las dependencias contextuales.
+El uso de mecanismos de atención no solo mejora la calidad de la traducción, sino que también optimiza la eficiencia del entrenamiento al permitir que múltiples palabras se procesen en paralelo. Al eliminar la necesidad de la arquitectura jerárquica tradicional y permitir que el modelo "preste atención" a las partes más relevantes de la entrada para cada palabra generada en la salida, el Transformer establece un nuevo paradigma en las técnicas de traducción automática, ofreciendo una solución robusta a los desafíos planteados por las carencias de los enfoques anteriores.
+- El modelo Transformer introduce un nuevo enfoque en la traducción automática al prescindir de las arquitecturas convencionales de redes neuronales recurrentes y convolucionales, lo que mejora la eficiencia y efectividad de la traducción de oraciones largas y complejas.
+- Se demuestra que el Transformer supera los resultados previos en benchmarks establecidos, alcanzando un BLEU score destacado en la tarea de traducción inglés-alemán y en la tarea inglés-francés, lo que respalda su superioridad sobre modelos anteriores.
+- El modelo es capaz de realizar un entrenamiento más rápido y eficiente, gracias a su capacidad para procesar múltiples palabras en paralelo mediante el mecanismo de atención.
+- Se documenta cómo el Transformer puede generalizar bien a otras tareas de procesamiento del lenguaje natural, lo que sugiere su versatilidad y potencial aplicación en múltiples dominios más allá de la traducción automática.
+La validación del trabajo se lleva a cabo a través de una serie de experimentos aplicados al conjunto de datos WMT 2014, que es un estándar en la evaluación de modelos de traducción automática. Estos experimentos permiten analizar cómo el modelo Transformer, basado en mecanismos de atención, se comporta en comparación con las arquitecturas existentes. Se realizan estudios de caso que demuestran la eficacia del modelo en tareas de traducción de oraciones largas y complejas, destacando su capacidad para captar las dependencias contextuales. Además, se presentan ejemplos ilustrativos que respaldan las contribuciones del trabajo, mostrando cómo el enfoque propuesto mejora la calidad y la eficiencia de la traducción automática, evidenciando así su potencial aplicabilidad en el procesamiento del lenguaje natural.
+El resto del artículo se organiza en secciones que abordan, en primer lugar, una descripción detallada del modelo y su arquitectura, seguidas de la presentación de los experimentos realizados y los resultados obtenidos. Finalmente, se incluye una discusión que reflexiona sobre la generalización del modelo a otras tareas dentro del procesamiento del lenguaje natural.</t>
         </is>
       </c>
     </row>

--- a/introducciones/comparacion_introducciones.xlsx
+++ b/introducciones/comparacion_introducciones.xlsx
@@ -491,17 +491,14 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>﻿El campo de la traducción automática ha experimentado avances significativos en las últimas décadas, impulsados por la creciente disponibilidad de datos y mejoras en las técnicas de aprendizaje automático. En particular, la traducción automática basada en redes neuronales ha demostrado ser una innovación clave, superando a los enfoques tradicionales de traducción estadística mediante la utilización de modelos end-to-end que pueden ser entrenados para aprender relaciones complejas entre secuencias de entrada y salida. A medida que los modelos han evolucionado, se ha vuelto evidente que las arquitecturas convencionales, que dependen de vectores de longitud fija para representar oraciones, presentan limitaciones significativas, especialmente cuando se enfrentan a oraciones largas y complejas.
-Las arquitecturas de codificador-decodificador, como las implementadas en los modelos de traducción automática, se han convertido en la base del estado del arte. Sin embargo, a menudo enfrentan desafíos al intentar capturar la rica contextualidad y las dependencias a largo plazo que caracterizan los textos naturales. En este contexto, el surgimiento del modelo Transformer, introducido por 'Attention Is All You Need', representa una convergencia crítica de la investigación, prometiendo mejorar la calidad y la eficiencia de la traducción automática al utilizar mecanismos de atención que permiten una interacción más directa y flexible con las entradas. Este enfoque no solo aborda las limitaciones de sus predecesores, sino que también establece un nuevo paradigma en el ámbito de la traducción automática.
-A pesar de los avances significativos en el campo de la traducción automática, persisten limitaciones en los enfoques existentes que utilizan vectores de longitud fija para representar oraciones en las arquitecturas de codificador-decodificador. Por ejemplo, el trabajo de Bahdanau et al. (2014) presenta un modelo de atención que permite un mejor manejo de la información en contextos complejos, pero su dependencia de un vector de longitud fija todavía restringe su capacidad para traducir oraciones largas de manera eficaz. De manera similar, Sutskever et al. (2014) discuten cómo esta limitación afecta negativamente el rendimiento de los modelos de LSTM cuando se enfrentan a oraciones más extensas, resaltando la necesidad de un enfoque más flexible. Cho et al. (2014) también abordan este problema al presentar una arquitectura que mejora la alineación entre palabras de las entradas y salidas, pero aún se enfrentan a retos debido a la rigidez de los vectores de longitud fija en la representación de oraciones. Estas carencias en la literatura justifican la investigación de nuevos métodos que superen estas limitaciones y ofrezcan soluciones más efectivas en la traducción automática de secuencias complejas.
-La propuesta central del trabajo radica en el desarrollo del modelo Transformer, que utiliza exclusivamente mecanismos de atención para abordar las limitaciones de las arquitecturas de codificador-decodificador tradicionales que dependen de vectores de longitud fija. A diferencia de modelos previos que se ven restringidos al intentar comprimir toda la información necesaria de una oración en un único vector, el Transformer permite que cada palabra en la secuencia de salida pueda considerar todas las posiciones en la entrada de manera flexible y dinámica. Este enfoque es especialmente relevante para resolver la limitación identificada, ya que facilita el manejo de oraciones largas y complejas, permitiendo una traducción más efectiva al captar mejor las dependencias contextuales.
-El uso de mecanismos de atención no solo mejora la calidad de la traducción, sino que también optimiza la eficiencia del entrenamiento al permitir que múltiples palabras se procesen en paralelo. Al eliminar la necesidad de la arquitectura jerárquica tradicional y permitir que el modelo "preste atención" a las partes más relevantes de la entrada para cada palabra generada en la salida, el Transformer establece un nuevo paradigma en las técnicas de traducción automática, ofreciendo una solución robusta a los desafíos planteados por las carencias de los enfoques anteriores.
-- El modelo Transformer introduce un nuevo enfoque en la traducción automática al prescindir de las arquitecturas convencionales de redes neuronales recurrentes y convolucionales, lo que mejora la eficiencia y efectividad de la traducción de oraciones largas y complejas.
-- Se demuestra que el Transformer supera los resultados previos en benchmarks establecidos, alcanzando un BLEU score destacado en la tarea de traducción inglés-alemán y en la tarea inglés-francés, lo que respalda su superioridad sobre modelos anteriores.
-- El modelo es capaz de realizar un entrenamiento más rápido y eficiente, gracias a su capacidad para procesar múltiples palabras en paralelo mediante el mecanismo de atención.
-- Se documenta cómo el Transformer puede generalizar bien a otras tareas de procesamiento del lenguaje natural, lo que sugiere su versatilidad y potencial aplicación en múltiples dominios más allá de la traducción automática.
-La validación del trabajo se lleva a cabo a través de una serie de experimentos aplicados al conjunto de datos WMT 2014, que es un estándar en la evaluación de modelos de traducción automática. Estos experimentos permiten analizar cómo el modelo Transformer, basado en mecanismos de atención, se comporta en comparación con las arquitecturas existentes. Se realizan estudios de caso que demuestran la eficacia del modelo en tareas de traducción de oraciones largas y complejas, destacando su capacidad para captar las dependencias contextuales. Además, se presentan ejemplos ilustrativos que respaldan las contribuciones del trabajo, mostrando cómo el enfoque propuesto mejora la calidad y la eficiencia de la traducción automática, evidenciando así su potencial aplicabilidad en el procesamiento del lenguaje natural.
-El resto del artículo se organiza en secciones que abordan, en primer lugar, una descripción detallada del modelo y su arquitectura, seguidas de la presentación de los experimentos realizados y los resultados obtenidos. Finalmente, se incluye una discusión que reflexiona sobre la generalización del modelo a otras tareas dentro del procesamiento del lenguaje natural.</t>
+          <t>﻿El estudio del artículo "Attention Is All You Need" se sitúa en el campo de la traducción automática y los modelos de transducción de secuencias, un área crítica en la evolución del procesamiento del lenguaje natural. La relevancia de este campo radica en la necesidad creciente de construir sistemas que no solo interpreten, sino que también traduzcan eficazmente entre diferentes idiomas, aprovechando las mejoras en las tecnologías computacionales. Tradicionalmente, los enfoques de traducción automática se basaban en modelos recurrentes y convolucionales que, aunque efectivos, presentan limitaciones significativas, especialmente en la gestión de dependencias a largo plazo y en la eficacia al manejar oraciones largas. 
+A medida que la investigación avanza, se ha hecho evidente que los modelos basados en atención ofrecen una solución prometedora para superar estas deficiencias. Estos modelos, al permitir que el sistema se enfoque en partes específicas de la entrada a medida que produce la salida, pueden capturar mejor los matices del lenguaje y mejorar la calidad de la traducción. En este contexto, el artículo propone el Transformer como una innovadora arquitectura que se fundamenta exclusivamente en mecanismos de atención, desafiando los enfoques establecidos y estableciendo un nuevo estándar en el rendimiento de la traducción automática.
+A pesar de los avances en los modelos de transducción de secuencias, persisten limitaciones significativas en los enfoques tradicionales basados en redes neuronales recurrentes (RNNs). Por ejemplo, en el trabajo de Cho et al. (2014a), se identifica que depender de un mapeo a un vector de longitud fija es un obstáculo que dificulta el manejo eficaz de secuencias largas. Esto se ve acompañado por las conclusiones de Graves (2013), que destaca que su mecanismo de atención no puede resolver completamente los problemas de reordenamiento a larga distancia necesarios para traducciones precisas. 
+Asimismo, Kalchbrenner y Blunsom (2013) explican que el uso de redes neuronales convolucionales, aunque innovador, puede llevar a una pérdida del orden de las palabras, afectando así la calidad de la traducción. También, Sutskever et al. (2014) concluyen que los modelos basados en RNN son propensos a fallar en oraciones largas, lo que refuerza la noción de que un mapeo rígido puede comprometer el rendimiento. Finalmente, el trabajo de Pouget-Abadie et al. (2014) aborda la segmentación automática como un intento de superar el desafío del exceso de longitud de las oraciones, pero puede no abordar la falta de flexibilidad en el procesamiento de la información contextual. Estas limitaciones marcan claramente la necesidad de enfoques más avanzados, como el propuesto en este artículo, que busca eliminar la dependencia de la recurrencia y mejorar sustancialmente la capacidad de los modelos para manejar la complejidad de las traducciones automáticas.
+Para abordar estas limitaciones, este artículo presenta el modelo Transformer, que se basa exclusivamente en mecanismos de atención y elimina la necesidad de recurrir a redes neuronales recurrentes (RNNs) y redes convolucionales (CNNs). Este enfoque es especialmente relevante dado que las dependencias a largo plazo y la capacidad de manejar secuencias extensas son esenciales para una traducción precisa y efectiva. Con el Transformer, se propone que la atención se focalice en diferentes partes del texto de entrada mientras se genera la salida, lo que permite al sistema adaptarse mejor a la complejidad y la variabilidad de los idiomas.
+Este diseño también permite una paralelización significativa en el proceso de entrenamiento, resultando en tiempos de aprendizaje reducidos sin sacrificar la calidad de la traducción. La decisión de prescindir de una codificación rígida en un vector de longitud fija responde directamente a las carencias identificadas en trabajos previos como los de Cho et al. (2014a) y Sutskever et al. (2014), permitiendo que el Transformer mantenga la contextualización necesaria a lo largo de toda la secuencia de entrada. Con esta nueva arquitectura, se busca no solo mejorar la calidad de las traducciones, sino también ofrecer un enfoque más flexible y eficiente que pueda adaptarse a la complejidad inherente de los lenguajes naturales.
+Las contribuciones del artículo son múltiples: presenta una nueva arquitectura, el Transformer, que logra resultados de primer nivel en traducción automática y mejora la capacidad de atención a partes relevantes de una secuencia de entrada a lo largo de toda su longitud. La validación del trabajo se lleva a cabo a través de una serie de experimentos rigurosos que utilizan métricas estándar como BLEU, aplicadas en conjuntos de datos bien establecidos, específicamente en las tareas de traducción automática del WMT 2014 para las combinaciones de inglés-alemán y inglés-francés. Estas evaluaciones permiten comparar el rendimiento del modelo Transformer con el de los modelos existentes en la literatura, ofreciendo evidencia de su eficacia y calidad superior en la traducción. Además, se analiza cómo las contribuciones del modelo no solo mejoran la calidad de la traducción, sino que también optimizan la eficiencia durante el entrenamiento, validando así la relevancia y el impacto del enfoque propuesto.
+El resto del artículo se organiza en varias secciones que incluyen una descripción detallada de la arquitectura del Transformer, comparaciones con modelos existentes, así como la presentación de experimentos y resultados obtenidos. También se incluye una conclusión que sintetiza las aportaciones y hallazgos del estudio. Estas secciones están diseñadas para guiar al lector a través del razonamiento que respalda el diseño del modelo y su eficacia en el contexto de la traducción automática.</t>
         </is>
       </c>
     </row>

--- a/introducciones/comparacion_introducciones.xlsx
+++ b/introducciones/comparacion_introducciones.xlsx
@@ -491,14 +491,15 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>﻿El estudio del artículo "Attention Is All You Need" se sitúa en el campo de la traducción automática y los modelos de transducción de secuencias, un área crítica en la evolución del procesamiento del lenguaje natural. La relevancia de este campo radica en la necesidad creciente de construir sistemas que no solo interpreten, sino que también traduzcan eficazmente entre diferentes idiomas, aprovechando las mejoras en las tecnologías computacionales. Tradicionalmente, los enfoques de traducción automática se basaban en modelos recurrentes y convolucionales que, aunque efectivos, presentan limitaciones significativas, especialmente en la gestión de dependencias a largo plazo y en la eficacia al manejar oraciones largas. 
-A medida que la investigación avanza, se ha hecho evidente que los modelos basados en atención ofrecen una solución prometedora para superar estas deficiencias. Estos modelos, al permitir que el sistema se enfoque en partes específicas de la entrada a medida que produce la salida, pueden capturar mejor los matices del lenguaje y mejorar la calidad de la traducción. En este contexto, el artículo propone el Transformer como una innovadora arquitectura que se fundamenta exclusivamente en mecanismos de atención, desafiando los enfoques establecidos y estableciendo un nuevo estándar en el rendimiento de la traducción automática.
-A pesar de los avances en los modelos de transducción de secuencias, persisten limitaciones significativas en los enfoques tradicionales basados en redes neuronales recurrentes (RNNs). Por ejemplo, en el trabajo de Cho et al. (2014a), se identifica que depender de un mapeo a un vector de longitud fija es un obstáculo que dificulta el manejo eficaz de secuencias largas. Esto se ve acompañado por las conclusiones de Graves (2013), que destaca que su mecanismo de atención no puede resolver completamente los problemas de reordenamiento a larga distancia necesarios para traducciones precisas. 
-Asimismo, Kalchbrenner y Blunsom (2013) explican que el uso de redes neuronales convolucionales, aunque innovador, puede llevar a una pérdida del orden de las palabras, afectando así la calidad de la traducción. También, Sutskever et al. (2014) concluyen que los modelos basados en RNN son propensos a fallar en oraciones largas, lo que refuerza la noción de que un mapeo rígido puede comprometer el rendimiento. Finalmente, el trabajo de Pouget-Abadie et al. (2014) aborda la segmentación automática como un intento de superar el desafío del exceso de longitud de las oraciones, pero puede no abordar la falta de flexibilidad en el procesamiento de la información contextual. Estas limitaciones marcan claramente la necesidad de enfoques más avanzados, como el propuesto en este artículo, que busca eliminar la dependencia de la recurrencia y mejorar sustancialmente la capacidad de los modelos para manejar la complejidad de las traducciones automáticas.
-Para abordar estas limitaciones, este artículo presenta el modelo Transformer, que se basa exclusivamente en mecanismos de atención y elimina la necesidad de recurrir a redes neuronales recurrentes (RNNs) y redes convolucionales (CNNs). Este enfoque es especialmente relevante dado que las dependencias a largo plazo y la capacidad de manejar secuencias extensas son esenciales para una traducción precisa y efectiva. Con el Transformer, se propone que la atención se focalice en diferentes partes del texto de entrada mientras se genera la salida, lo que permite al sistema adaptarse mejor a la complejidad y la variabilidad de los idiomas.
-Este diseño también permite una paralelización significativa en el proceso de entrenamiento, resultando en tiempos de aprendizaje reducidos sin sacrificar la calidad de la traducción. La decisión de prescindir de una codificación rígida en un vector de longitud fija responde directamente a las carencias identificadas en trabajos previos como los de Cho et al. (2014a) y Sutskever et al. (2014), permitiendo que el Transformer mantenga la contextualización necesaria a lo largo de toda la secuencia de entrada. Con esta nueva arquitectura, se busca no solo mejorar la calidad de las traducciones, sino también ofrecer un enfoque más flexible y eficiente que pueda adaptarse a la complejidad inherente de los lenguajes naturales.
-Las contribuciones del artículo son múltiples: presenta una nueva arquitectura, el Transformer, que logra resultados de primer nivel en traducción automática y mejora la capacidad de atención a partes relevantes de una secuencia de entrada a lo largo de toda su longitud. La validación del trabajo se lleva a cabo a través de una serie de experimentos rigurosos que utilizan métricas estándar como BLEU, aplicadas en conjuntos de datos bien establecidos, específicamente en las tareas de traducción automática del WMT 2014 para las combinaciones de inglés-alemán y inglés-francés. Estas evaluaciones permiten comparar el rendimiento del modelo Transformer con el de los modelos existentes en la literatura, ofreciendo evidencia de su eficacia y calidad superior en la traducción. Además, se analiza cómo las contribuciones del modelo no solo mejoran la calidad de la traducción, sino que también optimizan la eficiencia durante el entrenamiento, validando así la relevancia y el impacto del enfoque propuesto.
-El resto del artículo se organiza en varias secciones que incluyen una descripción detallada de la arquitectura del Transformer, comparaciones con modelos existentes, así como la presentación de experimentos y resultados obtenidos. También se incluye una conclusión que sintetiza las aportaciones y hallazgos del estudio. Estas secciones están diseñadas para guiar al lector a través del razonamiento que respalda el diseño del modelo y su eficacia en el contexto de la traducción automática.</t>
+          <t>﻿El contexto de esta investigación se enmarca dentro del campo de la traducción automática, una disciplina de creciente relevancia en la era digital, donde la globalización y la necesidad de comunicación interlingüística son cada vez más frecuentes. La traducción automática permite a las personas y empresas superar las barreras lingüísticas, facilitando el acceso a información y servicios a nivel internacional. En este sentido, se ha intensificado el interés por desarrollar sistemas más eficientes y precisos que puedan manejar la complejidad y diversidad de los idiomas.
+La literatura existente en traducción automática ha estado dominada tradicionalmente por enfoques basados en estadísticas y modelos de redes neuronales recurrentes (RNN). Sin embargo, estos modelos presentan limitaciones significativas, especialmente en el tratamiento de oraciones largas, donde sufren de problemas de memoria y requieren un largo tiempo de entrenamiento. Diversos estudios, como los de Bahdanau et al. y Sutskever et al., han abordado estas limitaciones, pero han dejado un espacio para el desarrollo de nuevas arquitecturas que puedan ofrecer mejoras sustanciales. La arquitectura Transformer, presentada en el artículo, surge como una alternativa innovadora que promete abordar estos desafíos, al introducir mecanismos de atención que permiten procesos de traducción más paralelizados y efectivos.
+A pesar de los avances en la traducción automática y el aporte significativo de estudios anteriores, como los de Bahdanau et al. (2014) y Sutskever et al. (2014), persisten limitaciones notables en los enfoques existentes. Estos trabajos, aunque pioneros en la implementación de modelos de redes neuronales para la traducción, aún se encuentran constreñidos por la necesidad de comprimir toda la información de una oración en un vector de longitud fija. Esta compresión a menudo se traduce en un cuello de botella que dificulta el aprendizaje efectivo de dependencias a largo plazo, crucial para el manejo de oraciones más extensas y complejas.
+Además, aunque Bahdanau et al. introducen un mecanismo de alineación para mejorar la relevancia de las partes de la entrada durante la generación de la salida, los resultados logrados no superan completamente los modelos de traducción estadística más establecidos. Este vacío en el rendimiento indica una necesidad urgente de un nuevo enfoque que no solo supere estas limitaciones, sino que también ofrezca una solución robusta y escalable que mejore la efectividad y la eficiencia en la traducción automática de idiomas complejos.
+La propuesta central de este trabajo es la arquitectura Transformer, la cual aborda directamente las limitaciones identificadas en estudios previos sobre traducción automática. Al eliminar la necesidad de comprimir toda la información de una oración en un vector de longitud fija, el Transformer utiliza mecanismos de atención que permiten al modelo procesar partes relevantes de la entrada de forma más eficiente y dinámica durante la generación de la salida. Este enfoque no solo mejora la capacidad de aprender dependencias a largo plazo, sino que también optimiza el manejo de oraciones largas y complejas, un desafío recurrente en modelos de traducción basados en RNN.
+La arquitectura Transformer se fundamenta en la auto-atención, lo que permite que el modelo preste atención a diferentes posiciones en la secuencia de entrada sin las restricciones impuestas por enfoques anteriores. Al integrar esta técnica, el modelo puede mantener información de manera más efectiva y contextualizar la relevancia de las palabras dentro de un rango dinámico, mejorando así la precisión y la fluidez de las traducciones generadas. Este enfoque se considera un avance significativo en comparación con las metodologías previas, ofreciendo una solución robusta a las deficiencias detectadas en trabajos anteriores.
+Las aportaciones del trabajo incluyen: la introducción de la arquitectura Transformer, que mejora significativamente la eficiencia en tareas de traducción automática; el desarrollo de un nuevo modelo que establece un estado del arte en puntuaciones BLEU en traducción automática; y la implementación de un mecanismo de atención que permite que el modelo asigne relevancia a diferentes partes de la entrada a medida que genera la salida.
+La validación del trabajo se lleva a cabo a través de una serie de experimentos diseñados específicamente para evaluar la eficacia del modelo en tareas de traducción automática. Estos experimentos incluyen comparaciones directas con modelos de referencia establecidos, permitiendo un análisis exhaustivo del rendimiento del Transformer en diferentes escenarios, incluyendo oraciones de diversas longitudes. A través de estos análisis, se respalda la relevancia de las contribuciones presentadas, mostrando que el enfoque propuesto no solo mejora la eficiencia, sino que también establece nuevas referencias en términos de precisión en la traducción. Además, la robustez del modelo se evidencia mediante su capacidad para manejar la complejidad del lenguaje, lo que refuerza la validez de los hallazgos y contribuciones plasmadas en el documento.
+El resto del documento se organiza en varias secciones que incluyen una revisión de los métodos previos en el campo, una descripción técnica detallada de la arquitectura del Transformer, así como los resultados experimentales que evidencian la efectividad del modelo. Posteriormente, se presenta una discusión sobre las implicaciones de estos hallazgos para la traducción automática y el aprendizaje de secuencias, finalizando con una conclusión que destaca la promesa de futuras investigaciones en modelos basados en atención.</t>
         </is>
       </c>
     </row>

--- a/introducciones/comparacion_introducciones.xlsx
+++ b/introducciones/comparacion_introducciones.xlsx
@@ -491,15 +491,11 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>﻿El contexto de esta investigación se enmarca dentro del campo de la traducción automática, una disciplina de creciente relevancia en la era digital, donde la globalización y la necesidad de comunicación interlingüística son cada vez más frecuentes. La traducción automática permite a las personas y empresas superar las barreras lingüísticas, facilitando el acceso a información y servicios a nivel internacional. En este sentido, se ha intensificado el interés por desarrollar sistemas más eficientes y precisos que puedan manejar la complejidad y diversidad de los idiomas.
-La literatura existente en traducción automática ha estado dominada tradicionalmente por enfoques basados en estadísticas y modelos de redes neuronales recurrentes (RNN). Sin embargo, estos modelos presentan limitaciones significativas, especialmente en el tratamiento de oraciones largas, donde sufren de problemas de memoria y requieren un largo tiempo de entrenamiento. Diversos estudios, como los de Bahdanau et al. y Sutskever et al., han abordado estas limitaciones, pero han dejado un espacio para el desarrollo de nuevas arquitecturas que puedan ofrecer mejoras sustanciales. La arquitectura Transformer, presentada en el artículo, surge como una alternativa innovadora que promete abordar estos desafíos, al introducir mecanismos de atención que permiten procesos de traducción más paralelizados y efectivos.
-A pesar de los avances en la traducción automática y el aporte significativo de estudios anteriores, como los de Bahdanau et al. (2014) y Sutskever et al. (2014), persisten limitaciones notables en los enfoques existentes. Estos trabajos, aunque pioneros en la implementación de modelos de redes neuronales para la traducción, aún se encuentran constreñidos por la necesidad de comprimir toda la información de una oración en un vector de longitud fija. Esta compresión a menudo se traduce en un cuello de botella que dificulta el aprendizaje efectivo de dependencias a largo plazo, crucial para el manejo de oraciones más extensas y complejas.
-Además, aunque Bahdanau et al. introducen un mecanismo de alineación para mejorar la relevancia de las partes de la entrada durante la generación de la salida, los resultados logrados no superan completamente los modelos de traducción estadística más establecidos. Este vacío en el rendimiento indica una necesidad urgente de un nuevo enfoque que no solo supere estas limitaciones, sino que también ofrezca una solución robusta y escalable que mejore la efectividad y la eficiencia en la traducción automática de idiomas complejos.
-La propuesta central de este trabajo es la arquitectura Transformer, la cual aborda directamente las limitaciones identificadas en estudios previos sobre traducción automática. Al eliminar la necesidad de comprimir toda la información de una oración en un vector de longitud fija, el Transformer utiliza mecanismos de atención que permiten al modelo procesar partes relevantes de la entrada de forma más eficiente y dinámica durante la generación de la salida. Este enfoque no solo mejora la capacidad de aprender dependencias a largo plazo, sino que también optimiza el manejo de oraciones largas y complejas, un desafío recurrente en modelos de traducción basados en RNN.
-La arquitectura Transformer se fundamenta en la auto-atención, lo que permite que el modelo preste atención a diferentes posiciones en la secuencia de entrada sin las restricciones impuestas por enfoques anteriores. Al integrar esta técnica, el modelo puede mantener información de manera más efectiva y contextualizar la relevancia de las palabras dentro de un rango dinámico, mejorando así la precisión y la fluidez de las traducciones generadas. Este enfoque se considera un avance significativo en comparación con las metodologías previas, ofreciendo una solución robusta a las deficiencias detectadas en trabajos anteriores.
-Las aportaciones del trabajo incluyen: la introducción de la arquitectura Transformer, que mejora significativamente la eficiencia en tareas de traducción automática; el desarrollo de un nuevo modelo que establece un estado del arte en puntuaciones BLEU en traducción automática; y la implementación de un mecanismo de atención que permite que el modelo asigne relevancia a diferentes partes de la entrada a medida que genera la salida.
-La validación del trabajo se lleva a cabo a través de una serie de experimentos diseñados específicamente para evaluar la eficacia del modelo en tareas de traducción automática. Estos experimentos incluyen comparaciones directas con modelos de referencia establecidos, permitiendo un análisis exhaustivo del rendimiento del Transformer en diferentes escenarios, incluyendo oraciones de diversas longitudes. A través de estos análisis, se respalda la relevancia de las contribuciones presentadas, mostrando que el enfoque propuesto no solo mejora la eficiencia, sino que también establece nuevas referencias en términos de precisión en la traducción. Además, la robustez del modelo se evidencia mediante su capacidad para manejar la complejidad del lenguaje, lo que refuerza la validez de los hallazgos y contribuciones plasmadas en el documento.
-El resto del documento se organiza en varias secciones que incluyen una revisión de los métodos previos en el campo, una descripción técnica detallada de la arquitectura del Transformer, así como los resultados experimentales que evidencian la efectividad del modelo. Posteriormente, se presenta una discusión sobre las implicaciones de estos hallazgos para la traducción automática y el aprendizaje de secuencias, finalizando con una conclusión que destaca la promesa de futuras investigaciones en modelos basados en atención.</t>
+          <t>﻿El ámbito de la traducción automática ha experimentado una evolución significativa en las últimas décadas, transformándose de enfoques basados en reglas a sistemas más sofisticados, como la traducción neuronal, que ha redefinido el campo. Este avance ha permitido que las máquinas no solo interpreten el significado de palabras individuales, sino que también comprendan y reproduzcan estructuras complejas y matices del lenguaje, ofreciendo traducciones más precisas y contextualmente relevantes. En particular, la traducción neuronal ha demostrado ser eficaz en el manejo de diferentes pares de idiomas, así como en la captura de relaciones de larga distancia entre palabras, lo cual es fundamental para asegurar la coherencia y fluidez del texto traducido.
+A pesar de los avances logrados en el campo del procesamiento de secuencias mediante redes neuronales recurrentes (RNN), persisten limitaciones significativas en la gestión eficiente de relaciones a largo plazo. Aunque Bahdanau et al. (2015) proponen un enfoque innovador basado en alinear y traducir, sus resultados aún evidencian dificultades al manejar secuencias extensas, lo que sugiere que la solución presentada no resuelve completamente el problema de las interdependencias a largo plazo en los datos secuenciales. Esta carencia en los modelos existentes deja un vacío que justifica la necesidad de investigar nuevas estrategias o arquitecturas que puedan abordar estas limitaciones de manera más efectiva. Por lo tanto, se requiere una exploración más profunda en la optimización del manejo de relaciones a largo plazo en secuencias, dado que los enfoques actuales no son suficientes para superar estos desafíos, lo que abre la puerta a estudios que busquen innovar en esta dirección.
+En respuesta a las limitaciones evidenciadas en los modelos basados en redes neuronales recurrentes (RNN), este trabajo propone la implementación y evaluación de un modelo Transformer. Este enfoque se fundamenta en la arquitectura innovadora del Transformer, que utiliza un mecanismo de atención para capturar de manera efectiva las dependencias globales en las secuencias de datos. A diferencia de las RNN, que procesan la información de manera secuencial y, por ende, suelen enfrentarse a dificultades en la memorización de información distante, el modelo Transformer permite que cada entrada interactúe con todas las demás de forma simultánea gracias a su estructura de autoatención. Esto no solo optimiza el tiempo de cálculo, sino que también potencializa la comprensión contextual de relaciones complejas en datos extensos. Al centrarse en este modelo, la investigación busca no solo resolver las deficiencias detectadas en la gestión de relaciones a largo plazo, sino también mejorar la eficiencia en el entrenamiento y la inferencia.
+Las contribuciones del trabajo son notables y se detallan de la siguiente manera: se introduce el Transformer, que utiliza exclusivamente atención, superando así a técnicas anteriores como RNN y CNN; se alcanzan puntuaciones BLEU significativamente mejores en conjuntos de datos WMT 2014 para traducción inglés-alemán y francés, estableciendo nuevos récords; y se verifica la generalización efectiva del modelo en otras tareas de procesamiento del lenguaje natural. La validación del trabajo se fundamenta en comparaciones de puntuaciones BLEU obtenidas en los benchmarks de traducción de WMT 2014, donde el modelo exhibe mejoras significativas en relación con las mejores prácticas previamente establecidas. Esta validación resalta la efectividad de las contribuciones propuestas y su impacto en el ámbito de la traducción automática.
+El resto del artículo se organiza en las siguientes secciones.</t>
         </is>
       </c>
     </row>

--- a/introducciones/comparacion_introducciones.xlsx
+++ b/introducciones/comparacion_introducciones.xlsx
@@ -491,11 +491,15 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>﻿El ámbito de la traducción automática ha experimentado una evolución significativa en las últimas décadas, transformándose de enfoques basados en reglas a sistemas más sofisticados, como la traducción neuronal, que ha redefinido el campo. Este avance ha permitido que las máquinas no solo interpreten el significado de palabras individuales, sino que también comprendan y reproduzcan estructuras complejas y matices del lenguaje, ofreciendo traducciones más precisas y contextualmente relevantes. En particular, la traducción neuronal ha demostrado ser eficaz en el manejo de diferentes pares de idiomas, así como en la captura de relaciones de larga distancia entre palabras, lo cual es fundamental para asegurar la coherencia y fluidez del texto traducido.
-A pesar de los avances logrados en el campo del procesamiento de secuencias mediante redes neuronales recurrentes (RNN), persisten limitaciones significativas en la gestión eficiente de relaciones a largo plazo. Aunque Bahdanau et al. (2015) proponen un enfoque innovador basado en alinear y traducir, sus resultados aún evidencian dificultades al manejar secuencias extensas, lo que sugiere que la solución presentada no resuelve completamente el problema de las interdependencias a largo plazo en los datos secuenciales. Esta carencia en los modelos existentes deja un vacío que justifica la necesidad de investigar nuevas estrategias o arquitecturas que puedan abordar estas limitaciones de manera más efectiva. Por lo tanto, se requiere una exploración más profunda en la optimización del manejo de relaciones a largo plazo en secuencias, dado que los enfoques actuales no son suficientes para superar estos desafíos, lo que abre la puerta a estudios que busquen innovar en esta dirección.
-En respuesta a las limitaciones evidenciadas en los modelos basados en redes neuronales recurrentes (RNN), este trabajo propone la implementación y evaluación de un modelo Transformer. Este enfoque se fundamenta en la arquitectura innovadora del Transformer, que utiliza un mecanismo de atención para capturar de manera efectiva las dependencias globales en las secuencias de datos. A diferencia de las RNN, que procesan la información de manera secuencial y, por ende, suelen enfrentarse a dificultades en la memorización de información distante, el modelo Transformer permite que cada entrada interactúe con todas las demás de forma simultánea gracias a su estructura de autoatención. Esto no solo optimiza el tiempo de cálculo, sino que también potencializa la comprensión contextual de relaciones complejas en datos extensos. Al centrarse en este modelo, la investigación busca no solo resolver las deficiencias detectadas en la gestión de relaciones a largo plazo, sino también mejorar la eficiencia en el entrenamiento y la inferencia.
-Las contribuciones del trabajo son notables y se detallan de la siguiente manera: se introduce el Transformer, que utiliza exclusivamente atención, superando así a técnicas anteriores como RNN y CNN; se alcanzan puntuaciones BLEU significativamente mejores en conjuntos de datos WMT 2014 para traducción inglés-alemán y francés, estableciendo nuevos récords; y se verifica la generalización efectiva del modelo en otras tareas de procesamiento del lenguaje natural. La validación del trabajo se fundamenta en comparaciones de puntuaciones BLEU obtenidas en los benchmarks de traducción de WMT 2014, donde el modelo exhibe mejoras significativas en relación con las mejores prácticas previamente establecidas. Esta validación resalta la efectividad de las contribuciones propuestas y su impacto en el ámbito de la traducción automática.
-El resto del artículo se organiza en las siguientes secciones.</t>
+          <t>﻿El artículo se sitúa en el ámbito del procesamiento del lenguaje natural (PLN), un campo de estudio que ha cobrado una importancia creciente con el avance de las tecnologías de interacción humano-computadora. La capacidad de las máquinas para entender, interpretar y generar lenguaje humano es fundamental para una variedad de aplicaciones, desde sistemas de traducción automática hasta asistentes personales y análisis de sentimientos. Dentro de este amplio territorio, la traducción automática se ha destacado como una de las disciplinas más desafiantes y relevantes, dado su impacto en la comunicación global y el acceso a la información.
+A pesar de los avances significativos en el procesamiento del lenguaje natural y la traducción automática que se han logrado mediante el uso de sistemas neuronales, muchos de los modelos anteriores, como los sistemas de traducción automática que utilizan redes neuronales recurrentes, padecen limitaciones al aprender dependencias a largo alcance. Por ejemplo, Bahdanau et al. (2014) introdujeron un enfoque que, aunque innovador, no resolvió completamente el problema del alineamiento entre la entrada y la salida. De manera similar, Sutskever et al. (2014) también reconocieron las dificultades asociadas con la traducción de oraciones largas, lo que sugiere que aún hay un espacio considerable para la mejora en el rendimiento de las traducciones automáticas.
+A pesar de estas contribuciones, los problemas de eficacia en la generación de traducciones precisas y contextualmente relevantes persisten en los modelos existentes, lo que lleva a la necesidad de nuevas soluciones que integren las ventajas de los mecanismos de atención. Este artículo propone el modelo Transformer como una respuesta a estas limitaciones, ofreciendo una arquitectura que no solo mejora el aprendizaje de dependencias a largo plazo, sino que también promete eficiencia en el proceso de entrenamiento.
+El modelo Transformer se propone como una solución innovadora para abordar las limitaciones de los modelos tradicionales en el aprendizaje de dependencias a largo alcance. Al eliminar la necesidad de recurrencia y convolución, el Transformer se basa exclusivamente en mecanismos de atención, lo que permite que la arquitectura se enfoque de manera más efectiva en la información relevante de la entrada mientras genera la salida correspondiente. Este enfoque no solo mejora la capacidad del modelo para manejar oraciones más largas, sino que también proporciona una mayor paralelización durante el entrenamiento, resultando en una eficiencia notable. En consecuencia, el Transformer no solo propone un avance en el rendimiento en tareas de traducción, sino que también abre nuevas posibilidades para su aplicación en diversas tareas dentro del PLN.
+- Presentación del modelo Transformer como una nueva arquitectura que reemplaza las redes neuronales recurrentes y convolucionales por mecanismos de atención.
+- Mejora en el rendimiento en tareas de traducción automática, estableciendo nuevos récords en las puntuaciones BLEU para traducción de inglés a alemán y francés.
+- Generalización del modelo a otras tareas de procesamiento del lenguaje natural (PLN).
+La evaluación del modelo Transformer se lleva a cabo mediante comparaciones sistemáticas con arquitecturas previas, como ByteNet y GNMT, que han sido reconocidas por su rendimiento en tareas de traducción automática. A través de estos experimentos, se demuestra que el Transformer no solo supera la calidad de las traducciones generadas por estos modelos, sino que también optimiza la eficiencia en el proceso de entrenamiento. Esta validación se respalda por un conjunto riguroso de casos de estudio que destacan las ventajas del enfoque basado en atención propuesto, lo que confirma la relevancia y aplicabilidad de las contribuciones presentadas en este artículo.
+El resto del artículo se organiza en secciones que abordan el contexto del modelo presentado, la arquitectura del Transformer, las motivaciones detrás de su desarrollo, los resultados obtenidos en comparación con enfoques anteriores y finalmente, las conclusiones que esbozan las direcciones futuras de la investigación.</t>
         </is>
       </c>
     </row>

--- a/introducciones/comparacion_introducciones.xlsx
+++ b/introducciones/comparacion_introducciones.xlsx
@@ -491,15 +491,18 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>﻿El artículo se sitúa en el ámbito del procesamiento del lenguaje natural (PLN), un campo de estudio que ha cobrado una importancia creciente con el avance de las tecnologías de interacción humano-computadora. La capacidad de las máquinas para entender, interpretar y generar lenguaje humano es fundamental para una variedad de aplicaciones, desde sistemas de traducción automática hasta asistentes personales y análisis de sentimientos. Dentro de este amplio territorio, la traducción automática se ha destacado como una de las disciplinas más desafiantes y relevantes, dado su impacto en la comunicación global y el acceso a la información.
-A pesar de los avances significativos en el procesamiento del lenguaje natural y la traducción automática que se han logrado mediante el uso de sistemas neuronales, muchos de los modelos anteriores, como los sistemas de traducción automática que utilizan redes neuronales recurrentes, padecen limitaciones al aprender dependencias a largo alcance. Por ejemplo, Bahdanau et al. (2014) introdujeron un enfoque que, aunque innovador, no resolvió completamente el problema del alineamiento entre la entrada y la salida. De manera similar, Sutskever et al. (2014) también reconocieron las dificultades asociadas con la traducción de oraciones largas, lo que sugiere que aún hay un espacio considerable para la mejora en el rendimiento de las traducciones automáticas.
-A pesar de estas contribuciones, los problemas de eficacia en la generación de traducciones precisas y contextualmente relevantes persisten en los modelos existentes, lo que lleva a la necesidad de nuevas soluciones que integren las ventajas de los mecanismos de atención. Este artículo propone el modelo Transformer como una respuesta a estas limitaciones, ofreciendo una arquitectura que no solo mejora el aprendizaje de dependencias a largo plazo, sino que también promete eficiencia en el proceso de entrenamiento.
-El modelo Transformer se propone como una solución innovadora para abordar las limitaciones de los modelos tradicionales en el aprendizaje de dependencias a largo alcance. Al eliminar la necesidad de recurrencia y convolución, el Transformer se basa exclusivamente en mecanismos de atención, lo que permite que la arquitectura se enfoque de manera más efectiva en la información relevante de la entrada mientras genera la salida correspondiente. Este enfoque no solo mejora la capacidad del modelo para manejar oraciones más largas, sino que también proporciona una mayor paralelización durante el entrenamiento, resultando en una eficiencia notable. En consecuencia, el Transformer no solo propone un avance en el rendimiento en tareas de traducción, sino que también abre nuevas posibilidades para su aplicación en diversas tareas dentro del PLN.
-- Presentación del modelo Transformer como una nueva arquitectura que reemplaza las redes neuronales recurrentes y convolucionales por mecanismos de atención.
-- Mejora en el rendimiento en tareas de traducción automática, estableciendo nuevos récords en las puntuaciones BLEU para traducción de inglés a alemán y francés.
-- Generalización del modelo a otras tareas de procesamiento del lenguaje natural (PLN).
-La evaluación del modelo Transformer se lleva a cabo mediante comparaciones sistemáticas con arquitecturas previas, como ByteNet y GNMT, que han sido reconocidas por su rendimiento en tareas de traducción automática. A través de estos experimentos, se demuestra que el Transformer no solo supera la calidad de las traducciones generadas por estos modelos, sino que también optimiza la eficiencia en el proceso de entrenamiento. Esta validación se respalda por un conjunto riguroso de casos de estudio que destacan las ventajas del enfoque basado en atención propuesto, lo que confirma la relevancia y aplicabilidad de las contribuciones presentadas en este artículo.
-El resto del artículo se organiza en secciones que abordan el contexto del modelo presentado, la arquitectura del Transformer, las motivaciones detrás de su desarrollo, los resultados obtenidos en comparación con enfoques anteriores y finalmente, las conclusiones que esbozan las direcciones futuras de la investigación.</t>
+          <t>﻿La traducción automática se sitúa en el cruce de la inteligencia artificial y el procesamiento del lenguaje natural, y tiene como objetivo fundamental la conversión de texto entre diferentes idiomas. Este campo es de vital importancia, ya que las traducciones automáticas posibilitan la comunicación intercultural y el acceso a la información a escala global, abordando barreras lingüísticas que, de otro modo, limitarían la colaboración y el intercambio de conocimientos. En aplicaciones prácticas, tales como en empresas multinacionales, plataformas de contenido digital y servicios de atención al cliente, la traducción automática se vuelve imprescindible.
+A lo largo de los años, numerosas técnicas han sido desarrolladas para abordar este desafío. Desde los primeros sistemas basados en reglas hasta los enfoques estadísticos que dieron paso a la era de la traducción automática neural, el progreso ha sido notable. Sin embargo, los modelos más recientes, incluyendo redes neuronales profundas y mecanismos de atención, han demostrado ser particularmente eficaces al permitir una mejor comprensión del contexto y la semántica de las oraciones complejas. A pesar de estos avances, todavía existen limitaciones significativas en la capacidad de estos modelos para manejar la variabilidad y la riqueza de las lenguas naturales en todas sus formas.
+A pesar de los avances en la traducción automática mediante arquitecturas como redes neuronales profundas y modelos de atención, persisten desafíos significativos relacionados con el aprendizaje de dependencias a largo plazo y la adaptabilidad a oraciones de longitud variable. Por ejemplo, Bahdanau et al. (2014) y Sutskever et al. (2014) han abordado estos problemas utilizando métodos de atención; sin embargo, aún se enfrentan a limitaciones inherentes a la codificación de oraciones en un solo vector de longitud fija. Esta limitación puede resultar en la incapacidad de captar adecuadamente el contexto necesario para traducir oraciones complejas y largas, lo que indica la necesidad de enfoques que eviten la saturación de información en un único vector.
+Además, se observa que los modelos existentes suelen requerir un alto costo computacional y no siempre logran generalizar de manera óptima en diversos contextos lingüísticos, lo que resalta la falta de progreso en términos de eficiencia y efectividad en comparación con los sistemas de traducción basados en frases que, aunque más limitados en términos de flexibilidad, mantienen un rendimiento competitivo. Estos aspectos crean un contexto propicio para la investigación de nuevas metodologías que superen las barreras actuales y mejoren la calidad y velocidad de la traducción automática.
+En respuesta a las limitaciones identificadas en trabajos previos sobre traducción automática, la propuesta central de este artículo es la introducción del modelo Transformador, el cual se basa exclusivamente en mecanismos de atención. Este enfoque permite manejar de manera más efectiva las dependencias de largo alcance, superando la limitación crítica de la codificación de oraciones completas en un vector de longitud fija. Al hacerlo, el Transformador evita los problemas que surgen de la saturación de información en un único vector, permitiendo capturar mejor el contexto necesario para traducciones precisas de oraciones complejas y largas.
+Además, la arquitectura del Transformador facilita una mayor paralelización durante el entrenamiento, lo que no solo mejora la eficiencia de la formación del modelo, sino que también reduce significativamente el tiempo requerido para su entrenamiento. Este enfoque, en contraste con los modelos existentes que a menudo enfrentan dificultades en la generalización a diferentes contextos lingüísticos y son computacionalmente intensivos, promete no solo mejorar la calidad de las traducciones, sino también ofrecer una solución más escalable para aplicaciones prácticas en el campo de la traducción automática.
+Las principales contribuciones del trabajo son las siguientes:
+- Introducción del modelo Transformador, que se basa exclusivamente en mecanismos de atención y se describe en la sección 3 del documento.
+- Superación de los resultados anteriores en tareas de traducción del conjunto de datos WMT 2014 con puntuaciones BLEU mejoradas, lo que se detalla en la sección 6.
+- Validación de la robustez del modelo frente a la longitud de las oraciones, garantizando así su eficacia en una variedad de contextos y escenarios de traducción.
+La validación del trabajo se lleva a cabo a través de una serie de experimentos en tareas de traducción automática, donde se utilizan conjuntos de datos estándar para evaluar el desempeño del modelo Transformador. Los experimentos permiten medir la calidad de las traducciones generadas mediante la puntuación BLEU, proporcionando una métrica objetiva que respalda las contribuciones del estudio. Se implementan análisis detallados que contrastan el modelo propuesto con arquitecturas anteriores, así como la observación de su robustez en la traducción de oraciones de diversas longitudes, lo que añade una capa adicional de evidencia sobre la efectividad del enfoque. Estas metodologías experimentales aseguran que las mejoras en el rendimiento no solo sean significativas, sino también consistentes a través de diferentes contextos de uso en el campo de la traducción automática.
+El resto del documento se organiza en secciones que abordan de manera sistemática la introducción del contexto y el problema, los antecedentes sobre el estado del arte, la descripción detallada del modelo y sus componentes, seguido de la presentación de resultados experimentales, discusiones sobre los hallazgos y las conclusiones del estudio. Esta estructura permite una comprensión clara del desarrollo del trabajo, desde la motivación inicial hasta los resultados y su relevancia en el campo de la traducción automática.</t>
         </is>
       </c>
     </row>

--- a/introducciones/comparacion_introducciones.xlsx
+++ b/introducciones/comparacion_introducciones.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -491,18 +491,46 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>﻿La traducción automática se sitúa en el cruce de la inteligencia artificial y el procesamiento del lenguaje natural, y tiene como objetivo fundamental la conversión de texto entre diferentes idiomas. Este campo es de vital importancia, ya que las traducciones automáticas posibilitan la comunicación intercultural y el acceso a la información a escala global, abordando barreras lingüísticas que, de otro modo, limitarían la colaboración y el intercambio de conocimientos. En aplicaciones prácticas, tales como en empresas multinacionales, plataformas de contenido digital y servicios de atención al cliente, la traducción automática se vuelve imprescindible.
-A lo largo de los años, numerosas técnicas han sido desarrolladas para abordar este desafío. Desde los primeros sistemas basados en reglas hasta los enfoques estadísticos que dieron paso a la era de la traducción automática neural, el progreso ha sido notable. Sin embargo, los modelos más recientes, incluyendo redes neuronales profundas y mecanismos de atención, han demostrado ser particularmente eficaces al permitir una mejor comprensión del contexto y la semántica de las oraciones complejas. A pesar de estos avances, todavía existen limitaciones significativas en la capacidad de estos modelos para manejar la variabilidad y la riqueza de las lenguas naturales en todas sus formas.
-A pesar de los avances en la traducción automática mediante arquitecturas como redes neuronales profundas y modelos de atención, persisten desafíos significativos relacionados con el aprendizaje de dependencias a largo plazo y la adaptabilidad a oraciones de longitud variable. Por ejemplo, Bahdanau et al. (2014) y Sutskever et al. (2014) han abordado estos problemas utilizando métodos de atención; sin embargo, aún se enfrentan a limitaciones inherentes a la codificación de oraciones en un solo vector de longitud fija. Esta limitación puede resultar en la incapacidad de captar adecuadamente el contexto necesario para traducir oraciones complejas y largas, lo que indica la necesidad de enfoques que eviten la saturación de información en un único vector.
-Además, se observa que los modelos existentes suelen requerir un alto costo computacional y no siempre logran generalizar de manera óptima en diversos contextos lingüísticos, lo que resalta la falta de progreso en términos de eficiencia y efectividad en comparación con los sistemas de traducción basados en frases que, aunque más limitados en términos de flexibilidad, mantienen un rendimiento competitivo. Estos aspectos crean un contexto propicio para la investigación de nuevas metodologías que superen las barreras actuales y mejoren la calidad y velocidad de la traducción automática.
-En respuesta a las limitaciones identificadas en trabajos previos sobre traducción automática, la propuesta central de este artículo es la introducción del modelo Transformador, el cual se basa exclusivamente en mecanismos de atención. Este enfoque permite manejar de manera más efectiva las dependencias de largo alcance, superando la limitación crítica de la codificación de oraciones completas en un vector de longitud fija. Al hacerlo, el Transformador evita los problemas que surgen de la saturación de información en un único vector, permitiendo capturar mejor el contexto necesario para traducciones precisas de oraciones complejas y largas.
-Además, la arquitectura del Transformador facilita una mayor paralelización durante el entrenamiento, lo que no solo mejora la eficiencia de la formación del modelo, sino que también reduce significativamente el tiempo requerido para su entrenamiento. Este enfoque, en contraste con los modelos existentes que a menudo enfrentan dificultades en la generalización a diferentes contextos lingüísticos y son computacionalmente intensivos, promete no solo mejorar la calidad de las traducciones, sino también ofrecer una solución más escalable para aplicaciones prácticas en el campo de la traducción automática.
-Las principales contribuciones del trabajo son las siguientes:
-- Introducción del modelo Transformador, que se basa exclusivamente en mecanismos de atención y se describe en la sección 3 del documento.
-- Superación de los resultados anteriores en tareas de traducción del conjunto de datos WMT 2014 con puntuaciones BLEU mejoradas, lo que se detalla en la sección 6.
-- Validación de la robustez del modelo frente a la longitud de las oraciones, garantizando así su eficacia en una variedad de contextos y escenarios de traducción.
-La validación del trabajo se lleva a cabo a través de una serie de experimentos en tareas de traducción automática, donde se utilizan conjuntos de datos estándar para evaluar el desempeño del modelo Transformador. Los experimentos permiten medir la calidad de las traducciones generadas mediante la puntuación BLEU, proporcionando una métrica objetiva que respalda las contribuciones del estudio. Se implementan análisis detallados que contrastan el modelo propuesto con arquitecturas anteriores, así como la observación de su robustez en la traducción de oraciones de diversas longitudes, lo que añade una capa adicional de evidencia sobre la efectividad del enfoque. Estas metodologías experimentales aseguran que las mejoras en el rendimiento no solo sean significativas, sino también consistentes a través de diferentes contextos de uso en el campo de la traducción automática.
-El resto del documento se organiza en secciones que abordan de manera sistemática la introducción del contexto y el problema, los antecedentes sobre el estado del arte, la descripción detallada del modelo y sus componentes, seguido de la presentación de resultados experimentales, discusiones sobre los hallazgos y las conclusiones del estudio. Esta estructura permite una comprensión clara del desarrollo del trabajo, desde la motivación inicial hasta los resultados y su relevancia en el campo de la traducción automática.</t>
+          <t>﻿En el campo de los modelos de transducción de secuencias, las arquitecturas dominantes tradicionalmente han utilizado redes neuronales recurrentes (RNN) o convolucionales (CNN) que incluyen mecanismos de atención para conectar el codificador y el decodificador. Estos modelos han logrado avances significativos en tareas como la traducción automática, donde la eficiencia computacional y la calidad de la traducción son aspectos fundamentales. La atención se ha consolidado como un componente clave para mejorar el rendimiento al permitir que el modelo se enfoque dinámicamente en diferentes partes de la secuencia de entrada durante la generación de la salida.
+Dentro de este panorama, la búsqueda por mejorar la eficiencia y la capacidad de paralelización de los modelos ha sido un tema central. Las arquitecturas basadas en recurrencias o convoluciones presentan limitaciones inherentes, como la necesidad de cómputos secuenciales o la dificultad para capturar dependencias a largo plazo de manera efectiva. En este contexto, surge la relevancia de explorar nuevas aproximaciones que permitan superar estos obstáculos, manteniendo o mejorando la calidad en las tareas de procesamiento de lenguaje natural, específicamente en traducción automática. El Transformer se posiciona como una innovadora alternativa que prescinde por completo de recurrencias y convoluciones, utilizando exclusivamente mecanismos de atención para tratar las secuencias.
+A pesar de los avances en modelos basados en atención para la traducción neuronal, persisten limitaciones importantes. Bahdanau et al. (2015) [VERIFICAR] presentan un modelo que mejora la capacidad de los modelos encoder-decoder tradicionales al evitar comprimir toda la oración de entrada en un vector fijo, lo que dificulta el manejo de oraciones largas. Sin embargo, esta arquitectura sigue usando redes recurrentes, lo que limita la eficiencia computacional y la posibilidad de paralelización efectiva.
+Por otro lado, Sutskever et al. (2014) desarrollan un modelo sequence-to-sequence basado en LSTM profundos que logra mejoras en la traducción, pero depende de representar la secuencia completa en vectores de dimensión fija y requiere invertir la secuencia de entrada para manejar mejor las dependencias largas. Esta estrategia, aunque efectiva, implica desafíos en la optimización y procesamiento.
+En conjunto, estas limitaciones señalan la necesidad de una arquitectura que supere las restricciones propias de las redes recurrentes y convolucionales, principalmente la secuencialidad en el procesamiento y la dificultad para paralelizar, y que facilite un entrenamiento más eficiente y un manejo adecuado de las dependencias a largo plazo sin requerir codificaciones fijas. Este es el vacío que justifica la exploración de enfoques alternativos como el Transformer.
+La propuesta central del trabajo es el Transformer, una arquitectura que responde directamente a la necesidad de superar las limitaciones de eficiencia y paralelización presentes en las arquitecturas basadas en redes recurrentes y convolucionales. Este modelo elimina completamente el uso de recurrencias y convoluciones, sustituyéndolos por un mecanismo de auto-atención multi-cabeza que permite establecer conexiones directas entre cualquier par de posiciones dentro de una secuencia.
+Este enfoque es especialmente adecuado para abordar los problemas asociados a la secuencialidad en el cómputo y la dificultad de paralelización, ya que reduce el coste computacional a una cantidad constante en función de la profundidad del modelo. De esta manera, se posibilita un entrenamiento más eficiente, con una mejor capacidad para capturar dependencias de largo alcance en las secuencias, sin la necesidad de codificaciones fijas que suelen limitar otros métodos. Así, el Transformer ofrece una solución innovadora que mejora el rendimiento en tareas de traducción automática, cumpliendo con las demandas identificadas en investigaciones previas.
+- Introducción de la arquitectura Transformer basada completamente en atención multi-cabeza, que permite manejar las secuencias sin recurrir a recurrencias ni convoluciones (sección 3).
+- Propuesta del mecanismo de atención escalar producto punto y multi-cabeza, diseñado para mejorar la representación y el procesamiento paralelo de las secuencias.
+- Uso de codificaciones posicionales sinusoidales para incorporar información sobre el orden de los elementos en la secuencia sin depender de estructuras recurrentes (sección 3.5).
+- Demostración experimental de la superioridad del modelo Transformer en tareas de traducción automática, específicamente en los conjuntos de datos WMT 2014 inglés-alemán e inglés-francés (sección 6.1).
+- Aplicación del modelo para análisis de constituyentes en inglés, evidenciando la capacidad de generalización del enfoque más allá de la traducción (sección 6.3).
+- Análisis y visualización de los mecanismos de atención, mostrando comportamientos interpretables que se relacionan con la estructura sintáctica y semántica del idioma (apéndice y sección 4).
+- Publicación del código asociado al Transformer para facilitar la reproducibilidad y permitir que la comunidad científica utilice y extienda el modelo.
+La validación del Transformer se realiza mediante experimentos en tareas estándar de traducción automática, específicamente en los conjuntos de datos WMT 2014 para traducción de inglés a alemán e inglés a francés, donde se compara su desempeño con modelos existentes y variantes del propio modelo para evaluar el impacto de diferentes hiperparámetros. Además, se extiende la evaluación a tareas de análisis sintáctico en inglés, demostrando la capacidad de generalización del modelo. Complementariamente, se llevan a cabo análisis e interpretaciones de los mecanismos de atención internos para comprender su funcionamiento y características explicativas, todo ello respaldando y justificando la solidez y eficacia de las contribuciones presentadas.
+El resto del documento se organiza comenzando con la introducción y motivación del trabajo, seguida por una descripción detallada de la arquitectura del Transformer, una justificación y análisis de las ventajas del mecanismo de auto-atención, y la presentación del régimen de entrenamiento. A continuación, se exponen los resultados experimentales que evalúan el desempeño del modelo en diferentes tareas, para finalmente concluir con una discusión y planteamiento de líneas futuras de trabajo. Además, el documento incluye referencias y apéndices que complementan la información técnica y experimental presentada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="200" customHeight="1">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>﻿La simulación de sistemas del Internet de las Cosas (IoT) constituye el área de trabajo principal, dada la alta inversión en desarrollo, despliegue y pruebas que requieren estos proyectos antes de su implementación física. La simulación permite modelar y razonar sobre los sistemas IoT, facilitando la optimización y reducción de costos asociados. En la literatura existen dos grandes enfoques: simuladores a nivel bajo que se centran en aspectos de hardware, redes y capacidades de los nodos; y simuladores a nivel alto que abordan el modelado de entornos, dispositivos y servicios mediante lenguajes específicos de dominio (DSL) o desarrollo guiado por modelos (MDD).
+A pesar de estos avances, muchas herramientas disponibles demandan elevadas competencias técnicas, carecen de interfaces gráficas amigables, no ofrecen generación automática de código o no cuentan con mecanismos para validar previamente el entorno simulado. Asimismo, varios simuladores no contemplan adecuadamente conceptos clave emergentes en el ámbito IoT, como las arquitecturas de fog computing y cloud computing, el procesamiento de eventos complejos y los protocolos de comunicación publish-subscribe, todos ellos fundamentales para la correcta representación y simulación de sistemas IoT modernos y heterogéneos.
+Aunque existen diversas propuestas para la simulación de sistemas IoT, varios trabajos muestran limitaciones que evidencian la necesidad de nuevos enfoques. Alwasel et al. (2020) [VERIFICAR] con BigDataSDNSim se centran en la simulación de datos masivos en entornos cloud SDN, pero no ofrecen un modelado integral de simulación IoT que abarque un alto nivel de abstracción a través de múltiples capas arquitectónicas. Clemente et al. (2018) [VERIFICAR] desarrollaron un lenguaje específico de dominio para domótica, pero su enfoque no contempla la simulación ni aspectos relacionados con almacenamiento o procesamiento basados en eventos. Por su parte, Mehdi et al. (2014) [VERIFICAR] con CupCarbon proporcionan un simulador gráfico para redes de sensores WSN, sin embargo, no modelan almacenamiento avanzado, procesamiento complejo ni la comunicación mediante protocolos publish-subscribe con brokers. Finalmente, Zeng et al. (2017) con IOTSim abordan la simulación de aplicaciones IoT en cloud con un enfoque en big data, pero su herramienta exige configuraciones técnicas complejas y carece de diseño gráfico y validación previa de los modelos.
+En conjunto, estos trabajos presentan carencias importantes como la ausencia de abstracción visual adecuada para la representación de simulaciones IoT que integren las capas Edge, Fog y Cloud; una dependencia significativa en configuraciones técnicas de bajo nivel; la falta de generación automática de código integral y despliegue mediante arquitecturas basadas en microservicios; y la inexistencia de mecanismos para validar modelos antes de la simulación, aspectos clave para la viabilidad y usabilidad de entornos de simulación IoT modernos y representativos.
+La propuesta central de este trabajo consiste en el desarrollo de SimulateIoT, un enfoque basado en desarrollo guiado por modelos que permite definir, generar código y desplegar entornos de simulación IoT complejos sin necesidad de programación manual. Este enfoque incluye un metamodelo de dominio que representa de forma integral los conceptos clave del IoT, una sintaxis gráfica para facilitar el modelado visual del sistema y una transformación modelo-texto que genera automáticamente el código asociado, que incluye microservicios, contenedores Docker, brokers MQTT, bases de datos NoSQL y motores para el procesamiento de eventos y flujos de datos. La comunicación entre los distintos nodos IoT, como sensores, actuadores y nodos fog y cloud, se gestiona mediante un protocolo de publicación-suscripción, lo que permite una simulación fiel a arquitecturas reales y heterogéneas. Además, se incorporan mecanismos para la validación del modelo y para la monitorización durante la simulación, lo que garantiza la calidad y el control del entorno simulado.
+Este enfoque se adapta a las carencias detectadas en trabajos previos, al ofrecer una abstracción visual adecuada y una completa integración de las capas Edge, Fog y Cloud, facilitando la generación automática de código y el despliegue en arquitecturas modernas basadas en microservicios. De esta forma, SimulateIoT responde a la necesidad de contar con herramientas que simplifiquen el diseño y la ejecución de simulaciones IoT complejas, manteniendo una alta fidelidad con respecto a las arquitecturas actuales y reduciendo drásticamente la necesidad de configuraciones técnicas complejas o conocimiento especializado para su uso.
+- Definición de un metamodelo que captura conceptos IoT a alto nivel, abarcando capas Edge, Fog, Cloud, sensores, actuadores, bases de datos, procesamiento de eventos y comunicación (Sección III.A).
+- Desarrollo de una sintaxis gráfica para modelar estos sistemas (Sección III.B).
+- Implementación de reglas OCL para la validación del modelo en base a restricciones estructurales y semánticas (Sección III.B).
+- Creación de transformaciones modelo-texto en Acceleo para generar código completo que materializa los modelos en microservicios desplegables (Sección III.C).
+- Implementación del sistema de despliegue y ejecución sobre Docker Swarm y monitorización integrada (Sección III.D).
+- Presentación de dos estudios de caso reales (edificio inteligente y agricultura) mostrando la capacidad descriptiva, generación y despliegue (Sección V).
+- Discusión sobre las limitaciones y futuras extensiones para movilidad y dinámicas de la simulación (Sección VI).
+La validación del trabajo se lleva a cabo mediante la aplicación de dos estudios de caso prácticos que ejemplifican y respaldan las contribuciones propuestas. El primer estudio simula un edificio inteligente compuesto por múltiples nodos fog distribuidos por diferentes edificios, integrando sensores de temperatura, presencia y humo, junto con reglas para el control automatizado de sistemas como la calefacción, monitorizados mediante bases de datos y motores de procesamiento de eventos complejos. El segundo estudio de caso se centra en un entorno agrícola, donde se simulan sensores para medir variables como temperatura, humedad, pH y presión de agua, junto con actuadores de riego, utilizando arquitecturas basadas en nodos fog y cloud, almacenamiento en bases de datos MongoDB y reglas para notificaciones y control. Ambos casos de estudio permiten la generación automática de código, su despliegue en contenedores Docker y la ejecución completa de la simulación, demostrando así la expresividad, aplicabilidad y viabilidad del enfoque presentado.
+El resto del documento se organiza en varias secciones que incluyen una revisión del estado del arte, la presentación de la metodología SimulateIoT, una descripción detallada del metamodelo y las herramientas desarrolladas, la implementación del sistema de despliegue y ejecución, la exposición de casos de estudio aplicados, así como una discusión sobre las limitaciones detectadas y las conclusiones derivadas del trabajo.</t>
         </is>
       </c>
     </row>

--- a/introducciones/comparacion_introducciones.xlsx
+++ b/introducciones/comparacion_introducciones.xlsx
@@ -511,9 +511,32 @@
       </c>
     </row>
     <row r="3" ht="200" customHeight="1">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SimulateIoT: Domain Specific Language to Design, Code Generation and Execute IoT Simulation Environments</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>The Internet of Things (IoT) is widely applied in several areas such as smart-cities, home environments, agriculture, industry, intelligent buildings, etc. [46]. Usually, these IoT environments require using hundreds of sensors and actuators shared throughout these areas which are generating a vast amount of data. Data must be suitably stored, analysed and published using Big Data or Stream Processing techniques. Big Data or Stream Processing techniques must be applied to conveniently store and analyse published data. Taking into account where data are processed and stored, the IoT environment architecture can be defined by several computing layers (Edge, Fog and Cloud computing (see Figure 1) [30]). Edge layer is defined closer to data generators, Fog layer resides on top of the edge and act as intermediary layer with limited storing and processing capabilities and Cloud layer is defined with full storing and processing capabilities. Thus, the development of IoT systems requires the management and integration of conveniently heterogeneous technologies such as devices, actuators, databases, communication protocols, stream processing engines, etc. As a consequence, in order to implement, deploy and test the IoT systems a high investment must be made in time, money and effort.
+Simulating IoT environments is one way to decrease this initial investment because the users can measure and dimension the artefacts needed to deploy and interconnect the systems. Thus, these artefacts can include several kinds of devices from sensors or actuators to NoSQL databases, messaging brokers or stream processor engines. However, although there are several simulation environments for wireless sensor networks (WSN), there is a lack of IoT simulator tools for designing IoT environments at a high level that enable modeling this kind of systems by using the domain concepts and relationships. In addition, there is a lack of IoT simulation tools that makes it possible to deploy the IoT system on multiple nodes in order to test the communications among the system's elements and where complex IoT components such as databases, complex event processing or message brokers can be suitable deployed and tested.
+Currently, there is a lack of methodologies and tools to simulate IoT systems and allow users to properly describe the IoT environment. Currently, not only tools are needed but also methodologies to guide the simulation designing and simulation process of IoT environments. So, both methodologies and tools to simulate IoT systems are interesting research areas that should be developed. Thus, while methodologies would allow developers to describe the steps and the characteristics to simulate IoT systems, the tools would help to design and execute the IoT environment simulated in sandbox environments. These tools should take into account the main IoT characteristics including heterogeneous devices (sensors and actuators), heterogeneous communication mechanisms such as publish-subscribe communication protocol, analysis from information generated, storing of information, etc. However, an IoT environment is a broad and heterogeneous concept which involves heterogeneous technologies such as communication protocols such as publish-subscribe communication protocol, databases, analysis tools, etc. Not only should IoT methodologies and tools be designed and developed, but they should also be carried out using software engineering good practices.
+Model-Driven Development is an emerging software engineering research area that aims to develop software guided by models based on Metamodeling technique. Metamodeling is defined by four model layers (see Figure 2). Thus, a Model (M1) is conform to a MetaModel (M2). Moreover, a Metamodel conforms to a MetaMetaModel (M3) which is reflexive [2]. The MetaMetaModel level is represented by well-known standards and specifications such as Meta-Object Facilities (MOF) [29], ECore in EMF [48] and so on. A MetaModel defines the domain concepts and relationships in a specific domain in order to model partial reality. A Model (M1) defines a concrete system conform to a Metamodel. Then, from these models it is possible to generate totally or partially the application code (M0 - code) by model-to-text transformations [44]. Thus, high level definition (models) can be mapped by model-to-text transformations to specific technologies (target technology). Consequently, the software code can be generated for a specific technological platform, improving the technological independence and decreasing error proneness.
+So, Model-Driven Development (MDD) is proposed to tackle this heterogeneous technology (devices, actuators, complex event processing engines, notification technology, publish-subscribe communication protocol, etc.). Model-Driven Development [16], [20], [40], [43] increases the abstraction level where the software is implemented, focusing on the domain concepts and their relationships. These domain concepts (sensors, actuators, fog nodes, cloud nodes, etc.) and their relationships are defined by a model (M1), conform to a metamodel (M2), which can be analysed and validated using MDD techniques. Besides, the IoT environment code, including all the artefacts needed, can be generated from a model (M1) using model-to-text transformations, decreasing error proneness and increasing the user's productivity.
+The main contributions of this paper include:
+- This work shows that using Model-Driven Development techniques are suitable to develop tools and languages to tackle successfully the complexity of heterogeneous technologies in the context of IoT simulation environments.
+- A methodology called SimulateIoT to describe each step needed to define an IoT simulation environment and execute it.
+- A Model-Driven solution that supports the methodology proposed. It facilitates the development of each methodology phase by defining a SimulateIoT metamodel (M2), a graphical concrete syntax (graphical editor) to define models (M1) and a model-to-text transformation towards the code generation for specific IoT simulation environment (M0 - code). It includes the code generation to execute the IoT simulation. Furthermore, the IoT system generated can be deployed.
+- An IoT deployment process that makes it possible to deploy the simulation based on microservices which are deployed on Docker containers, including components such as databases, complex-event processing engines or message brokers.
+- The application of SimulateIoT to two case studies focused on different kinds of IoT systems (Smart buildings and Agricultural environment).
+The rest of the paper is structured as follows. In Section 2, we give an overview of existing IoT simulation approaches centered on both low level and high level IoT simulation environments. In Section 3, we present the SimulateIoT methodology. Section 4 describes SimulateIoT design and implementation phases including the SimulateIoT metamodel, the graphical editor and the model-to-text transformation developed. In Section 5 two case studies are presented. Finally, Section 6 elaborates on the limitations of the presented approach before Section 7 concludes the paper.</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>﻿La simulación de sistemas del Internet de las Cosas (IoT) constituye el área de trabajo principal, dada la alta inversión en desarrollo, despliegue y pruebas que requieren estos proyectos antes de su implementación física. La simulación permite modelar y razonar sobre los sistemas IoT, facilitando la optimización y reducción de costos asociados. En la literatura existen dos grandes enfoques: simuladores a nivel bajo que se centran en aspectos de hardware, redes y capacidades de los nodos; y simuladores a nivel alto que abordan el modelado de entornos, dispositivos y servicios mediante lenguajes específicos de dominio (DSL) o desarrollo guiado por modelos (MDD).

--- a/introducciones/comparacion_introducciones.xlsx
+++ b/introducciones/comparacion_introducciones.xlsx
@@ -491,22 +491,21 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>﻿En el campo de los modelos de transducción de secuencias, las arquitecturas dominantes tradicionalmente han utilizado redes neuronales recurrentes (RNN) o convolucionales (CNN) que incluyen mecanismos de atención para conectar el codificador y el decodificador. Estos modelos han logrado avances significativos en tareas como la traducción automática, donde la eficiencia computacional y la calidad de la traducción son aspectos fundamentales. La atención se ha consolidado como un componente clave para mejorar el rendimiento al permitir que el modelo se enfoque dinámicamente en diferentes partes de la secuencia de entrada durante la generación de la salida.
-Dentro de este panorama, la búsqueda por mejorar la eficiencia y la capacidad de paralelización de los modelos ha sido un tema central. Las arquitecturas basadas en recurrencias o convoluciones presentan limitaciones inherentes, como la necesidad de cómputos secuenciales o la dificultad para capturar dependencias a largo plazo de manera efectiva. En este contexto, surge la relevancia de explorar nuevas aproximaciones que permitan superar estos obstáculos, manteniendo o mejorando la calidad en las tareas de procesamiento de lenguaje natural, específicamente en traducción automática. El Transformer se posiciona como una innovadora alternativa que prescinde por completo de recurrencias y convoluciones, utilizando exclusivamente mecanismos de atención para tratar las secuencias.
-A pesar de los avances en modelos basados en atención para la traducción neuronal, persisten limitaciones importantes. Bahdanau et al. (2015) [VERIFICAR] presentan un modelo que mejora la capacidad de los modelos encoder-decoder tradicionales al evitar comprimir toda la oración de entrada en un vector fijo, lo que dificulta el manejo de oraciones largas. Sin embargo, esta arquitectura sigue usando redes recurrentes, lo que limita la eficiencia computacional y la posibilidad de paralelización efectiva.
-Por otro lado, Sutskever et al. (2014) desarrollan un modelo sequence-to-sequence basado en LSTM profundos que logra mejoras en la traducción, pero depende de representar la secuencia completa en vectores de dimensión fija y requiere invertir la secuencia de entrada para manejar mejor las dependencias largas. Esta estrategia, aunque efectiva, implica desafíos en la optimización y procesamiento.
-En conjunto, estas limitaciones señalan la necesidad de una arquitectura que supere las restricciones propias de las redes recurrentes y convolucionales, principalmente la secuencialidad en el procesamiento y la dificultad para paralelizar, y que facilite un entrenamiento más eficiente y un manejo adecuado de las dependencias a largo plazo sin requerir codificaciones fijas. Este es el vacío que justifica la exploración de enfoques alternativos como el Transformer.
-La propuesta central del trabajo es el Transformer, una arquitectura que responde directamente a la necesidad de superar las limitaciones de eficiencia y paralelización presentes en las arquitecturas basadas en redes recurrentes y convolucionales. Este modelo elimina completamente el uso de recurrencias y convoluciones, sustituyéndolos por un mecanismo de auto-atención multi-cabeza que permite establecer conexiones directas entre cualquier par de posiciones dentro de una secuencia.
-Este enfoque es especialmente adecuado para abordar los problemas asociados a la secuencialidad en el cómputo y la dificultad de paralelización, ya que reduce el coste computacional a una cantidad constante en función de la profundidad del modelo. De esta manera, se posibilita un entrenamiento más eficiente, con una mejor capacidad para capturar dependencias de largo alcance en las secuencias, sin la necesidad de codificaciones fijas que suelen limitar otros métodos. Así, el Transformer ofrece una solución innovadora que mejora el rendimiento en tareas de traducción automática, cumpliendo con las demandas identificadas en investigaciones previas.
-- Introducción de la arquitectura Transformer basada completamente en atención multi-cabeza, que permite manejar las secuencias sin recurrir a recurrencias ni convoluciones (sección 3).
-- Propuesta del mecanismo de atención escalar producto punto y multi-cabeza, diseñado para mejorar la representación y el procesamiento paralelo de las secuencias.
-- Uso de codificaciones posicionales sinusoidales para incorporar información sobre el orden de los elementos en la secuencia sin depender de estructuras recurrentes (sección 3.5).
-- Demostración experimental de la superioridad del modelo Transformer en tareas de traducción automática, específicamente en los conjuntos de datos WMT 2014 inglés-alemán e inglés-francés (sección 6.1).
-- Aplicación del modelo para análisis de constituyentes en inglés, evidenciando la capacidad de generalización del enfoque más allá de la traducción (sección 6.3).
-- Análisis y visualización de los mecanismos de atención, mostrando comportamientos interpretables que se relacionan con la estructura sintáctica y semántica del idioma (apéndice y sección 4).
-- Publicación del código asociado al Transformer para facilitar la reproducibilidad y permitir que la comunidad científica utilice y extienda el modelo.
-La validación del Transformer se realiza mediante experimentos en tareas estándar de traducción automática, específicamente en los conjuntos de datos WMT 2014 para traducción de inglés a alemán e inglés a francés, donde se compara su desempeño con modelos existentes y variantes del propio modelo para evaluar el impacto de diferentes hiperparámetros. Además, se extiende la evaluación a tareas de análisis sintáctico en inglés, demostrando la capacidad de generalización del modelo. Complementariamente, se llevan a cabo análisis e interpretaciones de los mecanismos de atención internos para comprender su funcionamiento y características explicativas, todo ello respaldando y justificando la solidez y eficacia de las contribuciones presentadas.
-El resto del documento se organiza comenzando con la introducción y motivación del trabajo, seguida por una descripción detallada de la arquitectura del Transformer, una justificación y análisis de las ventajas del mecanismo de auto-atención, y la presentación del régimen de entrenamiento. A continuación, se exponen los resultados experimentales que evalúan el desempeño del modelo en diferentes tareas, para finalmente concluir con una discusión y planteamiento de líneas futuras de trabajo. Además, el documento incluye referencias y apéndices que complementan la información técnica y experimental presentada.</t>
+          <t>﻿El área de trabajo se centra en la transducción de secuencias aplicada a tareas de traducción automática, un campo en el que los modelos tradicionales han empleado principalmente redes neuronales recurrentes y convolucionales complementadas con mecanismos de atención para mejorar la calidad de las traducciones. Estos métodos han tenido un papel destacado y han permitido avances significativos en el rendimiento de los sistemas, pero enfrentan importantes retos relacionados con la paralelización y el manejo de dependencias a largo plazo dentro de las secuencias, aspectos claves para la eficiencia y precisión de los modelos.
+La relevancia de este ámbito radica en la necesidad creciente de mejorar tanto la calidad como la eficiencia del entrenamiento de modelos de traducción automática, lo cual tiene un impacto directo en el procesamiento de grandes volúmenes de datos y en la capacidad de generalización de las soluciones implementadas. Los resultados previos y las motivaciones que sustentan este trabajo evidencian que, aunque los enfoques existentes han sido efectivos, se requiere explorar nuevas arquitecturas capaces de superar las limitaciones inherentes a la dependencia de las redes recurrentes y convolucionales, especialmente en lo que respecta a la paralelización y la gestión eficiente de relaciones a largo plazo en los datos secuenciales.
+A pesar de los avances significativos en modelos de traducción automática basados en arquitecturas recurrentes, persisten limitaciones importantes que justifican la propuesta de nuevas soluciones. Bahdanau et al. (2014) introducen un modelo encoder-decoder con mecanismo de atención suave que supera la restricción de codificar la oración completa en un vector de tamaño fijo. Sin embargo, su dependencia de arquitecturas recurrentes limita la paralelización y la eficiencia computacional, constituyendo una barrera para el entrenamiento rápido y escalable.
+Por otro lado, Sutskever et al. (2014) presentan un modelo de secuencia a secuencia basado en LSTM profundo que mejora el rendimiento, en parte, mediante la reversión del orden de las palabras en la secuencia de entrada. No obstante, este enfoque también depende de redes recurrentes, lo que dificulta la paralelización y el manejo eficiente de secuencias muy largas. En conjunto, estos trabajos comparten la limitación de basarse en modelos recurrentes para el procesamiento de secuencias, lo que reduce la capacidad de escalado y paralelización, problemas que el Transformer propone superar mediante un diseño exclusivo basado en mecanismos de atención.
+La propuesta central de este trabajo es el Transformer, una arquitectura de modelo de secuencia a secuencia que utiliza exclusivamente mecanismos de atención multi-cabeza para codificar y decodificar las secuencias, eliminando por completo la recurrencia y las convoluciones. Este enfoque tiene sentido frente a las limitaciones identificadas en los modelos recurrentes, ya que permite una mayor paralelización durante el entrenamiento y una gestión más eficiente de las dependencias a largo plazo en las secuencias, aspectos críticos que los modelos previos no podían optimizar adecuadamente debido a su naturaleza secuencial y dependiente.
+Al basarse únicamente en la atención, el Transformer logra conectar directamente todas las posiciones de entrada y salida, lo que facilita la captura de relaciones de largo alcance y mejora la escalabilidad computacional, superando así las barreras de paralelización y eficiencia impuestas por las arquitecturas recurrentes tradicionales. De esta forma, este modelo representa una innovación significativa al ofrecer una solución más rápida y efectiva para la transducción de secuencias en tareas como la traducción automática.
+- Desarrollo completo del Transformer basado exclusivamente en mecanismos de atención, sin recurrencia ni convoluciones, con una arquitectura detallada que permite mejorar la paralelización y el manejo de dependencias largas (sección 3).
+- Presentación y justificación de mecanismos de atención escalada y multi-cabeza, que permiten la atención a diferentes espacios de representación de manera simultánea.
+- Demostración de la eficiencia computacional y paralelización lograda por el modelo, comparada con arquitecturas recurrentes y convolucionales previas, evidenciada en análisis comparativo de complejidad y rendimiento (Tablas 1 y 2).
+- Presentación de resultados de estado del arte en las tareas de traducción automática inglés-alemán e inglés-francés que superan a modelos previos (sección 6).
+- Evaluación adicional del modelo en tareas de análisis sintáctico de parsing de constituyentes, mostrando la capacidad de generalización del Transformer a otras tareas de procesamiento del lenguaje (sección 6.3).
+- Publicación del código abierto utilizado para el entrenamiento y evaluación, promoviendo la reproducibilidad y extensión futura del trabajo.
+Cada una de estas contribuciones está desarrollada en las secciones específicas mencionadas del documento.
+El trabajo se valida mediante una serie de experimentos exhaustivos en tareas de traducción automática utilizando los conjuntos de datos WMT 2014 para los pares de idiomas inglés-alemán e inglés-francés, en los cuales se compara el rendimiento y la eficiencia del modelo propuesto frente a arquitecturas recurrentes y convolucionales previas. Además, se realiza una evaluación en tareas de análisis sintáctico, específicamente en parsing de constituyentes, para demostrar la capacidad del modelo para generalizar a otros ámbitos del procesamiento del lenguaje natural. Estos experimentos se complementan con análisis de variaciones del modelo y comparaciones detalladas que respaldan la solidez y versatilidad de la propuesta.
+El resto del artículo se organiza en secciones que abarcan la arquitectura del modelo, la justificación y comparación de los mecanismos de atención utilizados, los detalles del entrenamiento, los resultados y análisis de las experimentaciones realizadas, así como las conclusiones y las referencias bibliográficas. Esta estructura facilita una comprensión progresiva y detallada del desarrollo y la validación del modelo propuesto.</t>
         </is>
       </c>
     </row>

--- a/introducciones/comparacion_introducciones.xlsx
+++ b/introducciones/comparacion_introducciones.xlsx
@@ -491,21 +491,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>﻿El área de trabajo se centra en la transducción de secuencias aplicada a tareas de traducción automática, un campo en el que los modelos tradicionales han empleado principalmente redes neuronales recurrentes y convolucionales complementadas con mecanismos de atención para mejorar la calidad de las traducciones. Estos métodos han tenido un papel destacado y han permitido avances significativos en el rendimiento de los sistemas, pero enfrentan importantes retos relacionados con la paralelización y el manejo de dependencias a largo plazo dentro de las secuencias, aspectos claves para la eficiencia y precisión de los modelos.
-La relevancia de este ámbito radica en la necesidad creciente de mejorar tanto la calidad como la eficiencia del entrenamiento de modelos de traducción automática, lo cual tiene un impacto directo en el procesamiento de grandes volúmenes de datos y en la capacidad de generalización de las soluciones implementadas. Los resultados previos y las motivaciones que sustentan este trabajo evidencian que, aunque los enfoques existentes han sido efectivos, se requiere explorar nuevas arquitecturas capaces de superar las limitaciones inherentes a la dependencia de las redes recurrentes y convolucionales, especialmente en lo que respecta a la paralelización y la gestión eficiente de relaciones a largo plazo en los datos secuenciales.
-A pesar de los avances significativos en modelos de traducción automática basados en arquitecturas recurrentes, persisten limitaciones importantes que justifican la propuesta de nuevas soluciones. Bahdanau et al. (2014) introducen un modelo encoder-decoder con mecanismo de atención suave que supera la restricción de codificar la oración completa en un vector de tamaño fijo. Sin embargo, su dependencia de arquitecturas recurrentes limita la paralelización y la eficiencia computacional, constituyendo una barrera para el entrenamiento rápido y escalable.
-Por otro lado, Sutskever et al. (2014) presentan un modelo de secuencia a secuencia basado en LSTM profundo que mejora el rendimiento, en parte, mediante la reversión del orden de las palabras en la secuencia de entrada. No obstante, este enfoque también depende de redes recurrentes, lo que dificulta la paralelización y el manejo eficiente de secuencias muy largas. En conjunto, estos trabajos comparten la limitación de basarse en modelos recurrentes para el procesamiento de secuencias, lo que reduce la capacidad de escalado y paralelización, problemas que el Transformer propone superar mediante un diseño exclusivo basado en mecanismos de atención.
-La propuesta central de este trabajo es el Transformer, una arquitectura de modelo de secuencia a secuencia que utiliza exclusivamente mecanismos de atención multi-cabeza para codificar y decodificar las secuencias, eliminando por completo la recurrencia y las convoluciones. Este enfoque tiene sentido frente a las limitaciones identificadas en los modelos recurrentes, ya que permite una mayor paralelización durante el entrenamiento y una gestión más eficiente de las dependencias a largo plazo en las secuencias, aspectos críticos que los modelos previos no podían optimizar adecuadamente debido a su naturaleza secuencial y dependiente.
-Al basarse únicamente en la atención, el Transformer logra conectar directamente todas las posiciones de entrada y salida, lo que facilita la captura de relaciones de largo alcance y mejora la escalabilidad computacional, superando así las barreras de paralelización y eficiencia impuestas por las arquitecturas recurrentes tradicionales. De esta forma, este modelo representa una innovación significativa al ofrecer una solución más rápida y efectiva para la transducción de secuencias en tareas como la traducción automática.
-- Desarrollo completo del Transformer basado exclusivamente en mecanismos de atención, sin recurrencia ni convoluciones, con una arquitectura detallada que permite mejorar la paralelización y el manejo de dependencias largas (sección 3).
-- Presentación y justificación de mecanismos de atención escalada y multi-cabeza, que permiten la atención a diferentes espacios de representación de manera simultánea.
-- Demostración de la eficiencia computacional y paralelización lograda por el modelo, comparada con arquitecturas recurrentes y convolucionales previas, evidenciada en análisis comparativo de complejidad y rendimiento (Tablas 1 y 2).
-- Presentación de resultados de estado del arte en las tareas de traducción automática inglés-alemán e inglés-francés que superan a modelos previos (sección 6).
-- Evaluación adicional del modelo en tareas de análisis sintáctico de parsing de constituyentes, mostrando la capacidad de generalización del Transformer a otras tareas de procesamiento del lenguaje (sección 6.3).
-- Publicación del código abierto utilizado para el entrenamiento y evaluación, promoviendo la reproducibilidad y extensión futura del trabajo.
-Cada una de estas contribuciones está desarrollada en las secciones específicas mencionadas del documento.
-El trabajo se valida mediante una serie de experimentos exhaustivos en tareas de traducción automática utilizando los conjuntos de datos WMT 2014 para los pares de idiomas inglés-alemán e inglés-francés, en los cuales se compara el rendimiento y la eficiencia del modelo propuesto frente a arquitecturas recurrentes y convolucionales previas. Además, se realiza una evaluación en tareas de análisis sintáctico, específicamente en parsing de constituyentes, para demostrar la capacidad del modelo para generalizar a otros ámbitos del procesamiento del lenguaje natural. Estos experimentos se complementan con análisis de variaciones del modelo y comparaciones detalladas que respaldan la solidez y versatilidad de la propuesta.
-El resto del artículo se organiza en secciones que abarcan la arquitectura del modelo, la justificación y comparación de los mecanismos de atención utilizados, los detalles del entrenamiento, los resultados y análisis de las experimentaciones realizadas, así como las conclusiones y las referencias bibliográficas. Esta estructura facilita una comprensión progresiva y detallada del desarrollo y la validación del modelo propuesto.</t>
+          <t>﻿The field of sequence modeling and transduction has traditionally been dominated by recurrent neural networks (RNNs) and their variants, such as long short-term memory (LSTM) and gated recurrent units (GRU). These models have been widely applied to problems like language modeling and machine translation, due to their ability to process sequences of arbitrary length. However, the inherently sequential nature of RNNs limits parallelization during training and presents difficulties when modeling long-range dependencies within sequences. To address these issues, attention mechanisms have been incorporated into recurrent models, enabling them to capture dependencies between distant positions in input and output sequences more effectively. Despite these advances, attention is commonly used in conjunction with recurrence rather than replacing it.
+This work situates itself within this context by exploring a model architecture that entirely removes the recurrent components and relies solely on attention mechanisms to capture global dependencies. By doing so, it aims to overcome the computational and modeling constraints imposed by recurrent structures, offering both improved parallelization and potentially enhanced performance in sequence transduction tasks.
+Bahdanau et al. (2014) introduced an encoder-decoder model with an attention mechanism that addresses the limitation of encoding an entire input sentence into a single fixed-length vector. However, their approach still relies on recurrent neural networks (RNNs) and thus does not remove the inherent sequential computation that restricts training parallelism and efficiency. Similarly, Sutskever et al. (2014) presented deep LSTM models for sequence-to-sequence learning that achieve improved translation performance, but still depend on fixed vector representations and face challenges with long sentences and complex dependencies. Both these influential works do not fully eliminate recurrence, which limits their ability to fully parallelize training and effectively model long-range dependencies. Therefore, there remains a need for a model that completely removes the strict dependency on RNNs and convolutions, employing only attention mechanisms to enable more efficient parallel processing and better handling of global dependencies in sequence transduction.
+The central proposal of this work is the Transformer, a novel encoder-decoder architecture that entirely replaces recurrent layers with multi-head self-attention mechanisms and position-wise feed-forward networks to capture global dependencies within sequences. By relying solely on attention, the Transformer eliminates the sequential computation inherent in recurrent architectures, enabling significantly more parallelization during training. Additionally, the model uses sinusoidal positional encodings to inject information about the order of tokens in the sequence, which addresses the absence of recurrence or convolutional structure. This design not only facilitates highly parallel and efficient training but also achieves state-of-the-art performance in sequence transduction tasks like machine translation, directly addressing the limitations found in prior approaches.
+- Introduction of the Transformer, the first sequence transduction model based entirely on attention mechanisms without recurrence or convolution (Section 3).
+- Implementation of multi-head attention that allows the model to jointly attend to information from different representation subspaces at different positions (Section 3.2).
+- Proposal and effective use of sinusoidal positional encodings to provide information about the relative or absolute position of tokens in a sequence (Section 3.5).
+- Empirical demonstration that the Transformer outperforms previous state-of-the-art models in English-to-German and English-to-French translation tasks at a fraction of the computational training cost (Section 6.1).
+- Additional evaluation showing that the Transformer generalizes well to other tasks such as English constituency parsing (Section 6.3).
+The validation of this work is conducted through extensive empirical experiments on large-scale machine translation benchmarks, specifically the WMT 2014 English-to-German and English-to-French datasets. The model is trained using high-performance GPUs to assess its efficiency and scalability. Performance is evaluated on standardized test sets using the BLEU metric, enabling direct comparison with prior state-of-the-art methods such as recurrent and convolutional neural network models and their ensembles. Additionally, the model is tested on other natural language processing tasks, like English constituency parsing, to demonstrate its generalization capabilities. These experiments collectively support the effectiveness and advantages of the proposed Transformer architecture.
+The rest of the article is organized into sections that first provide the context and related work, followed by a detailed description of the model architecture including attention mechanisms and feed-forward networks. Subsequent sections cover the datasets and training procedures used, present experimental results and analyses, and conclude with discussions on future research directions.</t>
         </is>
       </c>
     </row>
@@ -538,21 +534,19 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>﻿La simulación de sistemas del Internet de las Cosas (IoT) constituye el área de trabajo principal, dada la alta inversión en desarrollo, despliegue y pruebas que requieren estos proyectos antes de su implementación física. La simulación permite modelar y razonar sobre los sistemas IoT, facilitando la optimización y reducción de costos asociados. En la literatura existen dos grandes enfoques: simuladores a nivel bajo que se centran en aspectos de hardware, redes y capacidades de los nodos; y simuladores a nivel alto que abordan el modelado de entornos, dispositivos y servicios mediante lenguajes específicos de dominio (DSL) o desarrollo guiado por modelos (MDD).
-A pesar de estos avances, muchas herramientas disponibles demandan elevadas competencias técnicas, carecen de interfaces gráficas amigables, no ofrecen generación automática de código o no cuentan con mecanismos para validar previamente el entorno simulado. Asimismo, varios simuladores no contemplan adecuadamente conceptos clave emergentes en el ámbito IoT, como las arquitecturas de fog computing y cloud computing, el procesamiento de eventos complejos y los protocolos de comunicación publish-subscribe, todos ellos fundamentales para la correcta representación y simulación de sistemas IoT modernos y heterogéneos.
-Aunque existen diversas propuestas para la simulación de sistemas IoT, varios trabajos muestran limitaciones que evidencian la necesidad de nuevos enfoques. Alwasel et al. (2020) [VERIFICAR] con BigDataSDNSim se centran en la simulación de datos masivos en entornos cloud SDN, pero no ofrecen un modelado integral de simulación IoT que abarque un alto nivel de abstracción a través de múltiples capas arquitectónicas. Clemente et al. (2018) [VERIFICAR] desarrollaron un lenguaje específico de dominio para domótica, pero su enfoque no contempla la simulación ni aspectos relacionados con almacenamiento o procesamiento basados en eventos. Por su parte, Mehdi et al. (2014) [VERIFICAR] con CupCarbon proporcionan un simulador gráfico para redes de sensores WSN, sin embargo, no modelan almacenamiento avanzado, procesamiento complejo ni la comunicación mediante protocolos publish-subscribe con brokers. Finalmente, Zeng et al. (2017) con IOTSim abordan la simulación de aplicaciones IoT en cloud con un enfoque en big data, pero su herramienta exige configuraciones técnicas complejas y carece de diseño gráfico y validación previa de los modelos.
-En conjunto, estos trabajos presentan carencias importantes como la ausencia de abstracción visual adecuada para la representación de simulaciones IoT que integren las capas Edge, Fog y Cloud; una dependencia significativa en configuraciones técnicas de bajo nivel; la falta de generación automática de código integral y despliegue mediante arquitecturas basadas en microservicios; y la inexistencia de mecanismos para validar modelos antes de la simulación, aspectos clave para la viabilidad y usabilidad de entornos de simulación IoT modernos y representativos.
-La propuesta central de este trabajo consiste en el desarrollo de SimulateIoT, un enfoque basado en desarrollo guiado por modelos que permite definir, generar código y desplegar entornos de simulación IoT complejos sin necesidad de programación manual. Este enfoque incluye un metamodelo de dominio que representa de forma integral los conceptos clave del IoT, una sintaxis gráfica para facilitar el modelado visual del sistema y una transformación modelo-texto que genera automáticamente el código asociado, que incluye microservicios, contenedores Docker, brokers MQTT, bases de datos NoSQL y motores para el procesamiento de eventos y flujos de datos. La comunicación entre los distintos nodos IoT, como sensores, actuadores y nodos fog y cloud, se gestiona mediante un protocolo de publicación-suscripción, lo que permite una simulación fiel a arquitecturas reales y heterogéneas. Además, se incorporan mecanismos para la validación del modelo y para la monitorización durante la simulación, lo que garantiza la calidad y el control del entorno simulado.
-Este enfoque se adapta a las carencias detectadas en trabajos previos, al ofrecer una abstracción visual adecuada y una completa integración de las capas Edge, Fog y Cloud, facilitando la generación automática de código y el despliegue en arquitecturas modernas basadas en microservicios. De esta forma, SimulateIoT responde a la necesidad de contar con herramientas que simplifiquen el diseño y la ejecución de simulaciones IoT complejas, manteniendo una alta fidelidad con respecto a las arquitecturas actuales y reduciendo drásticamente la necesidad de configuraciones técnicas complejas o conocimiento especializado para su uso.
-- Definición de un metamodelo que captura conceptos IoT a alto nivel, abarcando capas Edge, Fog, Cloud, sensores, actuadores, bases de datos, procesamiento de eventos y comunicación (Sección III.A).
-- Desarrollo de una sintaxis gráfica para modelar estos sistemas (Sección III.B).
-- Implementación de reglas OCL para la validación del modelo en base a restricciones estructurales y semánticas (Sección III.B).
-- Creación de transformaciones modelo-texto en Acceleo para generar código completo que materializa los modelos en microservicios desplegables (Sección III.C).
-- Implementación del sistema de despliegue y ejecución sobre Docker Swarm y monitorización integrada (Sección III.D).
-- Presentación de dos estudios de caso reales (edificio inteligente y agricultura) mostrando la capacidad descriptiva, generación y despliegue (Sección V).
-- Discusión sobre las limitaciones y futuras extensiones para movilidad y dinámicas de la simulación (Sección VI).
-La validación del trabajo se lleva a cabo mediante la aplicación de dos estudios de caso prácticos que ejemplifican y respaldan las contribuciones propuestas. El primer estudio simula un edificio inteligente compuesto por múltiples nodos fog distribuidos por diferentes edificios, integrando sensores de temperatura, presencia y humo, junto con reglas para el control automatizado de sistemas como la calefacción, monitorizados mediante bases de datos y motores de procesamiento de eventos complejos. El segundo estudio de caso se centra en un entorno agrícola, donde se simulan sensores para medir variables como temperatura, humedad, pH y presión de agua, junto con actuadores de riego, utilizando arquitecturas basadas en nodos fog y cloud, almacenamiento en bases de datos MongoDB y reglas para notificaciones y control. Ambos casos de estudio permiten la generación automática de código, su despliegue en contenedores Docker y la ejecución completa de la simulación, demostrando así la expresividad, aplicabilidad y viabilidad del enfoque presentado.
-El resto del documento se organiza en varias secciones que incluyen una revisión del estado del arte, la presentación de la metodología SimulateIoT, una descripción detallada del metamodelo y las herramientas desarrolladas, la implementación del sistema de despliegue y ejecución, la exposición de casos de estudio aplicados, así como una discusión sobre las limitaciones detectadas y las conclusiones derivadas del trabajo.</t>
+          <t>﻿The increasing importance of Internet of Things (IoT) technologies across domains such as smart cities, home environments, agriculture, and industry has generated a growing need for effective tools to develop, deploy, and test IoT systems. Developing and validating such systems in real-world settings often involves significant investments in hardware and software infrastructure, as well as considerable time and effort. To address these challenges, simulation environments have been proposed to model and reason about IoT systems before actual deployment. Prior approaches focus either on low-level simulation aspects—such as hardware details, sensor network behavior, and network protocols—or on higher-level abstractions emphasizing contextual modeling and system components.
+Model-driven development (MDD) has emerged as a promising paradigm to capture domain-specific concepts and relationships in IoT systems, facilitating system design through domain-specific languages and automated code generation. Existing IoT simulation frameworks and modeling tools, however, tend to focus on either detailed hardware/network simulation or on limited abstraction levels that lack integration of key IoT architectural layers such as Edge, Fog, and Cloud computing. Moreover, many solutions require advanced programming knowledge and lack user-friendly graphical interfaces to allow a broader range of users to design and analyze IoT scenarios effectively. These observations underscore the relevance of approaches that enable high-level, model-driven design and simulation of complex IoT environments with heterogeneous technology and communications, supporting various abstractions and easing the development and testing process.
+Despite the advances in IoT simulation and modeling, significant gaps remain in the existing body of work. Alwasel et al. (2020) [VERIFICAR] present simulators focused on big data analytics in cloud environments but do not provide comprehensive simulation frameworks for IoT systems at a high level of abstraction. Clemente et al. (2018) [VERIFICAR] address complex event processing but do not extend their approach to complete IoT environment simulation nor to automatic code generation for deployment. Papadopoulos et al. (2013) [VERIFICAR] offer experimental platforms for wireless sensor networks; however, their focus is restricted to hardware-level simulation without including Fog or Cloud computing concepts. Patel and Cassou (2015) [VERIFICAR] develop high-level IoT application tools but lack integrated graphical interfaces to simulate full architectures spanning different layers or to validate configurations effectively. Lastly, Mehdi et al. (2014) [VERIFICAR] propose discrete-event, multi-agent wireless sensor network simulators but do not provide abstractions for highly configurable nodes with publish-subscribe communication patterns nor container-based deployment. Consequently, there is a clear absence of a comprehensive and accessible approach that allows modeling, validating, automatically generating code, and deploying simulations of complex IoT environments incorporating Edge, Fog, and Cloud layers, while supporting advanced data stream and event processing, and catering to users with varying technical expertise.
+The central proposal of this work is SimulateIoT, a domain-specific language (DSL) accompanied by a set of model-driven development (MDD) tools designed to define complex IoT environment models at a high level of abstraction. This approach enables automatic generation of source code for microservices deployable within Docker containers and supports the execution of simulations via a distributed architecture that leverages MQTT-based communication alongside Fog and Cloud processing. The solution encompasses a comprehensive metamodel that incorporates key IoT elements such as sensors, actuators, Edge, Fog, and Cloud nodes, as well as publish-subscribe communication topics, synthetic and historical data generation capabilities, complex event processing engines, and rules for data analysis and notification.
+This approach addresses the identified gaps by providing an integrated framework that not only models and validates heterogeneous IoT systems spanning multiple architectural layers but also automates code generation and deployment, thereby reducing the need for specialized programming skills. By combining high-level abstractions with practical deployment mechanisms, SimulateIoT facilitates the design, simulation, and analysis of sophisticated IoT scenarios, making it accessible to users with diverse technical backgrounds and effectively bridging the limitations present in existing solutions.
+- Design of the SimulateIoT metamodel that conceptually represents IoT environments with support for Edge, Fog, and Cloud layers, sensors/actuators, data, and communication (Section III).
+- Definition of a graphical syntax to build models conforming to the metamodel using Eclipse GMF tools (Section IV.B).
+- Implementation of model-to-text transformations to automatically generate code, including microservices, MQTT brokers, NoSQL databases, and processing engines (Section IV.C).
+- Proposal of a deployment and execution environment based on Docker containers orchestrated with Docker Swarm to simulate large and heterogeneous IoT environments (Section IV.D).
+- Presentation of two relevant case studies—an intelligent university building and an agricultural environment—with full deployment and results analysis (Section V).
+- Discussion of limitations and future improvements, particularly regarding node mobility and advanced data generation patterns (Section VI).
+The validation of this work is conducted through two practical case studies implemented using the SimulateIoT environment. The first case involves the simulation of a smart building—specifically, a technology school—with multiple sensors and actuators distributed across different buildings, where Fog and Cloud nodes analyze data and generate control rules for heating systems. The second case models an agricultural environment comprised of sensors measuring parameters such as temperature, humidity, pH, and water pressure, along with actuators controlling irrigation, all managed by Fog and Cloud nodes equipped with real-time processing engines. Both cases demonstrate the design, automatic code generation, deployment of simulations in Docker containers, and real-time monitoring capabilities. These studies provide evidence for the scalability, expressiveness, and applicability of the proposed methodology and tools in diverse real-world IoT contexts.
+The remainder of the article is organized into sections covering the introduction and motivation, related work, the SimulateIoT methodology, design and implementation aspects including the metamodel, graphical syntax, and model-to-text transformations, deployment and execution, case studies, discussion of limitations and future work, followed by the conclusion and references.</t>
         </is>
       </c>
     </row>

--- a/introducciones/comparacion_introducciones.xlsx
+++ b/introducciones/comparacion_introducciones.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -508,15 +508,88 @@
     <row r="3" ht="200" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>BERT: Pre-training of Deep Bidirectional Transformers for Language Understanding</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Language model pre-training has been shown to be effective for improving many natural language processing tasks (Dai and Le, 2015; Peters et al., 2018a; Radford et al., 2018; Howard and Ruder, 2018). These include sentence-level tasks such as natural language inference (Bowman et al., 2015; Williams et al., 2018) and paraphrasing (Dolan and Brockett, 2005), which aim to predict the relationships between sentences by analyzing them holistically, as well as token-level tasks such as named entity recognition and question answering, where models are required to produce fine-grained output at the token level (Tjong Kim Sang and De Meulder, 2003; Rajpurkar et al., 2016).
+There are two existing strategies for applying pre-trained language representations to downstream tasks: feature-based and fine-tuning. The feature-based approach, such as ELMo (Peters et al., 2018a), uses task-specific architectures that include the pre-trained representations as additional features. The fine-tuning approach, such as the Generative Pre-trained Transformer (OpenAI GPT) (Radford et al., 2018), introduces minimal task-specific parameters, and is trained on the downstream tasks by simply fine-tuning all pre-trained parameters. The two approaches share the same objective function during pre-training, where they use unidirectional language models to learn general language representations.
+We argue that current techniques restrict the power of the pre-trained representations, especially for the fine-tuning approaches. The major limitation is that standard language models are unidirectional, and this limits the choice of architectures that can be used during pre-training. For example, in OpenAI GPT, the authors use a left-to-right architecture, where every token can only attend to previous tokens in the self-attention layers of the Transformer (Vaswani et al., 2017). Such restrictions are sub-optimal for sentence-level tasks, and could be very harmful when applying fine-tuning based approaches to token-level tasks such as question answering, where it is crucial to incorporate context from both directions.
+In this paper, we improve the fine-tuning based approaches by proposing BERT: Bidirectional Encoder Representations from Transformers. BERT alleviates the previously mentioned unidirectionality constraint by using a "masked language model" (MLM) pre-training objective, inspired by the Cloze task (Taylor, 1953). The masked language model randomly masks some of the tokens from the input, and the objective is to predict the original vocabulary id of the masked word based only on its context. Unlike left-to-right language model pre-training, the MLM objective enables the representation to fuse the left and the right context, which allows us to pre-train a deep bidirectional Transformer. In addition to the masked language model, we also use a "next sentence prediction" task that jointly pre-trains text-pair representations. The contributions of our paper are as follows:
+- We demonstrate the importance of bidirectional pre-training for language representations. Unlike Radford et al. (2018), which uses unidirectional language models for pre-training, BERT uses masked language models to enable pre-trained deep bidirectional representations. This is also in contrast to Peters et al. (2018a), which uses a shallow concatenation of independently trained left-to-right and right-to-left LMs.
+- We show that pre-trained representations reduce the need for many heavily-engineered task-specific architectures. BERT is the first fine-tuning based representation model that achieves state-of-the-art performance on a large suite of sentence-level and token-level tasks, outperforming many task-specific architectures.
+- BERT advances the state of the art for eleven NLP tasks. The code and pre-trained models are available at https://github.com/google-research/bert.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>﻿Recent advances in natural language processing (NLP) have demonstrated the importance of pre-trained language models for improving performance across a diverse set of tasks. Traditional approaches often rely on unidirectional models that condition on either the left or right context, limiting the richness of learned representations. Modern architectures, such as Transformers and bidirectional LSTM-based models, have expanded the ability to capture comprehensive contextual information. Techniques like ELMo utilize bidirectional LSTMs to generate deep contextualized word embeddings, while models such as OpenAI GPT employ Transformer architectures with a unidirectional left-to-right focus. These models form the foundation of many state-of-the-art NLP systems, addressing challenges in tasks like textual entailment, question answering, and named entity recognition. Enhancing these pre-trained models to incorporate richer bidirectional context remains a central theme in advancing the field.
+Previous approaches have made significant strides in improving language representations, yet they retain notable limitations. Peters et al. (2018) propose ELMo, a bidirectional LSTM-based model that enhances NLP tasks by generating contextualized embeddings. However, its architecture relies on independently trained left-to-right and right-to-left LSTMs combined at a shallow level, which restricts the depth of bidirectionality and the representation’s completeness. Similarly, Radford et al. (2018) [VERIFICAR] introduce GPT, a Transformer-based model pre-trained in a unidirectional left-to-right manner. While GPT achieves strong performance, its unidirectional nature limits its ability to fully leverage context from both preceding and succeeding tokens. Together, these models fall short of capturing deep, truly bidirectional context, highlighting a gap that motivates the development of more fully bidirectional pre-training methods.
+The approach presented addresses these limitations by introducing a deeply bidirectional Transformer encoder that is pre-trained using two novel tasks: the Masked Language Model (Masked LM) and Next Sentence Prediction. This design enables the model to learn comprehensive context representations by conditioning on both left and right contexts simultaneously, overcoming the unidirectional constraints observed in prior models. By pre-training with these objectives, the model generates rich, fully bidirectional representations that can be fine-tuned for a wide array of natural language processing tasks without requiring task-specific architectural changes. This approach directly tackles the gap left by earlier models that either lacked deep bidirectionality or were limited by their unidirectional training, establishing a more versatile and effective framework for language understanding.
+- Introduction of deep bidirectional pre-training based on Transformers.
+- Combined use of Masked Language Model and Next Sentence Prediction tasks to capture context from both directions.
+- Demonstration of state-of-the-art improvements on eleven natural language processing tasks including GLUE, SQuAD v1.1 and v2.0, SWAG, among others.
+- Provision of pre-trained models and open-source code to the community (https://github.com/google-research/bert).
+- Comprehensive analysis of model ablations, including effects of model size and contribution of individual layers.
+The validation of the proposed work is conducted through fine-tuning experiments across eleven diverse natural language processing tasks, encompassing text classification, natural language inference, question answering, and benchmarks such as GLUE and SWAG. These experiments provide empirical evidence supporting the effectiveness and generality of the approach, demonstrating improvements in key evaluation metrics such as accuracy and F1 scores compared to prior state-of-the-art methods.
+The remainder of the article is organized into sections that first cover the pre-training tasks and detailed descriptions of the model components. This is followed by comprehensive experimental sections presenting the results and analyses, including ablation studies and discussions. The document is structured in a technical manner to thoroughly explain the model architecture, datasets, fine-tuning procedures, experiments, and corresponding analyses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="200" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Aplicación de Redes Neuronales Artificiales para la Clasificación de Actividades de la Vida Diaria en Sujetos con Enfermedad de Párkinson</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Español</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>La Enfermedad de Parkinson (EP) se caracteriza por ser una afección crónica y progresiva provocada por el deterioro neuronal en la sustancia nigra y la disminución de los niveles de dopamina en el cuerpo [1]. La enfermedad de Párkinson no es curable, por lo que el objetivo de los tratamientos es exclusivamente sintomático [2]. El manejo farmacológico es el principal tratamiento del paciente con EP. Se requiere de un tratamiento que incluya diversas disciplinas en su manejo para promover la participación del paciente en la sociedad y fomentar la actividad física desde el momento del diagnóstico con la finalidad de adquirir estrategias de movimiento antes de presentar limitaciones físicas y cognitivas más severas [3]. A pesar del óptimo tratamiento 70 % de los pacientes con enfermedad de Parkinson experimentan momentos donde los síntomas motores como tremor, bradicinesia e inestabilidad postural empeoran, estos momentos son conocidos como fluctuaciones motoras [4].
+El seguimiento de las fluctuaciones de los síntomas motores en pacientes con enfermedad de Párkinson se realiza actualmente a través de la autoevaluación subjetiva de los pacientes. Sin embargo, los médicos y especialistas requieren información objetiva y más confiable sobre la ocurrencia de las fluctuaciones para permitir una planeación precisa del tratamiento [5].
+La evaluación mediante sensores inerciales de los signos motores y fluctuaciones, pueden proporcionar retroalimentación objetiva y confiable sobre los efectos del manejo terapéutico [6]. A la fecha este tipo de sensores han sido estudiados para detectar actividades de la vida diaria, principalmente caminar y en pocos casos acostarse, sentarse y mantenerse de pie [7][8][9]. En estas investigaciones se han utilizado diversos tipos, números, ubicaciones de sensores y métodos de clasificación variables sin alcanzar un consenso a la fecha. Principalmente se ha utilizado una configuración de un sensor predominantemente en la cadera y de tipo acelerómetro [7][8][9]. Aunque los primeros experimentos se concentraban en la validación de laboratorio de los registros obtenidos con los sensores inerciales, actualmente el interés parece concentrarse en probar nuevos métodos de clasificación centrados en un propósito clínico, con precisiones reportadas entre un 55.9% y 90.8% [8][9][10].
+La clasificación de actividades de la vida diaria utilizando Redes Neuronales Artificiales (RNA) ha demostrado el alto potencial de aplicar Deep Learning a la resolución de los problemas en la clasificación de señales realizadas por pacientes con Enfermedad de Párkinson. Estas herramientas han ayudado a desarrollar nuevas posibilidades de apoyo para que los especialistas puedan llevar a cabo evaluaciones más certeras de la funcionalidad motora y de los tratamientos proporcionados mediante una mejor calidad de monitoreo en la rehabilitación de los pacientes. El uso de inteligencia artificial para ayudar a la detección y tratamiento de la EP es de creciente interés para médicos e investigadores alrededor del mundo [11]. Actualmente se está trabajando en el desarrollo de diversos métodos de inteligencia artificial basados en algoritmos de aprendizaje profundo que permitan la detección y poder hacer un seguimiento de los principales síntomas motores de la Enfermedad de Párkinson [12].
+De acuerdo con el estudio donde las RNA son utilizadas para clasificar las AVDs desempeñadas por 5 pacientes con Enfermedad de Párkinson, se obtuvo un porcentaje de exactitud del 99 % en el aprendizaje de clasificación [13]. Por lo que en este trabajo se busca obtener un método con resultados semejantes, pero realizando reducción de dimensionalidad de la base de datos a través de la extracción de la información más relevante para la clasificación de actividades de la vida diaria utilizando sensores inerciales.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>﻿El presente estudio se enmarca en la aplicación de inteligencia artificial y aprendizaje profundo para el monitoreo y evaluación de pacientes con enfermedad de Parkinson, centrándose específicamente en la clasificación de actividades de la vida diaria a partir de datos obtenidos mediante sensores inerciales. Esta área cobra relevancia debido a la amplia heterogeneidad y variabilidad de los síntomas motores en estos pacientes, lo que dificulta su seguimiento efectivo mediante métodos convencionales. En el campo, se observa un interés creciente en técnicas como el Análisis de Componentes Principales (PCA) para la reducción de dimensionalidad de datos y en el uso de modelos de Redes Neuronales Artificiales tipo Perceptrón Multicapa (MLP) para clasificar patrones motores, consolidando así la aplicación del aprendizaje profundo en la rehabilitación y monitoreo clínico.
+A pesar de los avances, los trabajos previos presentan limitaciones importantes, como la escasa capacidad de generalización de los modelos debido al bajo número de sujetos y a la falta de heterogeneidad en las muestras. También se destaca la posible influencia de la colocación de sensores sobre la calidad y consistencia de las señales capturadas, así como el desequilibrio en las bases de datos utilizadas, lo cual dificulta alcanzar resultados precisos y robustos en contextos reales. Estas deficiencias evidencian la necesidad de desarrollar métodos capaces de lograr alta precisión en escenarios variados y con datos desbalanceados, lo que fundamenta la investigación propuesta.
+En respuesta a estas limitaciones, este trabajo presenta el diseño y desarrollo de un modelo de Red Neuronal Artificial tipo Perceptrón Multicapa, combinado con la técnica de Análisis de Componentes Principales para reducir la dimensionalidad de la base de datos. Esta estrategia busca mejorar el desempeño del clasificador en la identificación automática de las actividades de la vida diaria en pacientes con enfermedad de Parkinson, gestionando eficazmente la complejidad y volumen de la información proveniente de los sensores. El modelo se entrena con datos de sensores inerciales, aplicando técnicas de preprocesamiento, normalización y codificación que permiten optimizar tanto la precisión como la eficiencia computacional. Esta solución resulta adecuada para su implementación en dispositivos con recursos limitados, ofreciendo un sistema robusto y generalizable para condiciones reales.
+Las contribuciones específicas de este trabajo son las siguientes:
+- Desarrollo de un modelo MLP entrenado con datos de PCA que clasifica con alta precisión seis actividades de la vida diaria (sección metodología y resultados).
+- Demostración de la efectividad de PCA para reducir dimensionalidad sin pérdida significativa de información, optimizando el entrenamiento de la RNA (sección materiales y métodos).
+- Evaluación detallada del desempeño de los modelos con diferentes divisiones de sujetos en entrenamiento y prueba, evidenciando la importancia de la representatividad de los datos para la generalización (sección resultados y discusión).
+- Análisis comparativo de parámetros y arquitecturas de red, mostrando la viabilidad de modelos con menos parámetros para dispositivos de bajo recurso (sección resultados).
+- Propuesta de aplicación futura para un sistema de apoyo al monitoreo clínico de pacientes con Parkinson basado en inteligencia artificial (conclusiones).
+Para validar este trabajo se realizaron experimentos con una amplia base de datos que incluye observaciones obtenidas mediante sensores inerciales en sujetos con Parkinson realizando seis actividades cotidianas. Se aplicó una división rigurosa entre datos de entrenamiento y prueba para evaluar el modelo a través de métricas como precisión, recall y F1-score. Asimismo, se analizaron diferentes configuraciones de la red y la capacidad de generalización del modelo empleando subconjuntos diversos de sujetos. Los resultados obtenidos fueron comparados con modelos reportados en la literatura, teniendo en cuenta limitaciones como el tamaño reducido de la muestra y la posible influencia de la ubicación de los sensores.
+El resto del artículo se estructura siguiendo el formato típico de trabajos de investigación, contemplando secciones de materiales y métodos, resultados y discusión, conclusiones, además de incluir las contribuciones de los autores y las referencias bibliográficas consultadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="200" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>SimulateIoT: Domain Specific Language to Design, Code Generation and Execute IoT Simulation Environments</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Inglés</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>The Internet of Things (IoT) is widely applied in several areas such as smart-cities, home environments, agriculture, industry, intelligent buildings, etc. [46]. Usually, these IoT environments require using hundreds of sensors and actuators shared throughout these areas which are generating a vast amount of data. Data must be suitably stored, analysed and published using Big Data or Stream Processing techniques. Big Data or Stream Processing techniques must be applied to conveniently store and analyse published data. Taking into account where data are processed and stored, the IoT environment architecture can be defined by several computing layers (Edge, Fog and Cloud computing (see Figure 1) [30]). Edge layer is defined closer to data generators, Fog layer resides on top of the edge and act as intermediary layer with limited storing and processing capabilities and Cloud layer is defined with full storing and processing capabilities. Thus, the development of IoT systems requires the management and integration of conveniently heterogeneous technologies such as devices, actuators, databases, communication protocols, stream processing engines, etc. As a consequence, in order to implement, deploy and test the IoT systems a high investment must be made in time, money and effort.
 Simulating IoT environments is one way to decrease this initial investment because the users can measure and dimension the artefacts needed to deploy and interconnect the systems. Thus, these artefacts can include several kinds of devices from sensors or actuators to NoSQL databases, messaging brokers or stream processor engines. However, although there are several simulation environments for wireless sensor networks (WSN), there is a lack of IoT simulator tools for designing IoT environments at a high level that enable modeling this kind of systems by using the domain concepts and relationships. In addition, there is a lack of IoT simulation tools that makes it possible to deploy the IoT system on multiple nodes in order to test the communications among the system's elements and where complex IoT components such as databases, complex event processing or message brokers can be suitable deployed and tested.
@@ -532,21 +605,20 @@
 The rest of the paper is structured as follows. In Section 2, we give an overview of existing IoT simulation approaches centered on both low level and high level IoT simulation environments. In Section 3, we present the SimulateIoT methodology. Section 4 describes SimulateIoT design and implementation phases including the SimulateIoT metamodel, the graphical editor and the model-to-text transformation developed. In Section 5 two case studies are presented. Finally, Section 6 elaborates on the limitations of the presented approach before Section 7 concludes the paper.</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>﻿The increasing importance of Internet of Things (IoT) technologies across domains such as smart cities, home environments, agriculture, and industry has generated a growing need for effective tools to develop, deploy, and test IoT systems. Developing and validating such systems in real-world settings often involves significant investments in hardware and software infrastructure, as well as considerable time and effort. To address these challenges, simulation environments have been proposed to model and reason about IoT systems before actual deployment. Prior approaches focus either on low-level simulation aspects—such as hardware details, sensor network behavior, and network protocols—or on higher-level abstractions emphasizing contextual modeling and system components.
-Model-driven development (MDD) has emerged as a promising paradigm to capture domain-specific concepts and relationships in IoT systems, facilitating system design through domain-specific languages and automated code generation. Existing IoT simulation frameworks and modeling tools, however, tend to focus on either detailed hardware/network simulation or on limited abstraction levels that lack integration of key IoT architectural layers such as Edge, Fog, and Cloud computing. Moreover, many solutions require advanced programming knowledge and lack user-friendly graphical interfaces to allow a broader range of users to design and analyze IoT scenarios effectively. These observations underscore the relevance of approaches that enable high-level, model-driven design and simulation of complex IoT environments with heterogeneous technology and communications, supporting various abstractions and easing the development and testing process.
-Despite the advances in IoT simulation and modeling, significant gaps remain in the existing body of work. Alwasel et al. (2020) [VERIFICAR] present simulators focused on big data analytics in cloud environments but do not provide comprehensive simulation frameworks for IoT systems at a high level of abstraction. Clemente et al. (2018) [VERIFICAR] address complex event processing but do not extend their approach to complete IoT environment simulation nor to automatic code generation for deployment. Papadopoulos et al. (2013) [VERIFICAR] offer experimental platforms for wireless sensor networks; however, their focus is restricted to hardware-level simulation without including Fog or Cloud computing concepts. Patel and Cassou (2015) [VERIFICAR] develop high-level IoT application tools but lack integrated graphical interfaces to simulate full architectures spanning different layers or to validate configurations effectively. Lastly, Mehdi et al. (2014) [VERIFICAR] propose discrete-event, multi-agent wireless sensor network simulators but do not provide abstractions for highly configurable nodes with publish-subscribe communication patterns nor container-based deployment. Consequently, there is a clear absence of a comprehensive and accessible approach that allows modeling, validating, automatically generating code, and deploying simulations of complex IoT environments incorporating Edge, Fog, and Cloud layers, while supporting advanced data stream and event processing, and catering to users with varying technical expertise.
-The central proposal of this work is SimulateIoT, a domain-specific language (DSL) accompanied by a set of model-driven development (MDD) tools designed to define complex IoT environment models at a high level of abstraction. This approach enables automatic generation of source code for microservices deployable within Docker containers and supports the execution of simulations via a distributed architecture that leverages MQTT-based communication alongside Fog and Cloud processing. The solution encompasses a comprehensive metamodel that incorporates key IoT elements such as sensors, actuators, Edge, Fog, and Cloud nodes, as well as publish-subscribe communication topics, synthetic and historical data generation capabilities, complex event processing engines, and rules for data analysis and notification.
-This approach addresses the identified gaps by providing an integrated framework that not only models and validates heterogeneous IoT systems spanning multiple architectural layers but also automates code generation and deployment, thereby reducing the need for specialized programming skills. By combining high-level abstractions with practical deployment mechanisms, SimulateIoT facilitates the design, simulation, and analysis of sophisticated IoT scenarios, making it accessible to users with diverse technical backgrounds and effectively bridging the limitations present in existing solutions.
-- Design of the SimulateIoT metamodel that conceptually represents IoT environments with support for Edge, Fog, and Cloud layers, sensors/actuators, data, and communication (Section III).
-- Definition of a graphical syntax to build models conforming to the metamodel using Eclipse GMF tools (Section IV.B).
-- Implementation of model-to-text transformations to automatically generate code, including microservices, MQTT brokers, NoSQL databases, and processing engines (Section IV.C).
-- Proposal of a deployment and execution environment based on Docker containers orchestrated with Docker Swarm to simulate large and heterogeneous IoT environments (Section IV.D).
-- Presentation of two relevant case studies—an intelligent university building and an agricultural environment—with full deployment and results analysis (Section V).
-- Discussion of limitations and future improvements, particularly regarding node mobility and advanced data generation patterns (Section VI).
-The validation of this work is conducted through two practical case studies implemented using the SimulateIoT environment. The first case involves the simulation of a smart building—specifically, a technology school—with multiple sensors and actuators distributed across different buildings, where Fog and Cloud nodes analyze data and generate control rules for heating systems. The second case models an agricultural environment comprised of sensors measuring parameters such as temperature, humidity, pH, and water pressure, along with actuators controlling irrigation, all managed by Fog and Cloud nodes equipped with real-time processing engines. Both cases demonstrate the design, automatic code generation, deployment of simulations in Docker containers, and real-time monitoring capabilities. These studies provide evidence for the scalability, expressiveness, and applicability of the proposed methodology and tools in diverse real-world IoT contexts.
-The remainder of the article is organized into sections covering the introduction and motivation, related work, the SimulateIoT methodology, design and implementation aspects including the metamodel, graphical syntax, and model-to-text transformations, deployment and execution, case studies, discussion of limitations and future work, followed by the conclusion and references.</t>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>﻿The Internet of Things (IoT) is increasingly applied across diverse domains such as smart cities, agriculture, industry, and home environments. Developing and deploying IoT projects requires significant investment in hardware and software components, including devices and various computing nodes spanning edge, fog, and cloud layers. Simulation environments have thus emerged as critical tools to model, test, and optimize IoT systems before actual implementation, helping reduce associated costs and development time. Existing IoT simulation solutions generally focus on either low-level aspects such as hardware and network details or higher-level abstractions. However, these approaches often lack comprehensive integration of IoT concepts across different architectural layers, as well as graphical tools for modeling, validation capabilities prior to simulation, or deployment frameworks oriented to microservice architectures.
+In the current state of the art, low-level simulators concentrate on network and hardware fidelity, supporting detailed sensor and communication modeling but requiring extensive technical expertise. Conversely, high-level approaches provide abstractions to facilitate system design but often omit key features such as complex event processing, publish-subscribe communication paradigms, or seamless code generation and deployment. Moreover, existing tools frequently do not support distributed architectures involving fog and cloud computing nodes or incorporate scalable deployment mechanisms based on containerization and orchestration. This landscape highlights the need for integrated methodologies and tools that combine expressive modeling, automated generation, and flexible deployment targeting heterogeneous IoT environments.
+Several existing works present notable limitations when contrasted with the comprehensive approach proposed in this research. Alwasel et al. (2020) [VERIFICAR] offer simulators aimed at Big Data analysis and cloud-based IoT, but these systems lack features such as graphical validation, deployment mechanisms, and the management of fog computing concepts and distributed architectures that are integral to the present approach. Cheong et al. (2005) [VERIFICAR] and Baldwin et al. (2004) [VERIFICAR] focus their simulations primarily on low-level network and sensor details without incorporating high-level modeling or intelligent components like Complex Event Processing (CEP) and Big Data support, thus limiting their applicability to holistic IoT environments. Mehdi et al. (2014) [VERIFICAR] provide capabilities to model and simulate Wireless Sensor Networks (WSN), yet they fall short of integrating Cloud/Fog computing or supporting publish-subscribe communication patterns within a unified model. Lastly, Clemente et al. (2018) [VERIFICAR] propose a domain-specific language for IoT environments but do not offer an integrated solution covering simulation, automatic code generation, deployment, and comprehensive analysis of complex IoT systems. These gaps across prior work underscore the absence of a modeling, validation, automatic generation, and container-based microservice deployment framework that the current research addresses for heterogeneous and distributed IoT environments.
+The proposed work introduces a comprehensive model-driven development (MDD) approach to address the identified gaps by enabling the complete definition of IoT simulations through a metamodel, graphical editor, and validation using OCL constraints. This approach leverages model-to-text transformations to automatically generate a deployable environment based on microservices contained within Docker containers. It integrates key IoT components such as sensors, actuators, fog and cloud nodes with publish-subscribe communication via MQTT, coupled with real-time data analysis through Complex Event Processing (CEP) and Event Stream Processing (ESP) engines, as well as data storage in NoSQL databases. This holistic methodology facilitates a high-level, technology-independent design that is seamlessly translated into operational simulation systems, effectively bridging the deficiencies of prior solutions lacking integrated modeling, validation, code generation, and scalable deployment in heterogeneous IoT environments.
+- A domain-specific language (DSL) metamodel specifically designed for IoT simulation, incorporating key concepts such as Edge, Fog, and Cloud nodes, sensors, actuators, topics, and processes (Sections III and IV).
+- A graphical editor based on Eclipse GMF for the visual creation and validation of IoT simulation models (Section IV-B).
+- Automated model-to-text transformation techniques that generate all necessary artifacts, including Java code, MQTT configuration, Docker containers, and deployment scripts (Section IV-C).
+- A deployment architecture founded on microservices packed into Docker containers and orchestrated via Docker Swarm, enabling scalable and flexible simulation environments (Section IV-D).
+- Demonstration and evaluation of the approach through two detailed case studies: a smart building scenario (School of Technology) and an agricultural environment (AgroTech), validating the expressiveness and practical utility of the system (Section V).
+- An analysis of performance attributes alongside a discussion of current limitations and potential future enhancements, such as mobility support and dynamic behavior modeling (Section VI).
+The validation of the proposed approach is supported through two comprehensive case studies. The first case study involves the simulation of a smart building environment with multiple nodes, temperature sensors, and actuators for heating control, incorporating Complex Event Processing (CEP) rules and distributed deployment. The second case study models an agricultural setting featuring sensors for humidity, pH, temperature, and irrigation actuators, managed via fog and cloud nodes with rule-based actuation and real-time monitoring capabilities. The simulation models are automatically transformed into executable code and deployed as Docker containers orchestrated by Docker Swarm. Monitoring and analysis are facilitated using tools such as MongoDB Compass and customized dashboards. These evaluations demonstrate key aspects of scalability, expressiveness, and adaptability while also informing discussions on current limitations and future enhancements.
+The remainder of the article is organized into sections that systematically cover the related work and state of the art, the SimulateIoT methodology for defining and executing simulations, detailed descriptions of the tool including the metamodel, graphical editor, and model transformations, deployment and execution using microservices and orchestration, comprehensive case studies demonstrating the approach, followed by discussions on limitations and future work, and concluding with references and appendices.</t>
         </is>
       </c>
     </row>

--- a/introducciones/comparacion_introducciones.xlsx
+++ b/introducciones/comparacion_introducciones.xlsx
@@ -564,17 +564,19 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>﻿El presente estudio se enmarca en la aplicación de inteligencia artificial y aprendizaje profundo para el monitoreo y evaluación de pacientes con enfermedad de Parkinson, centrándose específicamente en la clasificación de actividades de la vida diaria a partir de datos obtenidos mediante sensores inerciales. Esta área cobra relevancia debido a la amplia heterogeneidad y variabilidad de los síntomas motores en estos pacientes, lo que dificulta su seguimiento efectivo mediante métodos convencionales. En el campo, se observa un interés creciente en técnicas como el Análisis de Componentes Principales (PCA) para la reducción de dimensionalidad de datos y en el uso de modelos de Redes Neuronales Artificiales tipo Perceptrón Multicapa (MLP) para clasificar patrones motores, consolidando así la aplicación del aprendizaje profundo en la rehabilitación y monitoreo clínico.
-A pesar de los avances, los trabajos previos presentan limitaciones importantes, como la escasa capacidad de generalización de los modelos debido al bajo número de sujetos y a la falta de heterogeneidad en las muestras. También se destaca la posible influencia de la colocación de sensores sobre la calidad y consistencia de las señales capturadas, así como el desequilibrio en las bases de datos utilizadas, lo cual dificulta alcanzar resultados precisos y robustos en contextos reales. Estas deficiencias evidencian la necesidad de desarrollar métodos capaces de lograr alta precisión en escenarios variados y con datos desbalanceados, lo que fundamenta la investigación propuesta.
-En respuesta a estas limitaciones, este trabajo presenta el diseño y desarrollo de un modelo de Red Neuronal Artificial tipo Perceptrón Multicapa, combinado con la técnica de Análisis de Componentes Principales para reducir la dimensionalidad de la base de datos. Esta estrategia busca mejorar el desempeño del clasificador en la identificación automática de las actividades de la vida diaria en pacientes con enfermedad de Parkinson, gestionando eficazmente la complejidad y volumen de la información proveniente de los sensores. El modelo se entrena con datos de sensores inerciales, aplicando técnicas de preprocesamiento, normalización y codificación que permiten optimizar tanto la precisión como la eficiencia computacional. Esta solución resulta adecuada para su implementación en dispositivos con recursos limitados, ofreciendo un sistema robusto y generalizable para condiciones reales.
-Las contribuciones específicas de este trabajo son las siguientes:
-- Desarrollo de un modelo MLP entrenado con datos de PCA que clasifica con alta precisión seis actividades de la vida diaria (sección metodología y resultados).
-- Demostración de la efectividad de PCA para reducir dimensionalidad sin pérdida significativa de información, optimizando el entrenamiento de la RNA (sección materiales y métodos).
-- Evaluación detallada del desempeño de los modelos con diferentes divisiones de sujetos en entrenamiento y prueba, evidenciando la importancia de la representatividad de los datos para la generalización (sección resultados y discusión).
-- Análisis comparativo de parámetros y arquitecturas de red, mostrando la viabilidad de modelos con menos parámetros para dispositivos de bajo recurso (sección resultados).
-- Propuesta de aplicación futura para un sistema de apoyo al monitoreo clínico de pacientes con Parkinson basado en inteligencia artificial (conclusiones).
-Para validar este trabajo se realizaron experimentos con una amplia base de datos que incluye observaciones obtenidas mediante sensores inerciales en sujetos con Parkinson realizando seis actividades cotidianas. Se aplicó una división rigurosa entre datos de entrenamiento y prueba para evaluar el modelo a través de métricas como precisión, recall y F1-score. Asimismo, se analizaron diferentes configuraciones de la red y la capacidad de generalización del modelo empleando subconjuntos diversos de sujetos. Los resultados obtenidos fueron comparados con modelos reportados en la literatura, teniendo en cuenta limitaciones como el tamaño reducido de la muestra y la posible influencia de la ubicación de los sensores.
-El resto del artículo se estructura siguiendo el formato típico de trabajos de investigación, contemplando secciones de materiales y métodos, resultados y discusión, conclusiones, además de incluir las contribuciones de los autores y las referencias bibliográficas consultadas.</t>
+          <t>﻿El monitoreo de pacientes con Enfermedad de Parkinson (EP) representa un área de gran relevancia clínica debido a la complejidad y heterogeneidad de los síntomas motores característicos de esta patología. Los avances en sensores inerciales portátiles y técnicas de inteligencia artificial, particularmente las redes neuronales artificiales, han permitido desarrollar sistemas automáticos que facilitan la evaluación continua y objetiva de la función motora en estos pacientes. En este contexto, la combinación de sensores wearables con metodologías como el Análisis de Componentes Principales (PCA) y modelos de perceptrón multicapa (MLP) ha mostrado ser una estrategia efectiva para capturar y clasificar actividades de la vida diaria, contribuyendo así a un mejor seguimiento clínico y a la mejora en la calidad de la rehabilitación. Estos desarrollos se apoyan en un cuerpo de trabajo previo que ha explorado la aplicación de tecnologías similares en pacientes con EP y otros trastornos motores, consolidando un estado del arte que enfatiza la necesidad de soluciones precisas, adaptables y no invasivas para el monitoreo funcional en entornos reales.
+A pesar de los avances descritos en el territorio, persisten limitaciones importantes en el trabajo previo que motivan la presente investigación. Jung et al. (2020) destacan que los algoritmos desarrollados en entornos controlados enfrentan desafíos significativos para aplicarse eficazmente a datos obtenidos en condiciones naturales y no estructuradas, especialmente en poblaciones con patologías como la Enfermedad de Parkinson. Asimismo, Nguyen et al. (2018) señalan la ausencia de métodos robustos para la detección y segmentación automática de actividades complejas y no estructuradas de la vida diaria en pacientes con Parkinson, lo que limita la evaluación precisa y continua de su movilidad en entornos libres o simulados.
+Por otra parte, Pérez Sanpablo et al. (2021) evidencian las bajas precisiones, en torno al 60%, alcanzadas por técnicas clásicas de análisis discriminante para la clasificación de actividades en esta población, indicando la necesidad de enfoques más precisos y adaptados. Rast y Labruyère (2020) agregan que la heterogeneidad metodológica, la falta de estándares y la escasa evaluación de la usabilidad de los sistemas actuales dificultan la adopción clínica y el seguimiento efectivo. Finalmente, Rodríguez Montero et al. (2023) muestran que, aunque se han empleado redes neuronales para la clasificación de actividades de vida diaria en pacientes con EP, los resultados no alcanzan la precisión óptima y se podrían mejorar mediante técnicas avanzadas de selección de características y modelos profundos.
+Estos vacíos y limitaciones en el estado del arte justifican la necesidad de desarrollar y validar nuevas metodologías que permitan una clasificación más precisa, robusta y eficiente de las actividades en pacientes con EP, considerando bases de datos reales y desequilibradas, y sistemas que faciliten su aplicación clínica práctica.
+Como respuesta directa a estas limitaciones, el presente trabajo propone el uso de Redes Neuronales Artificiales multicapa diseñadas y entrenadas con señales inerciales que han sido previamente preprocesadas y reducidas dimensionalmente mediante Análisis de Componentes Principales (PCA). Esta combinación metodológica tiene sentido frente a las carencias identificadas porque permite una clasificación automática avanzada, alcanzando altas precisiones y superando los métodos clásicos de clasificación, como los análisis discriminantes, que mostraron resultados inferiores. Además, el enfoque se adapta eficazmente a bases de datos desbalanceadas y heterogéneas, como las que se encuentran en estudios con pacientes con Enfermedad de Parkinson, garantizando así un desempeño robusto y una mejor generalización para la identificación de actividades específicas de la vida diaria.
+Este enfoque aprovecha la versatilidad y capacidad de aprendizaje profundo de las redes neuronales para modelar patrones complejos en los datos recogidos en entornos naturales y no estructurados, abordando directamente los retos señalados en la detección y segmentación de actividades múltiples y variadas. Además, la reducción dimensional mediante PCA contribuye a la eficiencia y practicidad del sistema, facilitando su potencial implementación clínica para el seguimiento continuo y objetivo de pacientes con patologías motoras.
+- Desarrollo de un sistema basado en una red neuronal artificial de perceptrón multicapa (MLP) para la clasificación precisa de seis actividades de la vida diaria en pacientes con Enfermedad de Parkinson.  
+- Uso de técnicas de reducción dimensional mediante Análisis de Componentes Principales (PCA) para mejorar la eficiencia del modelo sin perder precisión.  
+- Evaluación exhaustiva del modelo mediante validación cruzada y comparación con otros clasificadores como análisis discriminante lineal y Naïve Bayes.  
+- Propuesta de configuraciones y recomendaciones para facilitar la aplicación práctica futura, incluyendo la reducción del número de sensores para mayor comodidad y menor costo.  
+- Implementación y codificación del sistema en Python, utilizando librerías especializadas que permiten la reproducibilidad y la extensión del desarrollo.
+La validación del trabajo se llevó a cabo mediante la utilización de una extensa base de datos que incluye 179,755 observaciones registradas por sensores inerciales ubicados en diferentes partes del cuerpo de pacientes con Enfermedad de Parkinson. Para respaldar las contribuciones propuestas, se aplicó una validación cruzada con particionamiento en 10 subconjuntos (10-fold), lo que permitió evaluar la robustez y capacidad generalizadora del modelo. Además, se comparó el desempeño de la red neuronal con seis clasificadores alternativos, analizando detalladamente la matriz de confusión y los patrones de error asociados a las diferentes actividades, lo que fortaleció la confianza en la efectividad y precisión de la propuesta para la clasificación automática de actividades de la vida diaria en esta población.
+El resto del documento se organiza en las siguientes secciones, donde se desarrollan de manera detallada la metodología empleada, los resultados obtenidos, la discusión de los hallazgos y las conclusiones del estudio.</t>
         </is>
       </c>
     </row>

--- a/introducciones/comparacion_introducciones.xlsx
+++ b/introducciones/comparacion_introducciones.xlsx
@@ -609,18 +609,19 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>﻿The Internet of Things (IoT) is increasingly applied across diverse domains such as smart cities, agriculture, industry, and home environments. Developing and deploying IoT projects requires significant investment in hardware and software components, including devices and various computing nodes spanning edge, fog, and cloud layers. Simulation environments have thus emerged as critical tools to model, test, and optimize IoT systems before actual implementation, helping reduce associated costs and development time. Existing IoT simulation solutions generally focus on either low-level aspects such as hardware and network details or higher-level abstractions. However, these approaches often lack comprehensive integration of IoT concepts across different architectural layers, as well as graphical tools for modeling, validation capabilities prior to simulation, or deployment frameworks oriented to microservice architectures.
-In the current state of the art, low-level simulators concentrate on network and hardware fidelity, supporting detailed sensor and communication modeling but requiring extensive technical expertise. Conversely, high-level approaches provide abstractions to facilitate system design but often omit key features such as complex event processing, publish-subscribe communication paradigms, or seamless code generation and deployment. Moreover, existing tools frequently do not support distributed architectures involving fog and cloud computing nodes or incorporate scalable deployment mechanisms based on containerization and orchestration. This landscape highlights the need for integrated methodologies and tools that combine expressive modeling, automated generation, and flexible deployment targeting heterogeneous IoT environments.
-Several existing works present notable limitations when contrasted with the comprehensive approach proposed in this research. Alwasel et al. (2020) [VERIFICAR] offer simulators aimed at Big Data analysis and cloud-based IoT, but these systems lack features such as graphical validation, deployment mechanisms, and the management of fog computing concepts and distributed architectures that are integral to the present approach. Cheong et al. (2005) [VERIFICAR] and Baldwin et al. (2004) [VERIFICAR] focus their simulations primarily on low-level network and sensor details without incorporating high-level modeling or intelligent components like Complex Event Processing (CEP) and Big Data support, thus limiting their applicability to holistic IoT environments. Mehdi et al. (2014) [VERIFICAR] provide capabilities to model and simulate Wireless Sensor Networks (WSN), yet they fall short of integrating Cloud/Fog computing or supporting publish-subscribe communication patterns within a unified model. Lastly, Clemente et al. (2018) [VERIFICAR] propose a domain-specific language for IoT environments but do not offer an integrated solution covering simulation, automatic code generation, deployment, and comprehensive analysis of complex IoT systems. These gaps across prior work underscore the absence of a modeling, validation, automatic generation, and container-based microservice deployment framework that the current research addresses for heterogeneous and distributed IoT environments.
-The proposed work introduces a comprehensive model-driven development (MDD) approach to address the identified gaps by enabling the complete definition of IoT simulations through a metamodel, graphical editor, and validation using OCL constraints. This approach leverages model-to-text transformations to automatically generate a deployable environment based on microservices contained within Docker containers. It integrates key IoT components such as sensors, actuators, fog and cloud nodes with publish-subscribe communication via MQTT, coupled with real-time data analysis through Complex Event Processing (CEP) and Event Stream Processing (ESP) engines, as well as data storage in NoSQL databases. This holistic methodology facilitates a high-level, technology-independent design that is seamlessly translated into operational simulation systems, effectively bridging the deficiencies of prior solutions lacking integrated modeling, validation, code generation, and scalable deployment in heterogeneous IoT environments.
-- A domain-specific language (DSL) metamodel specifically designed for IoT simulation, incorporating key concepts such as Edge, Fog, and Cloud nodes, sensors, actuators, topics, and processes (Sections III and IV).
-- A graphical editor based on Eclipse GMF for the visual creation and validation of IoT simulation models (Section IV-B).
-- Automated model-to-text transformation techniques that generate all necessary artifacts, including Java code, MQTT configuration, Docker containers, and deployment scripts (Section IV-C).
-- A deployment architecture founded on microservices packed into Docker containers and orchestrated via Docker Swarm, enabling scalable and flexible simulation environments (Section IV-D).
-- Demonstration and evaluation of the approach through two detailed case studies: a smart building scenario (School of Technology) and an agricultural environment (AgroTech), validating the expressiveness and practical utility of the system (Section V).
-- An analysis of performance attributes alongside a discussion of current limitations and potential future enhancements, such as mobility support and dynamic behavior modeling (Section VI).
-The validation of the proposed approach is supported through two comprehensive case studies. The first case study involves the simulation of a smart building environment with multiple nodes, temperature sensors, and actuators for heating control, incorporating Complex Event Processing (CEP) rules and distributed deployment. The second case study models an agricultural setting featuring sensors for humidity, pH, temperature, and irrigation actuators, managed via fog and cloud nodes with rule-based actuation and real-time monitoring capabilities. The simulation models are automatically transformed into executable code and deployed as Docker containers orchestrated by Docker Swarm. Monitoring and analysis are facilitated using tools such as MongoDB Compass and customized dashboards. These evaluations demonstrate key aspects of scalability, expressiveness, and adaptability while also informing discussions on current limitations and future enhancements.
-The remainder of the article is organized into sections that systematically cover the related work and state of the art, the SimulateIoT methodology for defining and executing simulations, detailed descriptions of the tool including the metamodel, graphical editor, and model transformations, deployment and execution using microservices and orchestration, comprehensive case studies demonstrating the approach, followed by discussions on limitations and future work, and concluding with references and appendices.</t>
+          <t>﻿The Internet of Things (IoT) has become increasingly prevalent in various domains such as smart cities, agriculture, industry, and home environments. These applications demand the integration of heterogeneous devices and technologies across multiple layers including Edge, Fog, and Cloud computing. However, developing, deploying, and testing such complex IoT systems typically require significant investments in physical hardware and software components, making the process costly and time-consuming. Simulation environments play a crucial role in addressing these challenges by enabling the modeling and reasoning of IoT systems before their physical implementation.
+Existing simulation approaches for IoT tend to focus either on low-level network and hardware aspects or on high-level abstract definitions of IoT contexts. Low-level simulators emphasize detailed hardware and network modeling but often lack support for higher-level IoT concepts and scalability. Conversely, some high-level simulation tools allow describing IoT environments but do not facilitate integration across computational layers or easy deployment. Moreover, many current solutions do not provide mechanisms for automatic code generation nor seamless communication through publish-subscribe protocols, limiting their practical usability and flexibility. Accordingly, there is a clear need for tools that can enable the design, generation, and deployment of complex IoT simulations through high-level models, promoting integration of Edge, Fog, and Cloud layers alongside scalable communication and data processing capabilities.
+Several works have addressed aspects of IoT simulation and modeling, yet important limitations remain. Alwasel et al. (2020) [VERIFICAR] present simulators for big data analysis in cloud environments, but these tools do not support modeling the specific simulation requirements of IoT systems, such as handling different abstraction levels and dynamic behavior. Levis et al. (2003) introduce Tossim, a low-level simulator tailored to sensor networks under TinyOS, yet it lacks capabilities for simulating Edge computing or high-level system abstractions necessary for broader IoT scenarios. Ruppen et al. (2015) [VERIFICAR] propose a model-driven approach for the Web of Things but do not encompass domain-specific aspects of simulation or storage relevant for IoT environments. Similarly, Mehdi et al. (2014) with CupCarbon provide graphical design and simulation of sensor networks but do not support storage modeling nor the complex publish-subscribe communication based on message brokers that are critical for scalable IoT systems. Zeng et al. (2017) with IoTSim simulate IoT applications in cloud contexts; however, the framework requires complex configurations, lacks a high-level graphical interface for complete system modeling, and does not incorporate prior validation mechanisms. In sum, these prior approaches do not offer an integrated tool capable of high-level modeling combined with automatic code generation for deployment in distributed architectures using Docker services, nor do they fully support layered Edge, Fog, and Cloud computing, complete with real-time analysis and native publish-subscribe communication.
+This work proposes SimulateIoT, a high-level Domain Specific Language (DSL) grounded in model-driven development to address the identified shortcomings in existing IoT simulation tools. By providing a metamodel that explicitly represents sensors, actuators, various node types, and publish-subscribe communication protocols alongside complex event processing rules, SimulateIoT enables comprehensive and scalable modeling of IoT simulation environments across Edge, Fog, and Cloud layers. This approach allows for automatic generation of deployable microservices as Docker containers, including MQTT brokers, NoSQL databases, and event-processing engines, thereby bridging the gap between high-level modeling and practical system deployment.
+The SimulateIoT framework facilitates the design and execution of IoT simulations without requiring users to engage in low-level coding or intricate configuration, which addresses the complexity and fragmentation observed in prior works. By enabling deployment on physical or virtual machines, it supports realistic experimentation and analysis, making it possible to dynamically enact scenarios and monitor behaviors within distributed IoT architectures. This integrated toolchain thus offers a coherent solution fulfilling the need for high-level, automated, and layered IoT system simulation with native support for scalable communication mechanisms.
+- Definition of a metamodel and Domain Specific Language (DSL) to model IoT simulation environments, including Edge, Fog, Cloud nodes, sensors, actuators, communication protocols, and complex event processing (described in Sections III and IV).
+- Tools for visual model editing with automatic validation based on Object Constraint Language (OCL) (Section IV.B).
+- Automatic code generation for deployment of microservices as Docker containers, MQTT brokers, NoSQL databases, and Complex Event Processing (CEP) engines (Sections IV.C and IV.D).
+- Orchestrated deployment and execution of the simulated system using Docker Swarm technology, with real-time monitoring capabilities (Section IV.D).
+- Evaluation of the approach through two case studies—one simulating a smart building and another simulating an agricultural environment—demonstrating expressiveness and scalability (Section V).
+- Discussion of limitations and potential future enhancements, including node mobility and dynamic discovery mechanisms (Section VI).
+The validation of this work is grounded in two comprehensive real-world case studies that demonstrate the expressiveness and applicability of the proposed approach. The first case study simulates a smart building environment, specifically the School of Technology, incorporating Fog and Cloud nodes, various sensors and actuators, MongoDB databases, and Complex Event Processing (CEP) engines, with communication managed via MQTT protocols for real-time data analysis and control. The second case study models an agricultural environment with distributed sensors monitoring temperature, humidity, pH, and water pressure, along with actuators for irrigation management, leveraging Fog/Cloud nodes, NoSQL databases, and stream processing engines. Both case studies involve the automatic generation and deployment of the simulation components as Docker containers, enabling realistic execution, real-time monitoring, and dynamic interaction among system elements. This approach provides rigorous validation of the framework’s capability to model, generate, deploy, and analyze scalable IoT simulation systems across multiple layers of computation and communication.
+The remainder of the article is organized into sections that provide an introduction and context of the problem, describe the SimulateIoT methodology and approach, detail the metamodel, graphical editor, model transformations, and deployment process, present two case studies including their models, deployment, and results, discuss limitations and future work, and conclude with final remarks.</t>
         </is>
       </c>
     </row>

--- a/introducciones/comparacion_introducciones.xlsx
+++ b/introducciones/comparacion_introducciones.xlsx
@@ -609,19 +609,20 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>﻿The Internet of Things (IoT) has become increasingly prevalent in various domains such as smart cities, agriculture, industry, and home environments. These applications demand the integration of heterogeneous devices and technologies across multiple layers including Edge, Fog, and Cloud computing. However, developing, deploying, and testing such complex IoT systems typically require significant investments in physical hardware and software components, making the process costly and time-consuming. Simulation environments play a crucial role in addressing these challenges by enabling the modeling and reasoning of IoT systems before their physical implementation.
-Existing simulation approaches for IoT tend to focus either on low-level network and hardware aspects or on high-level abstract definitions of IoT contexts. Low-level simulators emphasize detailed hardware and network modeling but often lack support for higher-level IoT concepts and scalability. Conversely, some high-level simulation tools allow describing IoT environments but do not facilitate integration across computational layers or easy deployment. Moreover, many current solutions do not provide mechanisms for automatic code generation nor seamless communication through publish-subscribe protocols, limiting their practical usability and flexibility. Accordingly, there is a clear need for tools that can enable the design, generation, and deployment of complex IoT simulations through high-level models, promoting integration of Edge, Fog, and Cloud layers alongside scalable communication and data processing capabilities.
-Several works have addressed aspects of IoT simulation and modeling, yet important limitations remain. Alwasel et al. (2020) [VERIFICAR] present simulators for big data analysis in cloud environments, but these tools do not support modeling the specific simulation requirements of IoT systems, such as handling different abstraction levels and dynamic behavior. Levis et al. (2003) introduce Tossim, a low-level simulator tailored to sensor networks under TinyOS, yet it lacks capabilities for simulating Edge computing or high-level system abstractions necessary for broader IoT scenarios. Ruppen et al. (2015) [VERIFICAR] propose a model-driven approach for the Web of Things but do not encompass domain-specific aspects of simulation or storage relevant for IoT environments. Similarly, Mehdi et al. (2014) with CupCarbon provide graphical design and simulation of sensor networks but do not support storage modeling nor the complex publish-subscribe communication based on message brokers that are critical for scalable IoT systems. Zeng et al. (2017) with IoTSim simulate IoT applications in cloud contexts; however, the framework requires complex configurations, lacks a high-level graphical interface for complete system modeling, and does not incorporate prior validation mechanisms. In sum, these prior approaches do not offer an integrated tool capable of high-level modeling combined with automatic code generation for deployment in distributed architectures using Docker services, nor do they fully support layered Edge, Fog, and Cloud computing, complete with real-time analysis and native publish-subscribe communication.
-This work proposes SimulateIoT, a high-level Domain Specific Language (DSL) grounded in model-driven development to address the identified shortcomings in existing IoT simulation tools. By providing a metamodel that explicitly represents sensors, actuators, various node types, and publish-subscribe communication protocols alongside complex event processing rules, SimulateIoT enables comprehensive and scalable modeling of IoT simulation environments across Edge, Fog, and Cloud layers. This approach allows for automatic generation of deployable microservices as Docker containers, including MQTT brokers, NoSQL databases, and event-processing engines, thereby bridging the gap between high-level modeling and practical system deployment.
-The SimulateIoT framework facilitates the design and execution of IoT simulations without requiring users to engage in low-level coding or intricate configuration, which addresses the complexity and fragmentation observed in prior works. By enabling deployment on physical or virtual machines, it supports realistic experimentation and analysis, making it possible to dynamically enact scenarios and monitor behaviors within distributed IoT architectures. This integrated toolchain thus offers a coherent solution fulfilling the need for high-level, automated, and layered IoT system simulation with native support for scalable communication mechanisms.
-- Definition of a metamodel and Domain Specific Language (DSL) to model IoT simulation environments, including Edge, Fog, Cloud nodes, sensors, actuators, communication protocols, and complex event processing (described in Sections III and IV).
-- Tools for visual model editing with automatic validation based on Object Constraint Language (OCL) (Section IV.B).
-- Automatic code generation for deployment of microservices as Docker containers, MQTT brokers, NoSQL databases, and Complex Event Processing (CEP) engines (Sections IV.C and IV.D).
-- Orchestrated deployment and execution of the simulated system using Docker Swarm technology, with real-time monitoring capabilities (Section IV.D).
-- Evaluation of the approach through two case studies—one simulating a smart building and another simulating an agricultural environment—demonstrating expressiveness and scalability (Section V).
-- Discussion of limitations and potential future enhancements, including node mobility and dynamic discovery mechanisms (Section VI).
-The validation of this work is grounded in two comprehensive real-world case studies that demonstrate the expressiveness and applicability of the proposed approach. The first case study simulates a smart building environment, specifically the School of Technology, incorporating Fog and Cloud nodes, various sensors and actuators, MongoDB databases, and Complex Event Processing (CEP) engines, with communication managed via MQTT protocols for real-time data analysis and control. The second case study models an agricultural environment with distributed sensors monitoring temperature, humidity, pH, and water pressure, along with actuators for irrigation management, leveraging Fog/Cloud nodes, NoSQL databases, and stream processing engines. Both case studies involve the automatic generation and deployment of the simulation components as Docker containers, enabling realistic execution, real-time monitoring, and dynamic interaction among system elements. This approach provides rigorous validation of the framework’s capability to model, generate, deploy, and analyze scalable IoT simulation systems across multiple layers of computation and communication.
-The remainder of the article is organized into sections that provide an introduction and context of the problem, describe the SimulateIoT methodology and approach, detail the metamodel, graphical editor, model transformations, and deployment process, present two case studies including their models, deployment, and results, discuss limitations and future work, and conclude with final remarks.</t>
+          <t>﻿The Internet of Things (IoT) is increasingly applied across various domains such as smart cities, smart homes, agriculture, and industrial environments. However, developing, deploying, and testing IoT projects require significant investments in hardware components like devices, fog nodes, cloud nodes, and analytics infrastructure, as well as substantial software development efforts. To mitigate these costs, simulation environments for IoT systems are essential as they facilitate system modeling, reasoning, and optimization prior to actual deployment.
+Existing IoT simulation environments predominantly focus on low-level aspects such as network protocols, sensor hardware, and motes, demanding advanced technical knowledge and programming skills from users. These tools often lack high-level abstractions for IoT concepts, such as Edge, Fog, and Cloud layers, and do not provide intuitive modeling or deployment mechanisms. Therefore, there is a pressing need for approaches that enable the design and execution of complex IoT simulations using domain-specific abstractions — including sensors, actuators, heterogeneous nodes, publish-subscribe communication, microservices, and containerization technologies — all within a user-friendly model-driven development framework.
+Several existing approaches have addressed aspects of IoT simulation but exhibit notable limitations that motivate further research. Alwasel et al. (2020) [VERIFICAR] simulate Big Data and software-defined networks in cloud environments but lack graphical interfaces and validation mechanisms for pre-configuration of IoT simulation environments. Levis et al. (2003) with Tossim focus on low-level simulation of TinyOS nodes without defining IoT communication patterns or modeling high-level processes, limiting the scope of IoT system representation. Mehdi et al. (2014) propose CupCarbon, which allows graphical simulation of IoT contexts but does not support modeling of storage or complex protocols such as publish/subscribe. Patel and Cassou (2015) offer IoTSuite to facilitate IoT application development, yet it does not encompass simulation capabilities nor modeling of storage and complex processing. Finally, Zeng et al. (2017) present IOTSim, a cloud IoT application simulator focused on big data processing, but without tools for high-level graphical modeling of entire IoT architectures.
+In summary, these works generally lack a comprehensive high-level domain-specific language with validation support, comprehensive modeling across the entire IoT architecture layers (Edge, Fog, Cloud), integrated support for publish-subscribe communication protocols, and deployment mechanisms leveraging containerized microservices. These gaps highlight the need for solutions that unify high-level modeling, validation, flexible communication abstractions, and realistic deployment strategies in IoT simulation.
+The central proposal of this work is a model-driven development approach to define, generate code for, and deploy IoT simulations. This approach is based on a domain-specific metamodel named SimulateIoT, which provides high-level abstractions representing sensors, actuators, and heterogeneous nodes across Edge, Fog, and Cloud layers. A graphical concrete syntax facilitates intuitive visual modeling, while Object Constraint Language (OCL) rules ensure model validation. From these validated models, model-to-text transformations automatically generate all necessary components, including microservices, MQTT brokers, NoSQL databases, complex event processing engines, and Docker containers for deployment.
+This comprehensive framework explicitly addresses the gaps found in prior work by unifying the full IoT architectural stack within a single, validated modeling language that supports publish-subscribe communication patterns and leverages containerized microservice deployment. By doing so, it enables users to efficiently design complex IoT simulation environments and execute them realistically without manual coding, thus overcoming limitations related to low-level focus, lack of high-level modeling support, and inadequate deployment automation.
+- Development of a comprehensive metamodel for IoT simulation that encompasses devices, nodes, communication protocols, storage, and processing capabilities (Sections III and IV).
+- Creation of a graphical concrete syntax that enables the design of simulation models conforming to the metamodel and supports OCL-based validation to ensure model correctness (Section IV-B).
+- Implementation of a model-to-text transformation workflow that automates the generation of all required code and deployment artefacts for the simulation environment (Section IV-C).
+- Integration with industrial technologies, including Docker containers, MQTT communication brokers, and complex event processing engines such as Esper and WSO2, facilitating realistic simulation and seamless deployment (Section IV-D).
+- Presentation of two detailed case studies—one in a smart building environment and another in an agricultural setting—that demonstrate the expressiveness and applicability of the proposed approach (Section V).
+- Development and deployment of a fully operational simulation platform featuring monitoring and real-time data analysis capabilities, allowing users to observe and analyze system behavior during execution (Sections V and VI).
+The validation of this work is conducted through two comprehensive case studies situated in distinct IoT domains: a smart building environment and an agricultural setting. These case studies demonstrate the modeling, code generation, deployment, and execution phases using Docker technology, showcasing the realistic simulation of complex IoT systems composed of various sensors, actuators, and heterogeneous nodes spanning Edge, Fog, and Cloud layers. The evaluation highlights the system’s capability for real-time data analysis, integrated monitoring, event management, and rule-based actions, thereby substantiating the expressiveness and practical applicability of the proposed model-driven development approach.
+The remainder of the article is organized into clearly differentiated main sections that guide the reader from the motivation behind the work through related research, the proposed SimulateIoT methodology, the design and implementation of supporting tools, detailed case studies focused on smart building and agricultural environments, and culminating with discussions on limitations, target users, and technologies, followed by conclusions and future work. This structured organization facilitates a comprehensive understanding of the development and application of the presented IoT simulation framework.</t>
         </is>
       </c>
     </row>

--- a/introducciones/comparacion_introducciones.xlsx
+++ b/introducciones/comparacion_introducciones.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -491,36 +491,107 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>﻿El área de trabajo se centra en la transducción de secuencias aplicada a tareas de traducción automática, un campo en el que los modelos tradicionales han empleado principalmente redes neuronales recurrentes y convolucionales complementadas con mecanismos de atención para mejorar la calidad de las traducciones. Estos métodos han tenido un papel destacado y han permitido avances significativos en el rendimiento de los sistemas, pero enfrentan importantes retos relacionados con la paralelización y el manejo de dependencias a largo plazo dentro de las secuencias, aspectos claves para la eficiencia y precisión de los modelos.
-La relevancia de este ámbito radica en la necesidad creciente de mejorar tanto la calidad como la eficiencia del entrenamiento de modelos de traducción automática, lo cual tiene un impacto directo en el procesamiento de grandes volúmenes de datos y en la capacidad de generalización de las soluciones implementadas. Los resultados previos y las motivaciones que sustentan este trabajo evidencian que, aunque los enfoques existentes han sido efectivos, se requiere explorar nuevas arquitecturas capaces de superar las limitaciones inherentes a la dependencia de las redes recurrentes y convolucionales, especialmente en lo que respecta a la paralelización y la gestión eficiente de relaciones a largo plazo en los datos secuenciales.
-A pesar de los avances significativos en modelos de traducción automática basados en arquitecturas recurrentes, persisten limitaciones importantes que justifican la propuesta de nuevas soluciones. Bahdanau et al. (2014) introducen un modelo encoder-decoder con mecanismo de atención suave que supera la restricción de codificar la oración completa en un vector de tamaño fijo. Sin embargo, su dependencia de arquitecturas recurrentes limita la paralelización y la eficiencia computacional, constituyendo una barrera para el entrenamiento rápido y escalable.
-Por otro lado, Sutskever et al. (2014) presentan un modelo de secuencia a secuencia basado en LSTM profundo que mejora el rendimiento, en parte, mediante la reversión del orden de las palabras en la secuencia de entrada. No obstante, este enfoque también depende de redes recurrentes, lo que dificulta la paralelización y el manejo eficiente de secuencias muy largas. En conjunto, estos trabajos comparten la limitación de basarse en modelos recurrentes para el procesamiento de secuencias, lo que reduce la capacidad de escalado y paralelización, problemas que el Transformer propone superar mediante un diseño exclusivo basado en mecanismos de atención.
-La propuesta central de este trabajo es el Transformer, una arquitectura de modelo de secuencia a secuencia que utiliza exclusivamente mecanismos de atención multi-cabeza para codificar y decodificar las secuencias, eliminando por completo la recurrencia y las convoluciones. Este enfoque tiene sentido frente a las limitaciones identificadas en los modelos recurrentes, ya que permite una mayor paralelización durante el entrenamiento y una gestión más eficiente de las dependencias a largo plazo en las secuencias, aspectos críticos que los modelos previos no podían optimizar adecuadamente debido a su naturaleza secuencial y dependiente.
-Al basarse únicamente en la atención, el Transformer logra conectar directamente todas las posiciones de entrada y salida, lo que facilita la captura de relaciones de largo alcance y mejora la escalabilidad computacional, superando así las barreras de paralelización y eficiencia impuestas por las arquitecturas recurrentes tradicionales. De esta forma, este modelo representa una innovación significativa al ofrecer una solución más rápida y efectiva para la transducción de secuencias en tareas como la traducción automática.
-- Desarrollo completo del Transformer basado exclusivamente en mecanismos de atención, sin recurrencia ni convoluciones, con una arquitectura detallada que permite mejorar la paralelización y el manejo de dependencias largas (sección 3).
-- Presentación y justificación de mecanismos de atención escalada y multi-cabeza, que permiten la atención a diferentes espacios de representación de manera simultánea.
-- Demostración de la eficiencia computacional y paralelización lograda por el modelo, comparada con arquitecturas recurrentes y convolucionales previas, evidenciada en análisis comparativo de complejidad y rendimiento (Tablas 1 y 2).
-- Presentación de resultados de estado del arte en las tareas de traducción automática inglés-alemán e inglés-francés que superan a modelos previos (sección 6).
-- Evaluación adicional del modelo en tareas de análisis sintáctico de parsing de constituyentes, mostrando la capacidad de generalización del Transformer a otras tareas de procesamiento del lenguaje (sección 6.3).
-- Publicación del código abierto utilizado para el entrenamiento y evaluación, promoviendo la reproducibilidad y extensión futura del trabajo.
-Cada una de estas contribuciones está desarrollada en las secciones específicas mencionadas del documento.
-El trabajo se valida mediante una serie de experimentos exhaustivos en tareas de traducción automática utilizando los conjuntos de datos WMT 2014 para los pares de idiomas inglés-alemán e inglés-francés, en los cuales se compara el rendimiento y la eficiencia del modelo propuesto frente a arquitecturas recurrentes y convolucionales previas. Además, se realiza una evaluación en tareas de análisis sintáctico, específicamente en parsing de constituyentes, para demostrar la capacidad del modelo para generalizar a otros ámbitos del procesamiento del lenguaje natural. Estos experimentos se complementan con análisis de variaciones del modelo y comparaciones detalladas que respaldan la solidez y versatilidad de la propuesta.
-El resto del artículo se organiza en secciones que abarcan la arquitectura del modelo, la justificación y comparación de los mecanismos de atención utilizados, los detalles del entrenamiento, los resultados y análisis de las experimentaciones realizadas, así como las conclusiones y las referencias bibliográficas. Esta estructura facilita una comprensión progresiva y detallada del desarrollo y la validación del modelo propuesto.</t>
+          <t>﻿The field of sequence modeling and transduction has traditionally been dominated by recurrent neural networks (RNNs) and their variants, such as long short-term memory (LSTM) and gated recurrent units (GRU). These models have been widely applied to problems like language modeling and machine translation, due to their ability to process sequences of arbitrary length. However, the inherently sequential nature of RNNs limits parallelization during training and presents difficulties when modeling long-range dependencies within sequences. To address these issues, attention mechanisms have been incorporated into recurrent models, enabling them to capture dependencies between distant positions in input and output sequences more effectively. Despite these advances, attention is commonly used in conjunction with recurrence rather than replacing it.
+This work situates itself within this context by exploring a model architecture that entirely removes the recurrent components and relies solely on attention mechanisms to capture global dependencies. By doing so, it aims to overcome the computational and modeling constraints imposed by recurrent structures, offering both improved parallelization and potentially enhanced performance in sequence transduction tasks.
+Bahdanau et al. (2014) introduced an encoder-decoder model with an attention mechanism that addresses the limitation of encoding an entire input sentence into a single fixed-length vector. However, their approach still relies on recurrent neural networks (RNNs) and thus does not remove the inherent sequential computation that restricts training parallelism and efficiency. Similarly, Sutskever et al. (2014) presented deep LSTM models for sequence-to-sequence learning that achieve improved translation performance, but still depend on fixed vector representations and face challenges with long sentences and complex dependencies. Both these influential works do not fully eliminate recurrence, which limits their ability to fully parallelize training and effectively model long-range dependencies. Therefore, there remains a need for a model that completely removes the strict dependency on RNNs and convolutions, employing only attention mechanisms to enable more efficient parallel processing and better handling of global dependencies in sequence transduction.
+The central proposal of this work is the Transformer, a novel encoder-decoder architecture that entirely replaces recurrent layers with multi-head self-attention mechanisms and position-wise feed-forward networks to capture global dependencies within sequences. By relying solely on attention, the Transformer eliminates the sequential computation inherent in recurrent architectures, enabling significantly more parallelization during training. Additionally, the model uses sinusoidal positional encodings to inject information about the order of tokens in the sequence, which addresses the absence of recurrence or convolutional structure. This design not only facilitates highly parallel and efficient training but also achieves state-of-the-art performance in sequence transduction tasks like machine translation, directly addressing the limitations found in prior approaches.
+- Introduction of the Transformer, the first sequence transduction model based entirely on attention mechanisms without recurrence or convolution (Section 3).
+- Implementation of multi-head attention that allows the model to jointly attend to information from different representation subspaces at different positions (Section 3.2).
+- Proposal and effective use of sinusoidal positional encodings to provide information about the relative or absolute position of tokens in a sequence (Section 3.5).
+- Empirical demonstration that the Transformer outperforms previous state-of-the-art models in English-to-German and English-to-French translation tasks at a fraction of the computational training cost (Section 6.1).
+- Additional evaluation showing that the Transformer generalizes well to other tasks such as English constituency parsing (Section 6.3).
+The validation of this work is conducted through extensive empirical experiments on large-scale machine translation benchmarks, specifically the WMT 2014 English-to-German and English-to-French datasets. The model is trained using high-performance GPUs to assess its efficiency and scalability. Performance is evaluated on standardized test sets using the BLEU metric, enabling direct comparison with prior state-of-the-art methods such as recurrent and convolutional neural network models and their ensembles. Additionally, the model is tested on other natural language processing tasks, like English constituency parsing, to demonstrate its generalization capabilities. These experiments collectively support the effectiveness and advantages of the proposed Transformer architecture.
+The rest of the article is organized into sections that first provide the context and related work, followed by a detailed description of the model architecture including attention mechanisms and feed-forward networks. Subsequent sections cover the datasets and training procedures used, present experimental results and analyses, and conclude with discussions on future research directions.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="200" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>BERT: Pre-training of Deep Bidirectional Transformers for Language Understanding</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Language model pre-training has been shown to be effective for improving many natural language processing tasks (Dai and Le, 2015; Peters et al., 2018a; Radford et al., 2018; Howard and Ruder, 2018). These include sentence-level tasks such as natural language inference (Bowman et al., 2015; Williams et al., 2018) and paraphrasing (Dolan and Brockett, 2005), which aim to predict the relationships between sentences by analyzing them holistically, as well as token-level tasks such as named entity recognition and question answering, where models are required to produce fine-grained output at the token level (Tjong Kim Sang and De Meulder, 2003; Rajpurkar et al., 2016).
+There are two existing strategies for applying pre-trained language representations to downstream tasks: feature-based and fine-tuning. The feature-based approach, such as ELMo (Peters et al., 2018a), uses task-specific architectures that include the pre-trained representations as additional features. The fine-tuning approach, such as the Generative Pre-trained Transformer (OpenAI GPT) (Radford et al., 2018), introduces minimal task-specific parameters, and is trained on the downstream tasks by simply fine-tuning all pre-trained parameters. The two approaches share the same objective function during pre-training, where they use unidirectional language models to learn general language representations.
+We argue that current techniques restrict the power of the pre-trained representations, especially for the fine-tuning approaches. The major limitation is that standard language models are unidirectional, and this limits the choice of architectures that can be used during pre-training. For example, in OpenAI GPT, the authors use a left-to-right architecture, where every token can only attend to previous tokens in the self-attention layers of the Transformer (Vaswani et al., 2017). Such restrictions are sub-optimal for sentence-level tasks, and could be very harmful when applying fine-tuning based approaches to token-level tasks such as question answering, where it is crucial to incorporate context from both directions.
+In this paper, we improve the fine-tuning based approaches by proposing BERT: Bidirectional Encoder Representations from Transformers. BERT alleviates the previously mentioned unidirectionality constraint by using a "masked language model" (MLM) pre-training objective, inspired by the Cloze task (Taylor, 1953). The masked language model randomly masks some of the tokens from the input, and the objective is to predict the original vocabulary id of the masked word based only on its context. Unlike left-to-right language model pre-training, the MLM objective enables the representation to fuse the left and the right context, which allows us to pre-train a deep bidirectional Transformer. In addition to the masked language model, we also use a "next sentence prediction" task that jointly pre-trains text-pair representations. The contributions of our paper are as follows:
+- We demonstrate the importance of bidirectional pre-training for language representations. Unlike Radford et al. (2018), which uses unidirectional language models for pre-training, BERT uses masked language models to enable pre-trained deep bidirectional representations. This is also in contrast to Peters et al. (2018a), which uses a shallow concatenation of independently trained left-to-right and right-to-left LMs.
+- We show that pre-trained representations reduce the need for many heavily-engineered task-specific architectures. BERT is the first fine-tuning based representation model that achieves state-of-the-art performance on a large suite of sentence-level and token-level tasks, outperforming many task-specific architectures.
+- BERT advances the state of the art for eleven NLP tasks. The code and pre-trained models are available at https://github.com/google-research/bert.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>﻿Recent advances in natural language processing (NLP) have demonstrated the importance of pre-trained language models for improving performance across a diverse set of tasks. Traditional approaches often rely on unidirectional models that condition on either the left or right context, limiting the richness of learned representations. Modern architectures, such as Transformers and bidirectional LSTM-based models, have expanded the ability to capture comprehensive contextual information. Techniques like ELMo utilize bidirectional LSTMs to generate deep contextualized word embeddings, while models such as OpenAI GPT employ Transformer architectures with a unidirectional left-to-right focus. These models form the foundation of many state-of-the-art NLP systems, addressing challenges in tasks like textual entailment, question answering, and named entity recognition. Enhancing these pre-trained models to incorporate richer bidirectional context remains a central theme in advancing the field.
+Previous approaches have made significant strides in improving language representations, yet they retain notable limitations. Peters et al. (2018) propose ELMo, a bidirectional LSTM-based model that enhances NLP tasks by generating contextualized embeddings. However, its architecture relies on independently trained left-to-right and right-to-left LSTMs combined at a shallow level, which restricts the depth of bidirectionality and the representation’s completeness. Similarly, Radford et al. (2018) [VERIFICAR] introduce GPT, a Transformer-based model pre-trained in a unidirectional left-to-right manner. While GPT achieves strong performance, its unidirectional nature limits its ability to fully leverage context from both preceding and succeeding tokens. Together, these models fall short of capturing deep, truly bidirectional context, highlighting a gap that motivates the development of more fully bidirectional pre-training methods.
+The approach presented addresses these limitations by introducing a deeply bidirectional Transformer encoder that is pre-trained using two novel tasks: the Masked Language Model (Masked LM) and Next Sentence Prediction. This design enables the model to learn comprehensive context representations by conditioning on both left and right contexts simultaneously, overcoming the unidirectional constraints observed in prior models. By pre-training with these objectives, the model generates rich, fully bidirectional representations that can be fine-tuned for a wide array of natural language processing tasks without requiring task-specific architectural changes. This approach directly tackles the gap left by earlier models that either lacked deep bidirectionality or were limited by their unidirectional training, establishing a more versatile and effective framework for language understanding.
+- Introduction of deep bidirectional pre-training based on Transformers.
+- Combined use of Masked Language Model and Next Sentence Prediction tasks to capture context from both directions.
+- Demonstration of state-of-the-art improvements on eleven natural language processing tasks including GLUE, SQuAD v1.1 and v2.0, SWAG, among others.
+- Provision of pre-trained models and open-source code to the community (https://github.com/google-research/bert).
+- Comprehensive analysis of model ablations, including effects of model size and contribution of individual layers.
+The validation of the proposed work is conducted through fine-tuning experiments across eleven diverse natural language processing tasks, encompassing text classification, natural language inference, question answering, and benchmarks such as GLUE and SWAG. These experiments provide empirical evidence supporting the effectiveness and generality of the approach, demonstrating improvements in key evaluation metrics such as accuracy and F1 scores compared to prior state-of-the-art methods.
+The remainder of the article is organized into sections that first cover the pre-training tasks and detailed descriptions of the model components. This is followed by comprehensive experimental sections presenting the results and analyses, including ablation studies and discussions. The document is structured in a technical manner to thoroughly explain the model architecture, datasets, fine-tuning procedures, experiments, and corresponding analyses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="200" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Aplicación de Redes Neuronales Artificiales para la Clasificación de Actividades de la Vida Diaria en Sujetos con Enfermedad de Párkinson</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Español</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>La Enfermedad de Parkinson (EP) se caracteriza por ser una afección crónica y progresiva provocada por el deterioro neuronal en la sustancia nigra y la disminución de los niveles de dopamina en el cuerpo [1]. La enfermedad de Párkinson no es curable, por lo que el objetivo de los tratamientos es exclusivamente sintomático [2]. El manejo farmacológico es el principal tratamiento del paciente con EP. Se requiere de un tratamiento que incluya diversas disciplinas en su manejo para promover la participación del paciente en la sociedad y fomentar la actividad física desde el momento del diagnóstico con la finalidad de adquirir estrategias de movimiento antes de presentar limitaciones físicas y cognitivas más severas [3]. A pesar del óptimo tratamiento 70 % de los pacientes con enfermedad de Parkinson experimentan momentos donde los síntomas motores como tremor, bradicinesia e inestabilidad postural empeoran, estos momentos son conocidos como fluctuaciones motoras [4].
+El seguimiento de las fluctuaciones de los síntomas motores en pacientes con enfermedad de Párkinson se realiza actualmente a través de la autoevaluación subjetiva de los pacientes. Sin embargo, los médicos y especialistas requieren información objetiva y más confiable sobre la ocurrencia de las fluctuaciones para permitir una planeación precisa del tratamiento [5].
+La evaluación mediante sensores inerciales de los signos motores y fluctuaciones, pueden proporcionar retroalimentación objetiva y confiable sobre los efectos del manejo terapéutico [6]. A la fecha este tipo de sensores han sido estudiados para detectar actividades de la vida diaria, principalmente caminar y en pocos casos acostarse, sentarse y mantenerse de pie [7][8][9]. En estas investigaciones se han utilizado diversos tipos, números, ubicaciones de sensores y métodos de clasificación variables sin alcanzar un consenso a la fecha. Principalmente se ha utilizado una configuración de un sensor predominantemente en la cadera y de tipo acelerómetro [7][8][9]. Aunque los primeros experimentos se concentraban en la validación de laboratorio de los registros obtenidos con los sensores inerciales, actualmente el interés parece concentrarse en probar nuevos métodos de clasificación centrados en un propósito clínico, con precisiones reportadas entre un 55.9% y 90.8% [8][9][10].
+La clasificación de actividades de la vida diaria utilizando Redes Neuronales Artificiales (RNA) ha demostrado el alto potencial de aplicar Deep Learning a la resolución de los problemas en la clasificación de señales realizadas por pacientes con Enfermedad de Párkinson. Estas herramientas han ayudado a desarrollar nuevas posibilidades de apoyo para que los especialistas puedan llevar a cabo evaluaciones más certeras de la funcionalidad motora y de los tratamientos proporcionados mediante una mejor calidad de monitoreo en la rehabilitación de los pacientes. El uso de inteligencia artificial para ayudar a la detección y tratamiento de la EP es de creciente interés para médicos e investigadores alrededor del mundo [11]. Actualmente se está trabajando en el desarrollo de diversos métodos de inteligencia artificial basados en algoritmos de aprendizaje profundo que permitan la detección y poder hacer un seguimiento de los principales síntomas motores de la Enfermedad de Párkinson [12].
+De acuerdo con el estudio donde las RNA son utilizadas para clasificar las AVDs desempeñadas por 5 pacientes con Enfermedad de Párkinson, se obtuvo un porcentaje de exactitud del 99 % en el aprendizaje de clasificación [13]. Por lo que en este trabajo se busca obtener un método con resultados semejantes, pero realizando reducción de dimensionalidad de la base de datos a través de la extracción de la información más relevante para la clasificación de actividades de la vida diaria utilizando sensores inerciales.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>﻿El monitoreo de pacientes con Enfermedad de Parkinson (EP) representa un área de gran relevancia clínica debido a la complejidad y heterogeneidad de los síntomas motores característicos de esta patología. Los avances en sensores inerciales portátiles y técnicas de inteligencia artificial, particularmente las redes neuronales artificiales, han permitido desarrollar sistemas automáticos que facilitan la evaluación continua y objetiva de la función motora en estos pacientes. En este contexto, la combinación de sensores wearables con metodologías como el Análisis de Componentes Principales (PCA) y modelos de perceptrón multicapa (MLP) ha mostrado ser una estrategia efectiva para capturar y clasificar actividades de la vida diaria, contribuyendo así a un mejor seguimiento clínico y a la mejora en la calidad de la rehabilitación. Estos desarrollos se apoyan en un cuerpo de trabajo previo que ha explorado la aplicación de tecnologías similares en pacientes con EP y otros trastornos motores, consolidando un estado del arte que enfatiza la necesidad de soluciones precisas, adaptables y no invasivas para el monitoreo funcional en entornos reales.
+A pesar de los avances descritos en el territorio, persisten limitaciones importantes en el trabajo previo que motivan la presente investigación. Jung et al. (2020) destacan que los algoritmos desarrollados en entornos controlados enfrentan desafíos significativos para aplicarse eficazmente a datos obtenidos en condiciones naturales y no estructuradas, especialmente en poblaciones con patologías como la Enfermedad de Parkinson. Asimismo, Nguyen et al. (2018) señalan la ausencia de métodos robustos para la detección y segmentación automática de actividades complejas y no estructuradas de la vida diaria en pacientes con Parkinson, lo que limita la evaluación precisa y continua de su movilidad en entornos libres o simulados.
+Por otra parte, Pérez Sanpablo et al. (2021) evidencian las bajas precisiones, en torno al 60%, alcanzadas por técnicas clásicas de análisis discriminante para la clasificación de actividades en esta población, indicando la necesidad de enfoques más precisos y adaptados. Rast y Labruyère (2020) agregan que la heterogeneidad metodológica, la falta de estándares y la escasa evaluación de la usabilidad de los sistemas actuales dificultan la adopción clínica y el seguimiento efectivo. Finalmente, Rodríguez Montero et al. (2023) muestran que, aunque se han empleado redes neuronales para la clasificación de actividades de vida diaria en pacientes con EP, los resultados no alcanzan la precisión óptima y se podrían mejorar mediante técnicas avanzadas de selección de características y modelos profundos.
+Estos vacíos y limitaciones en el estado del arte justifican la necesidad de desarrollar y validar nuevas metodologías que permitan una clasificación más precisa, robusta y eficiente de las actividades en pacientes con EP, considerando bases de datos reales y desequilibradas, y sistemas que faciliten su aplicación clínica práctica.
+Como respuesta directa a estas limitaciones, el presente trabajo propone el uso de Redes Neuronales Artificiales multicapa diseñadas y entrenadas con señales inerciales que han sido previamente preprocesadas y reducidas dimensionalmente mediante Análisis de Componentes Principales (PCA). Esta combinación metodológica tiene sentido frente a las carencias identificadas porque permite una clasificación automática avanzada, alcanzando altas precisiones y superando los métodos clásicos de clasificación, como los análisis discriminantes, que mostraron resultados inferiores. Además, el enfoque se adapta eficazmente a bases de datos desbalanceadas y heterogéneas, como las que se encuentran en estudios con pacientes con Enfermedad de Parkinson, garantizando así un desempeño robusto y una mejor generalización para la identificación de actividades específicas de la vida diaria.
+Este enfoque aprovecha la versatilidad y capacidad de aprendizaje profundo de las redes neuronales para modelar patrones complejos en los datos recogidos en entornos naturales y no estructurados, abordando directamente los retos señalados en la detección y segmentación de actividades múltiples y variadas. Además, la reducción dimensional mediante PCA contribuye a la eficiencia y practicidad del sistema, facilitando su potencial implementación clínica para el seguimiento continuo y objetivo de pacientes con patologías motoras.
+- Desarrollo de un sistema basado en una red neuronal artificial de perceptrón multicapa (MLP) para la clasificación precisa de seis actividades de la vida diaria en pacientes con Enfermedad de Parkinson.  
+- Uso de técnicas de reducción dimensional mediante Análisis de Componentes Principales (PCA) para mejorar la eficiencia del modelo sin perder precisión.  
+- Evaluación exhaustiva del modelo mediante validación cruzada y comparación con otros clasificadores como análisis discriminante lineal y Naïve Bayes.  
+- Propuesta de configuraciones y recomendaciones para facilitar la aplicación práctica futura, incluyendo la reducción del número de sensores para mayor comodidad y menor costo.  
+- Implementación y codificación del sistema en Python, utilizando librerías especializadas que permiten la reproducibilidad y la extensión del desarrollo.
+La validación del trabajo se llevó a cabo mediante la utilización de una extensa base de datos que incluye 179,755 observaciones registradas por sensores inerciales ubicados en diferentes partes del cuerpo de pacientes con Enfermedad de Parkinson. Para respaldar las contribuciones propuestas, se aplicó una validación cruzada con particionamiento en 10 subconjuntos (10-fold), lo que permitió evaluar la robustez y capacidad generalizadora del modelo. Además, se comparó el desempeño de la red neuronal con seis clasificadores alternativos, analizando detalladamente la matriz de confusión y los patrones de error asociados a las diferentes actividades, lo que fortaleció la confianza en la efectividad y precisión de la propuesta para la clasificación automática de actividades de la vida diaria en esta población.
+El resto del documento se organiza en las siguientes secciones, donde se desarrollan de manera detallada la metodología empleada, los resultados obtenidos, la discusión de los hallazgos y las conclusiones del estudio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="200" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>SimulateIoT: Domain Specific Language to Design, Code Generation and Execute IoT Simulation Environments</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Inglés</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>The Internet of Things (IoT) is widely applied in several areas such as smart-cities, home environments, agriculture, industry, intelligent buildings, etc. [46]. Usually, these IoT environments require using hundreds of sensors and actuators shared throughout these areas which are generating a vast amount of data. Data must be suitably stored, analysed and published using Big Data or Stream Processing techniques. Big Data or Stream Processing techniques must be applied to conveniently store and analyse published data. Taking into account where data are processed and stored, the IoT environment architecture can be defined by several computing layers (Edge, Fog and Cloud computing (see Figure 1) [30]). Edge layer is defined closer to data generators, Fog layer resides on top of the edge and act as intermediary layer with limited storing and processing capabilities and Cloud layer is defined with full storing and processing capabilities. Thus, the development of IoT systems requires the management and integration of conveniently heterogeneous technologies such as devices, actuators, databases, communication protocols, stream processing engines, etc. As a consequence, in order to implement, deploy and test the IoT systems a high investment must be made in time, money and effort.
 Simulating IoT environments is one way to decrease this initial investment because the users can measure and dimension the artefacts needed to deploy and interconnect the systems. Thus, these artefacts can include several kinds of devices from sensors or actuators to NoSQL databases, messaging brokers or stream processor engines. However, although there are several simulation environments for wireless sensor networks (WSN), there is a lack of IoT simulator tools for designing IoT environments at a high level that enable modeling this kind of systems by using the domain concepts and relationships. In addition, there is a lack of IoT simulation tools that makes it possible to deploy the IoT system on multiple nodes in order to test the communications among the system's elements and where complex IoT components such as databases, complex event processing or message brokers can be suitable deployed and tested.
@@ -536,23 +607,22 @@
 The rest of the paper is structured as follows. In Section 2, we give an overview of existing IoT simulation approaches centered on both low level and high level IoT simulation environments. In Section 3, we present the SimulateIoT methodology. Section 4 describes SimulateIoT design and implementation phases including the SimulateIoT metamodel, the graphical editor and the model-to-text transformation developed. In Section 5 two case studies are presented. Finally, Section 6 elaborates on the limitations of the presented approach before Section 7 concludes the paper.</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>﻿La simulación de sistemas del Internet de las Cosas (IoT) constituye el área de trabajo principal, dada la alta inversión en desarrollo, despliegue y pruebas que requieren estos proyectos antes de su implementación física. La simulación permite modelar y razonar sobre los sistemas IoT, facilitando la optimización y reducción de costos asociados. En la literatura existen dos grandes enfoques: simuladores a nivel bajo que se centran en aspectos de hardware, redes y capacidades de los nodos; y simuladores a nivel alto que abordan el modelado de entornos, dispositivos y servicios mediante lenguajes específicos de dominio (DSL) o desarrollo guiado por modelos (MDD).
-A pesar de estos avances, muchas herramientas disponibles demandan elevadas competencias técnicas, carecen de interfaces gráficas amigables, no ofrecen generación automática de código o no cuentan con mecanismos para validar previamente el entorno simulado. Asimismo, varios simuladores no contemplan adecuadamente conceptos clave emergentes en el ámbito IoT, como las arquitecturas de fog computing y cloud computing, el procesamiento de eventos complejos y los protocolos de comunicación publish-subscribe, todos ellos fundamentales para la correcta representación y simulación de sistemas IoT modernos y heterogéneos.
-Aunque existen diversas propuestas para la simulación de sistemas IoT, varios trabajos muestran limitaciones que evidencian la necesidad de nuevos enfoques. Alwasel et al. (2020) [VERIFICAR] con BigDataSDNSim se centran en la simulación de datos masivos en entornos cloud SDN, pero no ofrecen un modelado integral de simulación IoT que abarque un alto nivel de abstracción a través de múltiples capas arquitectónicas. Clemente et al. (2018) [VERIFICAR] desarrollaron un lenguaje específico de dominio para domótica, pero su enfoque no contempla la simulación ni aspectos relacionados con almacenamiento o procesamiento basados en eventos. Por su parte, Mehdi et al. (2014) [VERIFICAR] con CupCarbon proporcionan un simulador gráfico para redes de sensores WSN, sin embargo, no modelan almacenamiento avanzado, procesamiento complejo ni la comunicación mediante protocolos publish-subscribe con brokers. Finalmente, Zeng et al. (2017) con IOTSim abordan la simulación de aplicaciones IoT en cloud con un enfoque en big data, pero su herramienta exige configuraciones técnicas complejas y carece de diseño gráfico y validación previa de los modelos.
-En conjunto, estos trabajos presentan carencias importantes como la ausencia de abstracción visual adecuada para la representación de simulaciones IoT que integren las capas Edge, Fog y Cloud; una dependencia significativa en configuraciones técnicas de bajo nivel; la falta de generación automática de código integral y despliegue mediante arquitecturas basadas en microservicios; y la inexistencia de mecanismos para validar modelos antes de la simulación, aspectos clave para la viabilidad y usabilidad de entornos de simulación IoT modernos y representativos.
-La propuesta central de este trabajo consiste en el desarrollo de SimulateIoT, un enfoque basado en desarrollo guiado por modelos que permite definir, generar código y desplegar entornos de simulación IoT complejos sin necesidad de programación manual. Este enfoque incluye un metamodelo de dominio que representa de forma integral los conceptos clave del IoT, una sintaxis gráfica para facilitar el modelado visual del sistema y una transformación modelo-texto que genera automáticamente el código asociado, que incluye microservicios, contenedores Docker, brokers MQTT, bases de datos NoSQL y motores para el procesamiento de eventos y flujos de datos. La comunicación entre los distintos nodos IoT, como sensores, actuadores y nodos fog y cloud, se gestiona mediante un protocolo de publicación-suscripción, lo que permite una simulación fiel a arquitecturas reales y heterogéneas. Además, se incorporan mecanismos para la validación del modelo y para la monitorización durante la simulación, lo que garantiza la calidad y el control del entorno simulado.
-Este enfoque se adapta a las carencias detectadas en trabajos previos, al ofrecer una abstracción visual adecuada y una completa integración de las capas Edge, Fog y Cloud, facilitando la generación automática de código y el despliegue en arquitecturas modernas basadas en microservicios. De esta forma, SimulateIoT responde a la necesidad de contar con herramientas que simplifiquen el diseño y la ejecución de simulaciones IoT complejas, manteniendo una alta fidelidad con respecto a las arquitecturas actuales y reduciendo drásticamente la necesidad de configuraciones técnicas complejas o conocimiento especializado para su uso.
-- Definición de un metamodelo que captura conceptos IoT a alto nivel, abarcando capas Edge, Fog, Cloud, sensores, actuadores, bases de datos, procesamiento de eventos y comunicación (Sección III.A).
-- Desarrollo de una sintaxis gráfica para modelar estos sistemas (Sección III.B).
-- Implementación de reglas OCL para la validación del modelo en base a restricciones estructurales y semánticas (Sección III.B).
-- Creación de transformaciones modelo-texto en Acceleo para generar código completo que materializa los modelos en microservicios desplegables (Sección III.C).
-- Implementación del sistema de despliegue y ejecución sobre Docker Swarm y monitorización integrada (Sección III.D).
-- Presentación de dos estudios de caso reales (edificio inteligente y agricultura) mostrando la capacidad descriptiva, generación y despliegue (Sección V).
-- Discusión sobre las limitaciones y futuras extensiones para movilidad y dinámicas de la simulación (Sección VI).
-La validación del trabajo se lleva a cabo mediante la aplicación de dos estudios de caso prácticos que ejemplifican y respaldan las contribuciones propuestas. El primer estudio simula un edificio inteligente compuesto por múltiples nodos fog distribuidos por diferentes edificios, integrando sensores de temperatura, presencia y humo, junto con reglas para el control automatizado de sistemas como la calefacción, monitorizados mediante bases de datos y motores de procesamiento de eventos complejos. El segundo estudio de caso se centra en un entorno agrícola, donde se simulan sensores para medir variables como temperatura, humedad, pH y presión de agua, junto con actuadores de riego, utilizando arquitecturas basadas en nodos fog y cloud, almacenamiento en bases de datos MongoDB y reglas para notificaciones y control. Ambos casos de estudio permiten la generación automática de código, su despliegue en contenedores Docker y la ejecución completa de la simulación, demostrando así la expresividad, aplicabilidad y viabilidad del enfoque presentado.
-El resto del documento se organiza en varias secciones que incluyen una revisión del estado del arte, la presentación de la metodología SimulateIoT, una descripción detallada del metamodelo y las herramientas desarrolladas, la implementación del sistema de despliegue y ejecución, la exposición de casos de estudio aplicados, así como una discusión sobre las limitaciones detectadas y las conclusiones derivadas del trabajo.</t>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>﻿The Internet of Things (IoT) is increasingly applied across various domains such as smart cities, smart homes, agriculture, and industrial environments. However, developing, deploying, and testing IoT projects require significant investments in hardware components like devices, fog nodes, cloud nodes, and analytics infrastructure, as well as substantial software development efforts. To mitigate these costs, simulation environments for IoT systems are essential as they facilitate system modeling, reasoning, and optimization prior to actual deployment.
+Existing IoT simulation environments predominantly focus on low-level aspects such as network protocols, sensor hardware, and motes, demanding advanced technical knowledge and programming skills from users. These tools often lack high-level abstractions for IoT concepts, such as Edge, Fog, and Cloud layers, and do not provide intuitive modeling or deployment mechanisms. Therefore, there is a pressing need for approaches that enable the design and execution of complex IoT simulations using domain-specific abstractions — including sensors, actuators, heterogeneous nodes, publish-subscribe communication, microservices, and containerization technologies — all within a user-friendly model-driven development framework.
+Several existing approaches have addressed aspects of IoT simulation but exhibit notable limitations that motivate further research. Alwasel et al. (2020) [VERIFICAR] simulate Big Data and software-defined networks in cloud environments but lack graphical interfaces and validation mechanisms for pre-configuration of IoT simulation environments. Levis et al. (2003) with Tossim focus on low-level simulation of TinyOS nodes without defining IoT communication patterns or modeling high-level processes, limiting the scope of IoT system representation. Mehdi et al. (2014) propose CupCarbon, which allows graphical simulation of IoT contexts but does not support modeling of storage or complex protocols such as publish/subscribe. Patel and Cassou (2015) offer IoTSuite to facilitate IoT application development, yet it does not encompass simulation capabilities nor modeling of storage and complex processing. Finally, Zeng et al. (2017) present IOTSim, a cloud IoT application simulator focused on big data processing, but without tools for high-level graphical modeling of entire IoT architectures.
+In summary, these works generally lack a comprehensive high-level domain-specific language with validation support, comprehensive modeling across the entire IoT architecture layers (Edge, Fog, Cloud), integrated support for publish-subscribe communication protocols, and deployment mechanisms leveraging containerized microservices. These gaps highlight the need for solutions that unify high-level modeling, validation, flexible communication abstractions, and realistic deployment strategies in IoT simulation.
+The central proposal of this work is a model-driven development approach to define, generate code for, and deploy IoT simulations. This approach is based on a domain-specific metamodel named SimulateIoT, which provides high-level abstractions representing sensors, actuators, and heterogeneous nodes across Edge, Fog, and Cloud layers. A graphical concrete syntax facilitates intuitive visual modeling, while Object Constraint Language (OCL) rules ensure model validation. From these validated models, model-to-text transformations automatically generate all necessary components, including microservices, MQTT brokers, NoSQL databases, complex event processing engines, and Docker containers for deployment.
+This comprehensive framework explicitly addresses the gaps found in prior work by unifying the full IoT architectural stack within a single, validated modeling language that supports publish-subscribe communication patterns and leverages containerized microservice deployment. By doing so, it enables users to efficiently design complex IoT simulation environments and execute them realistically without manual coding, thus overcoming limitations related to low-level focus, lack of high-level modeling support, and inadequate deployment automation.
+- Development of a comprehensive metamodel for IoT simulation that encompasses devices, nodes, communication protocols, storage, and processing capabilities (Sections III and IV).
+- Creation of a graphical concrete syntax that enables the design of simulation models conforming to the metamodel and supports OCL-based validation to ensure model correctness (Section IV-B).
+- Implementation of a model-to-text transformation workflow that automates the generation of all required code and deployment artefacts for the simulation environment (Section IV-C).
+- Integration with industrial technologies, including Docker containers, MQTT communication brokers, and complex event processing engines such as Esper and WSO2, facilitating realistic simulation and seamless deployment (Section IV-D).
+- Presentation of two detailed case studies—one in a smart building environment and another in an agricultural setting—that demonstrate the expressiveness and applicability of the proposed approach (Section V).
+- Development and deployment of a fully operational simulation platform featuring monitoring and real-time data analysis capabilities, allowing users to observe and analyze system behavior during execution (Sections V and VI).
+The validation of this work is conducted through two comprehensive case studies situated in distinct IoT domains: a smart building environment and an agricultural setting. These case studies demonstrate the modeling, code generation, deployment, and execution phases using Docker technology, showcasing the realistic simulation of complex IoT systems composed of various sensors, actuators, and heterogeneous nodes spanning Edge, Fog, and Cloud layers. The evaluation highlights the system’s capability for real-time data analysis, integrated monitoring, event management, and rule-based actions, thereby substantiating the expressiveness and practical applicability of the proposed model-driven development approach.
+The remainder of the article is organized into clearly differentiated main sections that guide the reader from the motivation behind the work through related research, the proposed SimulateIoT methodology, the design and implementation of supporting tools, detailed case studies focused on smart building and agricultural environments, and culminating with discussions on limitations, target users, and technologies, followed by conclusions and future work. This structured organization facilitates a comprehensive understanding of the development and application of the presented IoT simulation framework.</t>
         </is>
       </c>
     </row>

--- a/introducciones/comparacion_introducciones.xlsx
+++ b/introducciones/comparacion_introducciones.xlsx
@@ -609,20 +609,19 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>﻿The Internet of Things (IoT) is increasingly applied across various domains such as smart cities, smart homes, agriculture, and industrial environments. However, developing, deploying, and testing IoT projects require significant investments in hardware components like devices, fog nodes, cloud nodes, and analytics infrastructure, as well as substantial software development efforts. To mitigate these costs, simulation environments for IoT systems are essential as they facilitate system modeling, reasoning, and optimization prior to actual deployment.
-Existing IoT simulation environments predominantly focus on low-level aspects such as network protocols, sensor hardware, and motes, demanding advanced technical knowledge and programming skills from users. These tools often lack high-level abstractions for IoT concepts, such as Edge, Fog, and Cloud layers, and do not provide intuitive modeling or deployment mechanisms. Therefore, there is a pressing need for approaches that enable the design and execution of complex IoT simulations using domain-specific abstractions — including sensors, actuators, heterogeneous nodes, publish-subscribe communication, microservices, and containerization technologies — all within a user-friendly model-driven development framework.
-Several existing approaches have addressed aspects of IoT simulation but exhibit notable limitations that motivate further research. Alwasel et al. (2020) [VERIFICAR] simulate Big Data and software-defined networks in cloud environments but lack graphical interfaces and validation mechanisms for pre-configuration of IoT simulation environments. Levis et al. (2003) with Tossim focus on low-level simulation of TinyOS nodes without defining IoT communication patterns or modeling high-level processes, limiting the scope of IoT system representation. Mehdi et al. (2014) propose CupCarbon, which allows graphical simulation of IoT contexts but does not support modeling of storage or complex protocols such as publish/subscribe. Patel and Cassou (2015) offer IoTSuite to facilitate IoT application development, yet it does not encompass simulation capabilities nor modeling of storage and complex processing. Finally, Zeng et al. (2017) present IOTSim, a cloud IoT application simulator focused on big data processing, but without tools for high-level graphical modeling of entire IoT architectures.
-In summary, these works generally lack a comprehensive high-level domain-specific language with validation support, comprehensive modeling across the entire IoT architecture layers (Edge, Fog, Cloud), integrated support for publish-subscribe communication protocols, and deployment mechanisms leveraging containerized microservices. These gaps highlight the need for solutions that unify high-level modeling, validation, flexible communication abstractions, and realistic deployment strategies in IoT simulation.
-The central proposal of this work is a model-driven development approach to define, generate code for, and deploy IoT simulations. This approach is based on a domain-specific metamodel named SimulateIoT, which provides high-level abstractions representing sensors, actuators, and heterogeneous nodes across Edge, Fog, and Cloud layers. A graphical concrete syntax facilitates intuitive visual modeling, while Object Constraint Language (OCL) rules ensure model validation. From these validated models, model-to-text transformations automatically generate all necessary components, including microservices, MQTT brokers, NoSQL databases, complex event processing engines, and Docker containers for deployment.
-This comprehensive framework explicitly addresses the gaps found in prior work by unifying the full IoT architectural stack within a single, validated modeling language that supports publish-subscribe communication patterns and leverages containerized microservice deployment. By doing so, it enables users to efficiently design complex IoT simulation environments and execute them realistically without manual coding, thus overcoming limitations related to low-level focus, lack of high-level modeling support, and inadequate deployment automation.
-- Development of a comprehensive metamodel for IoT simulation that encompasses devices, nodes, communication protocols, storage, and processing capabilities (Sections III and IV).
-- Creation of a graphical concrete syntax that enables the design of simulation models conforming to the metamodel and supports OCL-based validation to ensure model correctness (Section IV-B).
-- Implementation of a model-to-text transformation workflow that automates the generation of all required code and deployment artefacts for the simulation environment (Section IV-C).
-- Integration with industrial technologies, including Docker containers, MQTT communication brokers, and complex event processing engines such as Esper and WSO2, facilitating realistic simulation and seamless deployment (Section IV-D).
-- Presentation of two detailed case studies—one in a smart building environment and another in an agricultural setting—that demonstrate the expressiveness and applicability of the proposed approach (Section V).
-- Development and deployment of a fully operational simulation platform featuring monitoring and real-time data analysis capabilities, allowing users to observe and analyze system behavior during execution (Sections V and VI).
-The validation of this work is conducted through two comprehensive case studies situated in distinct IoT domains: a smart building environment and an agricultural setting. These case studies demonstrate the modeling, code generation, deployment, and execution phases using Docker technology, showcasing the realistic simulation of complex IoT systems composed of various sensors, actuators, and heterogeneous nodes spanning Edge, Fog, and Cloud layers. The evaluation highlights the system’s capability for real-time data analysis, integrated monitoring, event management, and rule-based actions, thereby substantiating the expressiveness and practical applicability of the proposed model-driven development approach.
-The remainder of the article is organized into clearly differentiated main sections that guide the reader from the motivation behind the work through related research, the proposed SimulateIoT methodology, the design and implementation of supporting tools, detailed case studies focused on smart building and agricultural environments, and culminating with discussions on limitations, target users, and technologies, followed by conclusions and future work. This structured organization facilitates a comprehensive understanding of the development and application of the presented IoT simulation framework.</t>
+          <t>﻿The Internet of Things (IoT) is increasingly applied across diverse domains such as smart cities, agriculture, industry, and home environments. Developing and testing real IoT systems typically demands significant investments in devices, fog and cloud nodes, hardware, and software, as well as considerable time and effort. Consequently, simulation environments have become essential tools to model IoT systems, enabling analysis and optimization without the need for physical deployment. This capability facilitates the development process by reducing costs and complexity.
+The state of the art in IoT simulation comprises a broad spectrum of approaches. On the one hand, there are low-level simulators focused primarily on network-level and hardware details. On the other, there are model-driven development (MDE) approaches for IoT systems that enable higher-level abstractions. However, existing solutions generally do not fully integrate complex aspects such as event processing or the architectural layers of Edge, Fog, and Cloud computing at a high abstraction level. This leaves room for approaches that can represent and simulate comprehensive IoT environments with detailed architectural considerations.
+Previous works in the area present important limitations that restrict their applicability to comprehensive IoT simulation. Alwasel et al. (2020) [VERIFICAR] propose simulators oriented to big data analysis and cloud IoT environments but lack a graphical interface and have not demonstrated validation in pre-configured environments. Clemente et al. (2018) apply model-driven development techniques to complex event processing but do not address modeling or simulation of IoT environments. Levis et al. (2003) developed TinyOS and a simulator focused on low-level mote simulation, lacking a focus on high-level IoT simulation. Mehdi et al. (2014) present simulators for sensor networks emphasizing events and multi-agent models; however, these do not employ model-driven development for system modeling. Zeng et al. (2017) created IoTSim to analyze IoT applications in cloud contexts but do not provide visual design tools nor support for simulating heterogeneous IoT environments. Papadopoulos et al. (2013) enable an experimental platform focused on wireless sensor networks limited to sensors, without full IoT system modeling. Collectively, these approaches cover partial aspects of IoT simulation or model-driven development, yet none offer an integrated visual language and a complete cycle encompassing design, validation, code generation, and deployment of simulated IoT environments with layered Edge, Fog, and Cloud architectures.
+This work proposes SimulateIoT, a domain-specific language (DSL) and an accompanying set of tools grounded in model-driven development to address the identified gaps in IoT simulation. The approach enables users to define high-level simulated IoT environments incorporating sensors, actuators, and computing nodes distributed across Edge, Fog, and Cloud layers. By modeling the relationships among components, data flows, complex event processing rules, and storage mechanisms, it facilitates the comprehensive representation of IoT systems.
+The use of a graphical editor combined with model-to-text transformations allows automatic generation of deployable artifacts in the form of Docker microservices, which can be instantiated and monitored in real-time. This integrated methodology supports a complete lifecycle—from design and validation to code generation and deployment—thus overcoming limitations of prior work that either lacked visual modeling tools, deployment automation, or did not fully consider the architectural layering inherent in modern IoT systems.
+- Definition of the SimulateIoT DSL for modeling simulated IoT environments (Sections III and IV).
+- A metamodel encompassing sensors, actuators, processing nodes, communication topics, and processing rules (Section IV-A).
+- A graphical editor to visually design IoT environments (Section IV-B).
+- An automatic code generation engine that produces microservices and supports deployment using Docker Swarm (Section IV-C).
+- A deployment and monitoring framework for simulated environments incorporating NoSQL databases, MQTT brokers, and Complex Event Processing (CEP) engines (Section IV-D).
+- Two case studies applied to smart buildings and agricultural environments to validate expressiveness and functionality (Section V).
+The validation of the proposed approach is conducted through two detailed case studies that model complex IoT environments: a smart university building with multiple sensors, actuators, and Fog/Cloud nodes, and an agricultural environment designed for irrigation using sensors for humidity, pH, temperature, and automated actuators. These case studies demonstrate the capability to generate code and deploy the simulated environments using Docker and microservices, supporting real-time simulation, data processing, monitoring, and the definition of complex event-driven behaviors.
+The remainder of the article is organized into several sections that include the introduction, related work, the SimulateIoT methodology, the design and implementation of the tools (covering the metamodel, graphical editor, model-to-text transformations, and deployment), detailed case studies on smart buildings and agricultural environments, followed by a discussion of limitations, concluding remarks, and references.</t>
         </is>
       </c>
     </row>
